--- a/audiobooks.xlsx
+++ b/audiobooks.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15000" yWindow="660" windowWidth="15240" windowHeight="17260" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mystery &amp; Thriller" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kids &amp; Family" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parenting &amp; Relationships" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Religion &amp; Spirituality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teen &amp; Young Adult" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Business &amp; Careers" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Entertainment Biography" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SciFi &amp; Fantasy" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Self-Help" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Romance" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Top" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Romance" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Mystery &amp; Thriller" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Kids &amp; Family" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Parenting &amp; Relationships" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="History" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Religion &amp; Spirituality" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Teen &amp; Young Adult" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Business &amp; Careers" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Entertainment Biography" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="SciFi &amp; Fantasy" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Self-Help" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -729,31 +729,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Fellowship of the Ring</t>
+          <t>A Little More Social: How Small Choices Create Unexpected Happiness, Health, and Connection</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>J.R.R. Tolkien</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>George Allen &amp; Unwin</t>
+          <t>Nicholas Epley</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>29/07/1954</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -762,31 +749,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fourth Wing</t>
+          <t>The Psychology of Money: Timeless lessons on wealth, greed, and happiness</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rebecca Yarros</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Red Tower Books</t>
+          <t>Morgan Housel</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>02/05/2023</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -795,27 +769,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Red Rising</t>
+          <t>Never Split the Difference: Unlock Your Persuasion Potential in Professional and Personal Life</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pierce Brown</t>
+          <t>Chris Voss, Tahl Raz</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Del Rey Books</t>
+          <t>Harper Business</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28/01/2014</t>
+          <t>17/05/2016</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -828,31 +802,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Throne of Glass</t>
+          <t>How to Talk to Anyone and Be More Charismatic: Improve Communication &amp; People Skills, Master Small Talk, Build Confidence &amp; Influence, Overcome Social Anxiety, and Make Friends in Any Conversation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>Nathan Soren</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bloomsbury Publishing</t>
+          <t>Independently Published</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>02/08/2012</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+          <t>03/07/2025</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -861,27 +832,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A Court of Wings and Ruin</t>
+          <t>Extreme Ownership: How U.S. Navy SEALs Lead and Win</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>Jocko Willink, Leif Babin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bloomsbury Publishing</t>
+          <t>St. Martin's Press</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>02/05/2017</t>
+          <t>01/10/2015</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -894,27 +865,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Heir of Fire</t>
+          <t>Unreasonable Hospitality: The Remarkable Power of Giving People More Than They Expect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>Will Guidara</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Optimism Press</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>02/09/2014</t>
+          <t>25/10/2022</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -927,27 +898,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Iron Flame</t>
+          <t>The 7 Habits of Highly Effective People: 30th Anniversary Edition</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rebecca Yarros</t>
+          <t>Stephen R. Covey, Sean Covey</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Red Tower Books (Entangled Publishing)</t>
+          <t>Free Press</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07/11/2023</t>
+          <t>01/01/1989</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -960,27 +931,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A Game of Thrones: A Song of Ice and Fire: Book One</t>
+          <t>Think and Grow Rich</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>George R. R. Martin</t>
+          <t>Napoleon Hill</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bantam Spectra</t>
+          <t>The Ralston Society</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/08/1996</t>
+          <t>01/01/1937</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -993,27 +964,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Crown of Midnight</t>
+          <t>Think and Grow Rich! The Original Version, Restored and Revised</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>Napoleon Hill, Ross Cornwell</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bloomsbury USA</t>
+          <t>The Ralston Society</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/08/2013</t>
+          <t>01/03/1937</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1026,31 +997,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Two Towers</t>
+          <t>Future Rich Person: The New Rules for Building Wealth (Even if You're Stuck, Broke, and that Billionaire Won't Text You Back...)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>J.R.R. Tolkien</t>
+          <t>Haley Sacks</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>George Allen &amp; Unwin</t>
+          <t>Ballantine Books</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11/11/1954</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
+          <t>12/05/2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1119,31 +1087,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Not giving a F*ck Anymore.: Stop People-Pleasing, Set Boundaries, and Start Living on Your Own Terms.</t>
+          <t>Strangers: A Memoir of Marriage</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Marieme Seck</t>
+          <t>Belle Burden</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pck;</t>
+          <t>Dial Press</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25/01/2025</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
+          <t>13/01/2026</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1152,31 +1117,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
+          <t>This Is Me: A Reckoning</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>James Clear</t>
+          <t>Hayden Panettiere</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Avery Publishing</t>
+          <t>Grand Central Publishing</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16/10/2018</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
+          <t>19/05/2026</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1185,27 +1147,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Detached: How to Let Go, Heal, and Become Irresistible</t>
+          <t>I'm Glad My Mom Died</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sabrina Alexis Bendory</t>
+          <t>Jennette McCurdy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thought Catalog Books</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>09/08/2022</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1218,31 +1180,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Subtle Art of Not Giving a F*ck: A Counterintuitive Approach to Living a Good Life</t>
+          <t>Stripped Down: Unfiltered and Unapologetic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mark Manson</t>
+          <t>Bunnie Xo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HarperOne</t>
+          <t>Dey Street Books</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13/09/2016</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+          <t>17/02/2026</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1251,31 +1210,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12 Laws of the Universe</t>
+          <t>You with the Sad Eyes: A Memoir</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Manhardeep Singh</t>
+          <t>Christina Applegate</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Independently published</t>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20/10/2021</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+          <t>03/03/2026</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1284,31 +1240,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mastering Conversation Skills Goodbye Awkwardness. Learn to Master the Art of Conversation and Become A Great Communicator, Even if You've Always Been Shy or Hate Small Talk</t>
+          <t>Start With Yourself: A New Vision for Work &amp; Life</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Helen Stone</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Author's Republic</t>
+          <t>Emma Grede</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>31/03/2020</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1317,17 +1260,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NO DAYS OFF: The Art of Everyday</t>
+          <t>Smile, or You're Doing it Wrong: A Journey from Rock Bottom to Redemption</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dr James Rouse</t>
+          <t>Andy Glaze</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fox Chapel Publishing</t>
+          <t>Fedd Books</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1337,11 +1280,8 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>02/05/2013</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
+          <t>31/03/2026</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1350,27 +1290,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>How To Win Friends And Influence People</t>
+          <t>Kitchen Confidential: Adventures in the Culinary Underbelly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dale Carnegie</t>
+          <t>Anthony Bourdain, Irvine Welsh</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/10/1936</t>
+          <t>01/08/2000</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1383,31 +1323,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Power of Now</t>
+          <t>Told You So</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eckhart Tolle</t>
+          <t>Mayci Neeley</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Namaste Publishing</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/01/1997</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
+          <t>07/10/2025</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1416,17 +1353,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop Letting Everything Affect You: How to break free from overthinking, emotional chaos and self-sabotage</t>
+          <t>Renaissance of a Boss: Notes from a Creative Reawakening</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Daniel Chidiac</t>
+          <t>Rick Ross, Neil Martinez-Belkin</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Undercover Publishing House</t>
+          <t>Hanover Square Press</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1436,7 +1373,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1506,28 +1443,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Famesick: A Memoir</t>
+          <t>The Fellowship of the Ring</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lena Dunham</t>
+          <t>J.R.R. Tolkien</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Random House</t>
+          <t>George Allen &amp; Unwin</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
-        </is>
+          <t>29/07/1954</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1536,28 +1476,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yesteryear: A GMA Book Club Pick: A Novel</t>
+          <t>Fourth Wing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Caro Claire Burke</t>
+          <t>Rebecca Yarros</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Knopf Publishing Group</t>
+          <t>Red Tower Books</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
-        </is>
+          <t>02/05/2023</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1566,27 +1509,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Not giving a F*ck Anymore.: Stop People-Pleasing, Set Boundaries, and Start Living on Your Own Terms.</t>
+          <t>Red Rising</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Marieme Seck</t>
+          <t>Pierce Brown</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pck;</t>
+          <t>Del Rey Books</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25/01/2025</t>
+          <t>28/01/2014</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1599,28 +1542,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dear Debbie</t>
+          <t>Throne of Glass</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Poisoned Pen Press</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
-        </is>
+          <t>02/08/2012</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1629,28 +1575,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Strangers: A Memoir of Marriage</t>
+          <t>A Court of Wings and Ruin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Belle Burden</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Dial Press</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
-        </is>
+          <t>02/05/2017</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1659,27 +1608,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Theo of Golden: A Novel</t>
+          <t>Heir of Fire</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Allen Levi</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Allen Levi</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>02/09/2014</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1692,27 +1641,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Remarkably Bright Creatures: A Novel - A Read with Jenna Pick</t>
+          <t>Iron Flame</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Shelby Van Pelt</t>
+          <t>Rebecca Yarros</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ecco</t>
+          <t>Entangled Publishing, LLC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>03/05/2022</t>
+          <t>07/11/2023</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1725,28 +1674,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Night We Met</t>
+          <t>A Game of Thrones: A Song of Ice and Fire: Book One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Abby Jimenez</t>
+          <t>George R. R. Martin</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Forever</t>
+          <t>Bantam Books</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
-        </is>
+          <t>01/08/1996</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1755,28 +1707,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Our Perfect Storm</t>
+          <t>Crown of Midnight</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Carley Fortune</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Penguin Publishing Group</t>
+          <t>Bloomsbury USA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
-        </is>
+          <t>27/08/2013</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1785,676 +1740,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Game On: An Into Darkness Novel</t>
+          <t>The Two Towers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
+          <t>J.R.R. Tolkien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Slowburn</t>
+          <t>George Allen &amp; Unwin</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Lights Out: An Into Darkness Novel</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Navessa Allen</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Zando</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>06/08/2024</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>A Court of Thorns and Roses</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Sarah J. Maas</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Bloomsbury Publishing</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>05/05/2015</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>My Husband's Wife: A Novel</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Alice Feeney</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Flatiron Books</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Macmillan</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>20/01/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>James Clear</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Avery Publishing</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>16/10/2018</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>The Correspondent: A Novel</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Virginia Evans</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Crown Publishing Group</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>29/04/2025</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>The Fellowship of the Ring</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>J.R.R. Tolkien</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>George Allen &amp; Unwin</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>29/07/1954</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>A Court of Mist and Fury</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Sarah J. Maas</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Bloomsbury Publishing</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>03/05/2016</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Stoicism: How to Use Stoic Philosophy to Find Inner Peace and Happiness</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Jason Hemlock</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Bouchard Publishing</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>01/01/2020</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Detached: How to Let Go, Heal, and Become Irresistible</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Sabrina Alexis Bendory</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Thought Catalog Books</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>01/01/2025</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Fourth Wing</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Rebecca Yarros</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Red Tower Books</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>02/05/2023</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>This Story Might Save Your Life: A Novel</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Tiffany Crum</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Flatiron Books</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Macmillan</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>The 48 Laws of Power</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Robert Greene</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Viking Press</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>01/01/1998</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>The Housemaid: An absolutely addictive psychological thriller with a jaw-dropping twist</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Freida McFadden</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Bookouture</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>01/04/2022</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Red Rising</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Pierce Brown</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Del Rey Books</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>28/01/2014</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Throne of Glass</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Sarah J. Maas</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Bloomsbury Publishing</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>02/08/2012</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>I'm Glad My Mom Died</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Jennette McCurdy</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>09/08/2022</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>A Court of Wings and Ruin</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Sarah J. Maas</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Bloomsbury Publishing</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>02/05/2017</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>You with the Sad Eyes: A Memoir</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Christina Applegate</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Little, Brown and Company</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>03/03/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Heir of Fire</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Sarah J. Maas</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>02/09/2014</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Stripped Down: Unfiltered and Unapologetic</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Bunnie Xo</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Dey Street Books</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>17/02/2026</t>
-        </is>
+          <t>11/11/1954</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2523,32 +1833,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lights Out: An Into Darkness Novel</t>
+          <t>Not giving a F*ck Anymore.: Stop People-Pleasing, Set Boundaries, and Start Living on Your Own Terms.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Zando</t>
-        </is>
-      </c>
+          <t>Marieme Seck</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>06/08/2024</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2556,30 +1856,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>This Story Might Save Your Life: A Novel</t>
+          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tiffany Crum</t>
+          <t>James Clear</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Flatiron Books</t>
+          <t>Avery Publishing</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>16/10/2018</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2587,17 +1889,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Caught Up</t>
+          <t>12 Laws of the Universe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
+          <t>Manhardeep Singh</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Quercus Books</t>
+          <t>Independently published</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2607,10 +1909,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>20/10/2021</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2618,17 +1922,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Heated Rivalry</t>
+          <t>Detached: How to Let Go, Heal, and Become Irresistible</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rachel Reid</t>
+          <t>Sabrina Alexis Bendory</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Carina Press</t>
+          <t>Thought Catalog Books</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2638,12 +1942,10 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25/03/2019</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2651,30 +1953,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Into the Blue: Reese's Book Club: A Love Story</t>
+          <t>The Subtle Art of Not Giving a F*ck: A Counterintuitive Approach to Living a Good Life</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Emma Brodie</t>
+          <t>Mark Manson</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ballantine Books</t>
+          <t>HarperOne</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>13/09/2016</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2682,17 +1986,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quicksilver: The Fae &amp; Alchemy Series, Book 1</t>
+          <t>Mastering Conversation Skills Goodbye Awkwardness. Learn to Master the Art of Conversation and Become A Great Communicator, Even if You've Always Been Shy or Hate Small Talk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Callie Hart</t>
+          <t>Helen Stone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Self-published</t>
+          <t>Author's Republic</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2702,7 +2006,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>04/06/2024</t>
+          <t>31/03/2020</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2715,30 +2019,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Brimstone: The Fae &amp; Alchemy Series, Book 2</t>
+          <t>Inner Engineering: A Yogi's Guide to Joy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Callie Hart</t>
+          <t>Sadhguru Vasudev</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Grand Central Publishing</t>
+          <t>Spiegel &amp; Grau</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>20/09/2016</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2746,32 +2052,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>People We Meet on Vacation</t>
+          <t>Stop Letting Everything Affect You: How to break free from overthinking, emotional chaos and self-sabotage</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emily Henry</t>
+          <t>Daniel Chidiac</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Berkley Books</t>
+          <t>Undercover Publishing House</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11/05/2021</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2779,17 +2083,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Long Game</t>
+          <t>The Mountain is You: Transforming Self-Sabotage Into Self-Mastery</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rachel Reid</t>
+          <t>Brianna Wiest</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Carina Press</t>
+          <t>Thought Catalog Books</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2799,7 +2103,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>26/04/2022</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2812,12 +2116,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Broken Country (Reese's Book Club)</t>
+          <t>How To Win Friends And Influence People</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Clare Leslie Hall</t>
+          <t>Dale Carnegie</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2832,7 +2136,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>04/03/2025</t>
+          <t>01/11/1936</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2850,7 +2154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2905,27 +2209,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dear Debbie</t>
+          <t>Yesteryear: A GMA Book Club Pick: A Novel</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
+          <t>Caro Claire Burke</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Poisoned Pen Press</t>
+          <t>Knopf</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -2935,31 +2239,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Housemaid: An absolutely addictive psychological thriller with a jaw-dropping twist</t>
+          <t>Famesick: A Memoir</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Bookouture</t>
+          <t>Lena Dunham</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>01/04/2022</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2968,31 +2259,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Silent Patient</t>
+          <t>Not giving a F*ck Anymore.: Stop People-Pleasing, Set Boundaries, and Start Living on Your Own Terms.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alex Michaelides</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Celadon Books</t>
+          <t>Marieme Seck</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>05/02/2019</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3001,7 +2279,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Housemaid's Secret: A totally gripping psychological thriller with a shocking twist</t>
+          <t>Dear Debbie</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3009,23 +2287,10 @@
           <t>Freida McFadden</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Bookouture</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>11/07/2023</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3034,31 +2299,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Asylum Confessions: Deathbed Confessions of the Criminally Insane</t>
+          <t>Strangers: A Memoir of Marriage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jack Steen</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Deathbed Publishing</t>
+          <t>Belle Burden</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>10/03/2021</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3067,27 +2319,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Mad Wife</t>
+          <t>Theo of Golden: A Novel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Meagan Church</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Sourcebooks Landmark</t>
+          <t>Allen Levi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>30/09/2025</t>
         </is>
       </c>
     </row>
@@ -3097,27 +2339,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Fourth Option: A Novel</t>
+          <t>Remarkably Bright Creatures: A Read with Jenna Pick</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jack Carr, M.P. Woodward</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Atria/Emily Bestler Books</t>
+          <t>Shelby Van Pelt</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -3127,27 +2359,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Intruder</t>
+          <t>Our Perfect Storm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Poisoned Pen Press</t>
+          <t>Carley Fortune</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>07/10/2025</t>
         </is>
       </c>
     </row>
@@ -3157,28 +2379,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mad Mabel: A Novel</t>
+          <t>Lights Out: An Into Darkness Novel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sally Hepworth</t>
+          <t>Navessa Allen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>St. Martin's Press</t>
+          <t>Slowburn</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
-        </is>
+          <t>06/08/2024</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3187,17 +2412,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nobody Knows You're Here: A Psychological Suspense Thriller</t>
+          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bryn Greenwood</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Podium Publishing</t>
+          <t>James Clear</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3205,10 +2425,595 @@
           <t>Independent</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>16/09/2025</t>
-        </is>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A Court of Thorns and Roses</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sarah J. Maas</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Game On: An Into Darkness Novel</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Navessa Allen</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Slowburn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The Night We Met</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Abby Jimenez</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Forever</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The Fellowship of the Ring</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>J.R.R. Tolkien</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>George Allen &amp; Unwin</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>29/07/1954</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stoicism: How to Use Stoic Philosophy to Find Inner Peace and Happiness</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Jason Hemlock</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bouchard Publishing</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>21/04/2020</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>My Husband's Wife: A Novel</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Alice Feeney</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Flatiron Books</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Macmillan</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>20/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The Correspondent: A Novel</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Virginia Evans</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Crown Publishing Group</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>29/04/2025</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fourth Wing</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Rebecca Yarros</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Red Tower Books</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>02/05/2023</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>A Court of Mist and Fury</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sarah J. Maas</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>The Things We Never Say: A Novel</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Elizabeth Strout</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>The Action Bible: God's Redemptive Story</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Doug Mauss</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>David C Cook</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>01/09/2010</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A Little More Social: How Small Choices Create Unexpected Happiness, Health, and Connection</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Nicholas Epley</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>The Deal – Reine Verhandlungssache: Off-Campus 1 \| Roman \| BookTok-Liebling \| Prickelnde College-Romance für New Adults</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Elle Kennedy</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bloom Books</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>24/02/2015</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Red Rising</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Pierce Brown</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Del Rey Books</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>28/01/2014</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Throne of Glass</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sarah J. Maas</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bloomsbury Publishing</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>02/08/2012</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The 48 Laws of Power</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Robert Greene</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Viking Press</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>01/01/1998</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>This Is Me: A Reckoning</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Hayden Panettiere</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Grand Central Publishing</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Hachette</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>This Story Might Save Your Life: A Novel</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tiffany Crum</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Flatiron Books</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Macmillan</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>The Fourth Option: A Novel</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Jack Carr, M.P. Woodward</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Atria/Emily Bestler Books</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>A Court of Wings and Ruin</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sarah J. Maas</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bloomsbury Publishing</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>02/05/2017</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3277,17 +3082,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Lightning Thief: Percy Jackson and the Olympians: Book 1</t>
+          <t>Lights Out: An Into Darkness Novel</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rick Riordan</t>
+          <t>Navessa Allen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Miramax Books</t>
+          <t>Slowburn</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3297,7 +3102,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28/06/2005</t>
+          <t>06/08/2024</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -3310,27 +3115,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Frog and Toad Audio Collection: A Box Set of 3 Books From the Classic Animal Friendship and Adventure Series for Kids \[ages 4-8\] – A Heartwarming Caldecott and Newbery Honor Collection</t>
+          <t>The Deal – Reine Verhandlungssache: Off-Campus 1 \| Roman \| BookTok-Liebling \| Prickelnde College-Romance für New Adults</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Arnold Lobel</t>
+          <t>Elle Kennedy</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Bloom Books</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>02/11/2004</t>
+          <t>24/02/2015</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -3343,31 +3148,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>If You Laugh, I'm Starting This Book Over</t>
+          <t>This Story Might Save Your Life: A Novel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chris Harris</t>
+          <t>Tiffany Crum</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Little, Brown Books for Young Readers</t>
+          <t>Flatiron Books</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27/09/2022</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
+          <t>10/03/2026</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3376,31 +3178,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Warriors #1: Into the Wild: A Stunning Deluxe Edition of the Epic Beginning of the Warriors Cats Series</t>
+          <t>Fever Dream: Small-town, dating show, rival's little sister romance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Erin Hunter</t>
+          <t>Elsie Silver</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Atria Books</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21/01/2003</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+          <t>19/05/2026</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3409,27 +3208,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KPop Demon Hunters: The Official Deluxe Junior Novelization: The Official Retelling</t>
+          <t>Caught Up</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jessica Yoon</t>
+          <t>Navessa Allen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Random House Children's Books</t>
+          <t>Zando – Slowburn</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>10/06/2025</t>
         </is>
       </c>
     </row>
@@ -3439,31 +3238,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Beginner's Bible: Timeless Children's Stories</t>
+          <t>Into the Blue: Reese's Book Club: A Love Story</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Beginner's Bible</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Mission City Press, Inc.</t>
+          <t>Emma Brodie</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>01/01/1989</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3472,17 +3258,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Lion, the Witch and the Wardrobe: Classic Fantasy Tale for Kids</t>
+          <t>Heated Rivalry</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C. S. Lewis</t>
+          <t>Rachel Reid</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Geoffrey Bles</t>
+          <t>Carina Press</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3492,7 +3278,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16/10/1950</t>
+          <t>25/03/2019</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3505,31 +3291,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Disney\*Pixar Storybook Collection</t>
+          <t>Quicksilver: The Fae &amp; Alchemy Series, Book 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Disney Press</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Disney Press</t>
+          <t>Callie Hart</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>01/01/2006</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3538,31 +3311,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Boxcar Children Collection Volume 1: The Boxcar Children, Surprise Island, Yellow House Mystery</t>
+          <t>Brimstone: The Fae &amp; Alchemy Series, Book 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gertrude Chandler Warner</t>
+          <t>Callie Hart</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rand McNally</t>
+          <t>Grand Central Publishing</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/01/1924</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
+          <t>18/11/2025</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -3571,28 +3341,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Junie B. Jones Audio Collection: Books 1-8: The Stupid Smelly Bus; A Little Monkey Business; Her Big Fat Mouth; Some Sneaky Peeky Spying; The Yucky Blucky Fruitcake; That Meanie Jim's Birthday and more</t>
+          <t>Every Summer After</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Barbara Park</t>
+          <t>Carley Fortune</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Listening Library</t>
+          <t>Berkley Books</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
-        </is>
+          <t>10/05/2022</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3661,31 +3434,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Anxious Generation: How the Great Rewiring of Childhood Is Causing an Epidemic of Mental Illness</t>
+          <t>Dear Debbie</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jonathan Haidt</t>
+          <t>Freida McFadden</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Penguin Press</t>
+          <t>Poisoned Pen Press</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26/03/2024</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
+          <t>27/01/2026</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -3694,31 +3464,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adult Children of Emotionally Immature Parents: How to Heal from Distant, Rejecting, or Self-Involved Parents</t>
+          <t>The Fourth Option: A Novel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lindsay C. Gibson, PsyD</t>
+          <t>Jack Carr, M.P. Woodward</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>New Harbinger Publications</t>
+          <t>Atria/Emily Bestler Books</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01/06/2015</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
+          <t>12/05/2026</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -3727,27 +3494,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hunt, Gather, Parent: What Ancient Cultures Can Teach Us About the Lost Art of Raising Happy, Helpful Little Humans</t>
+          <t>The Housemaid: An absolutely addictive psychological thriller with a jaw-dropping twist</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Michaeleen Doucleff</t>
+          <t>Freida McFadden</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Avid Reader Press / Simon &amp; Schuster</t>
+          <t>Bookouture</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>02/03/2021</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -3760,27 +3527,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Good Inside: A Guide to Becoming the Parent You Want to Be - A Practical Guide to Resilient Parenting Prioritizing Connection Over Correction</t>
+          <t>The Silent Patient</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Becky Kennedy</t>
+          <t>Alex Michaelides</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Harper Wave</t>
+          <t>Celadon Books</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01/09/2022</t>
+          <t>05/02/2019</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -3793,27 +3560,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Tired Dad.: 100 Reflections on Showing Up for What Matters Most</t>
+          <t>The Asylum Confessions: Deathbed Confessions of the Criminally Insane</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jon Gustin</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Convergent Books</t>
+          <t>Jack Steen</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -3823,17 +3580,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Men with Adult ADHD: How to Raise Emotionally Intelligent Men and Improve Relationships</t>
+          <t>The Mad Wife</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Garth Zeus</t>
+          <t>Meagan Church</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Garth Zeus</t>
+          <t>Sourcebooks Landmark</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3843,11 +3600,8 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
+          <t>30/09/2025</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -3856,31 +3610,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Expecting Better: Why the Conventional Pregnancy Wisdom Is Wrong--and What You Really Need to Know</t>
+          <t>Nobody Knows You're Here: A Psychological Suspense Thriller</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emily Oster</t>
+          <t>Bryn Greenwood</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Penguin Books</t>
+          <t>Podium Publishing</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/06/2014</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
+          <t>16/09/2025</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -3889,31 +3640,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cribsheet: A Data-Driven Guide to Better, More Relaxed Parenting, from Birth to Preschool</t>
+          <t>Mad Mabel: A Novel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emily Oster</t>
+          <t>Sally Hepworth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Penguin Books</t>
+          <t>St. Martin's Press</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21/04/2020</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
+          <t>21/04/2026</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -3922,31 +3670,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Seven Principles for Making Marriage Work: A Practical Guide from the Country’s Foremost Relationship Expert, Revised and Updated</t>
+          <t>The Housemaid's Secret: A totally gripping psychological thriller with a shocking twist</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>John M. Gottman, PhD, Nan Silver</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Harmony</t>
+          <t>Freida McFadden</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>01/05/1999</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -3955,31 +3690,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Danish Secret to Happy Kids: How the Viking Way of Raising Children Makes Them Happier, Healthier, and More Independent</t>
+          <t>Judge Stone: A Novel</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Helen Russell</t>
+          <t>James Patterson, Viola Davis</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sourcebooks</t>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>09/07/2024</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
+          <t>09/03/2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4048,27 +3780,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sapiens: A Brief History of Humankind</t>
+          <t>If You Laugh, I'm Starting This Book Over</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yuval Noah Harari</t>
+          <t>Chris Harris</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Dvir Publishing House Ltd.</t>
+          <t>Little, Brown Books for Young Readers</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01/01/2011</t>
+          <t>27/09/2022</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -4081,17 +3813,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Traversal</t>
+          <t>The Lightning Thief: Percy Jackson and the Olympians: Book 1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Maria Popova</t>
+          <t>Rick Riordan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Farrar, Straus and Giroux</t>
+          <t>Miramax Books</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4101,8 +3833,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
-        </is>
+          <t>28/06/2005</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4111,17 +3846,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A People's History of the United States</t>
+          <t>Frog and Toad Audio Collection: A Box Set of 3 Books From the Classic Animal Friendship and Adventure Series for Kids [ages 4-8] – A Heartwarming Caldecott and Newbery Honor Collection</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Howard Zinn</t>
+          <t>Arnold Lobel</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Harper &amp; Row</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4131,7 +3866,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/01/1980</t>
+          <t>02/11/2004</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -4144,28 +3879,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1929: Inside the Greatest Crash in Wall Street History--and How It Shattered a Nation</t>
+          <t>Warriors #1: Into the Wild: A Stunning Deluxe Edition of the Epic Beginning of the Warriors Cats Series</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Andrew Ross Sorkin</t>
+          <t>Erin Hunter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Viking Press</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
-        </is>
+          <t>21/01/2003</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -4174,31 +3912,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mythos</t>
+          <t>KPop Demon Hunters: The Official Deluxe Junior Novelization: The Official Retelling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Stephen Fry</t>
+          <t>Jessica Yoon</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Michael Joseph</t>
+          <t>Random House Books for Young Readers</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+          <t>31/03/2026</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4207,17 +3942,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>How to Hide an Empire: A History of the Greater United States</t>
+          <t>Miles the Brave</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Daniel Immerwahr</t>
+          <t>Storybutton, Mike Marshall, Steven Forbis</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Farrar, Straus and Giroux</t>
+          <t>Storybutton</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4227,7 +3962,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>12/10/2024</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -4240,27 +3975,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Third Reich: A History of Nazi Germany</t>
+          <t>The Boxcar Children Collection Volume 1: The Boxcar Children, Surprise Island, Yellow House Mystery</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thomas Childers</t>
+          <t>Gertrude Chandler Warner</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Rand McNally</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/1924</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4273,17 +4008,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>We the People: A History of the U.S. Constitution</t>
+          <t>The Beginner's Bible: Timeless Children's Stories</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jill Lepore</t>
+          <t>The Beginner's Bible</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Liveright Publishing Corporation</t>
+          <t>Mission City Press, Inc.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4293,8 +4028,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
-        </is>
+          <t>01/01/1989</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -4303,17 +4041,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Very Secret Sex Lives of Medieval Women: An Inside Look at Women &amp; Sex in Medieval Times</t>
+          <t>The Lion, the Witch and the Wardrobe: Classic Fantasy Tale for Kids</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rosalie Gilbert</t>
+          <t>C. S. Lewis</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mango Publishing</t>
+          <t>Geoffrey Bles</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4323,7 +4061,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>27/10/2020</t>
+          <t>16/10/1950</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4336,27 +4074,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Empire of the Summer Moon: Quanah Parker and the Rise and Fall of the Comanches, the Most Powerful Indian Tribe in American History</t>
+          <t>Pete the Cat and the Perfect Pizza Party</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>S. C. Gwynne</t>
+          <t>James Dean, Kimberly Dean</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Scribner</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25/03/2010</t>
+          <t>03/09/2019</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4429,27 +4167,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Action Bible: God's Redemptive Story</t>
+          <t>The Anxious Generation: How the Great Rewiring of Childhood Is Causing an Epidemic of Mental Illness</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Doug Mauss</t>
+          <t>Jonathan Haidt</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>David C Cook</t>
+          <t>Penguin Press</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01/09/2010</t>
+          <t>26/03/2024</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -4462,31 +4200,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>How to Hold a Cockroach: A book for those who are free and don't know it</t>
+          <t>Adult Children of Emotionally Immature Parents: How to Heal from Distant, Rejecting, or Self-Involved Parents</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Matthew Maxwell</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Hearthstone</t>
+          <t>Lindsay C. Gibson, PsyD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>20/04/2020</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4495,27 +4220,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The King James Bible</t>
+          <t>Hunt, Gather, Parent: What Ancient Cultures Can Teach Us About the Lost Art of Raising Happy, Helpful Little Humans</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uncredited</t>
+          <t>Michaeleen Doucleff</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Robert Barker</t>
+          <t>Avid Reader Press / Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/01/1611</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -4528,31 +4253,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Alchemist: A Modern Classic Fable of Spiritual Healing, Self-Discovery, and the Power of Dreams in a Visually Stunning Graphic Novel—Get Lost in the Pages of This Captivating Summer Read</t>
+          <t>Good Inside: A Practical Guide to Resilient Parenting Prioritizing Connection Over Correction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paulo Coelho</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HarperOne</t>
+          <t>Becky Kennedy</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>01/11/2010</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4561,31 +4273,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NIV Listener's Audio Bible: Complete Bible: Vocal Performance by Max McLean</t>
+          <t>The Tired Dad.: 100 Reflections on Showing Up for What Matters Most</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Zondervan</t>
+          <t>Jon Gustin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Zondervan</t>
+          <t>Convergent Books</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>03/11/2015</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+          <t>05/05/2026</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4594,27 +4303,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Become What You Are</t>
+          <t>Expecting Better: Why the Conventional Pregnancy Wisdom Is Wrong--and What You Really Need to Know</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alan Watts</t>
+          <t>Emily Oster</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Shambhala</t>
+          <t>Penguin Press</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01/01/1995</t>
+          <t>20/08/2013</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -4627,27 +4336,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mere Christianity</t>
+          <t>The Seven Principles for Making Marriage Work: A Practical Guide from the Country’s Foremost Relationship Expert, Revised and Updated</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C. S. Lewis</t>
+          <t>John M. Gottman, PhD, Nan Silver</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Geoffrey Bles</t>
+          <t>Harmony</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07/07/1952</t>
+          <t>01/01/1999</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4660,27 +4369,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Four Agreements: A Practical Guide to Personal Freedom</t>
+          <t>Cribsheet: A Data-Driven Guide to Better, More Relaxed Parenting, from Birth to Preschool</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Don Miguel Ruiz, Janet Mills</t>
+          <t>Emily Oster</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Amber-Allen Publishing</t>
+          <t>Penguin Books</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07/11/1997</t>
+          <t>21/04/2020</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4693,17 +4402,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Book of Enoch: The Complete Audiobook</t>
+          <t>Men with Adult ADHD: How to Raise Emotionally Intelligent Men and Improve Relationships</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Christopher Glyn</t>
+          <t>Garth Zeus</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SAGA Egmont</t>
+          <t>Garth Zeus</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4713,7 +4422,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>08/07/2019</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4726,28 +4435,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stand Firm and Act Like Men: Becoming the Man You Were Created to Be Instead of Who the World Says You Are</t>
+          <t>Oh Crap! Potty Training: Everything Modern Parents Need to Know to Do It Once and Do It Right</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Joby Martin, Charles Martin</t>
+          <t>Jamie Glowacki</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Faithwords</t>
+          <t>Lovebugs</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
-        </is>
+          <t>02/02/2015</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4816,27 +4528,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A Court of Thorns and Roses</t>
+          <t>Sapiens: A Brief History of Humankind</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>Yuval Noah Harari</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bloomsbury Publishing</t>
+          <t>Dvir Publishing House Ltd.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>05/05/2015</t>
+          <t>01/01/2011</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -4849,31 +4561,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A Court of Mist and Fury</t>
+          <t>Traversal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>Maria Popova</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bloomsbury Publishing</t>
+          <t>Farrar, Straus and Giroux</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>03/05/2016</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
+          <t>17/02/2026</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -4882,31 +4591,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lord of the Flies</t>
+          <t>Mythos</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>William Golding</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Faber and Faber</t>
+          <t>Stephen Fry</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>17/09/1954</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -4915,27 +4611,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Twilight</t>
+          <t>A People's History of the United States</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Stephenie Meyer</t>
+          <t>Howard Zinn</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Little, Brown and Company</t>
+          <t>Harper &amp; Row</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>05/10/2005</t>
+          <t>01/01/1980</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -4948,31 +4644,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Better Than the Movies</t>
+          <t>1929: Inside the Greatest Crash in Wall Street History--and How It Shattered a Nation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lynn Painter</t>
+          <t>Andrew Ross Sorkin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Viking Press</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>04/05/2021</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+          <t>14/10/2025</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4981,31 +4674,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Midnight Sun</t>
+          <t>The Very Secret Sex Lives of Medieval Women: An Inside Look at Women &amp; Sex in Medieval Times</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Stephenie Meyer</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Little, Brown and Company</t>
+          <t>Rosalie Gilbert</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>04/08/2020</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5014,27 +4694,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Powerless</t>
+          <t>How to Hide an Empire: A History of the Greater United States</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lauren Roberts</t>
+          <t>Daniel Immerwahr</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Farrar, Straus and Giroux</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07/11/2023</t>
+          <t>19/02/2019</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -5047,27 +4727,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Summer I Turned Pretty</t>
+          <t>Codename Nemo: The Hunt for a Nazi U-Boat and the Elusive Enigma Machine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jenny Han</t>
+          <t>Charles Lachman</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster Books for Young Readers</t>
+          <t>Diversion Books</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>05/05/2009</t>
+          <t>04/06/2024</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -5080,27 +4760,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eragon: Inheritance, Book I</t>
+          <t>The Third Reich: A History of Nazi Germany</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Christopher Paolini</t>
+          <t>Thomas Childers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paolini International, LLC</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/01/2002</t>
+          <t>01/04/2017</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -5113,31 +4793,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Cruel Prince</t>
+          <t>On Witness and Respair: Essays</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Holly Black</t>
+          <t>Jesmyn Ward</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Little, Brown Books for Young Readers</t>
+          <t>Scribner</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>02/01/2018</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
+          <t>19/05/2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5206,17 +4883,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Psychology of Money: Timeless lessons on wealth, greed, and happiness</t>
+          <t>The Action Bible: God's Redemptive Story</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Morgan Housel</t>
+          <t>Doug Mauss</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Harriman House</t>
+          <t>David C Cook</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5226,7 +4903,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/09/2010</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -5239,28 +4916,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Drownproof: Eight Life Lessons to Keep Your Head Above Water</t>
+          <t>How to Hold a Cockroach: A book for those who are free and don't know it</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Andy Stumpf</t>
+          <t>Matthew Maxwell</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>St. Martin's Press</t>
+          <t>Hearthstone</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
-        </is>
+          <t>20/04/2020</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -5269,17 +4949,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Never Split the Difference: Negotiating As If Your Life Depended On It - Unlock Your Persuasion Potential in Professional and Personal Life</t>
+          <t>The King James Bible</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chris Voss, Tahl Raz</t>
+          <t>Uncredited</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HarperBusiness</t>
+          <t>Robert Barker</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5289,7 +4969,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17/05/2016</t>
+          <t>01/01/1611</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -5302,27 +4982,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Extreme Ownership: How U.S. Navy SEALs Lead and Win</t>
+          <t>The Alchemist: A Modern Classic Fable of Spiritual Healing, Self-Discovery, and the Power of Dreams in a Visually Stunning Graphic Novel—Get Lost in the Pages of This Captivating Summer Read</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jocko Willink, Leif Babin</t>
+          <t>Paulo Coelho</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>St. Martin's Press</t>
+          <t>HarperOne</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>01/11/2010</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -5335,27 +5015,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unreasonable Hospitality: The Remarkable Power of Giving People More Than They Expect</t>
+          <t>NIV Listener's Audio Bible: Complete Bible: Vocal Performance by Max McLean</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Will Guidara</t>
+          <t>Zondervan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Optimism Press</t>
+          <t>Zondervan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25/10/2022</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -5368,18 +5048,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The 7 Habits of Highly Effective People: 30th Anniversary Edition</t>
+          <t>Become What You Are</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Stephen R. Covey, Sean Covey</t>
+          <t>Alan Watts</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Shambhala</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>01/01/1995</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -5388,17 +5081,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>How to Talk to Anyone and Be More Charismatic: Improve Communication &amp; People Skills, Master Small Talk, Build Confidence &amp; Influence, Overcome Social Anxiety, and Make Friends in Any Conversation</t>
+          <t>Mere Christianity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathan Soren</t>
+          <t>C. S. Lewis</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Independently Published</t>
+          <t>Geoffrey Bles</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5408,8 +5101,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>03/07/2025</t>
-        </is>
+          <t>07/07/1952</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -5418,17 +5114,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Think and Grow Rich! The Original Version, Restored and Revised</t>
+          <t>The Four Agreements: A Practical Guide to Personal Freedom</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Napoleon Hill, Ross Cornwell</t>
+          <t>Don Miguel Ruiz, Janet Mills</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mindpower Press</t>
+          <t>Amber-Allen Publishing</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5438,7 +5134,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>07/11/1997</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -5451,31 +5147,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Think and Grow Rich</t>
+          <t>Stand Firm and Act Like Men: Becoming the Man You Were Created to Be Instead of Who the World Says You Are</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Napoleon Hill</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>The Ralston Society</t>
+          <t>Joby Martin, Charles Martin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>01/03/1937</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -5484,17 +5167,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Think Faster, Talk Smarter: How to Speak Successfully When You're Put on the Spot</t>
+          <t>The Book of Enoch: The Complete Audiobook</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Matt Abrahams</t>
+          <t>Christopher Glyn</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Simon Element/Simon Acumen</t>
+          <t>SAGA Egmont</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5504,7 +5187,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>08/07/2019</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -5577,28 +5260,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Strangers: A Memoir of Marriage</t>
+          <t>A Court of Thorns and Roses</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Belle Burden</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Dial Press</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
-        </is>
+          <t>01/05/2015</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -5607,27 +5293,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I'm Glad My Mom Died</t>
+          <t>A Court of Mist and Fury</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jennette McCurdy</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>09/08/2022</t>
+          <t>03/05/2016</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -5640,12 +5326,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>You with the Sad Eyes: A Memoir</t>
+          <t>Twilight</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Christina Applegate</t>
+          <t>Stephenie Meyer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5660,8 +5346,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
-        </is>
+          <t>05/10/2005</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -5670,17 +5359,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stripped Down: Unfiltered and Unapologetic</t>
+          <t>Lord of the Flies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bunnie Xo</t>
+          <t>William Golding</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Dey Street Books</t>
+          <t>Faber and Faber</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5690,8 +5379,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
-        </is>
+          <t>17/09/1954</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -5700,28 +5392,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Smile, or You're Doing it Wrong: A Journey from Rock Bottom to Redemption</t>
+          <t>Midnight Sun</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Andy Glaze</t>
+          <t>Stephenie Meyer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fedd Books</t>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
-        </is>
+          <t>04/08/2020</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -5730,17 +5425,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Start With Yourself: A New Vision for Work &amp; Life</t>
+          <t>The Summer I Turned Pretty</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Emma Grede</t>
+          <t>Jenny Han</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Avid Reader Press/Simon &amp; Schuster</t>
+          <t>Simon &amp; Schuster Books for Young Readers</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5750,8 +5445,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
-        </is>
+          <t>05/05/2009</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -5760,12 +5458,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Told You So</t>
+          <t>Better Than the Movies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mayci Neeley</t>
+          <t>Lynn Painter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5780,8 +5478,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
-        </is>
+          <t>04/05/2021</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -5790,27 +5491,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kitchen Confidential: Adventures in the Culinary Underbelly</t>
+          <t>Powerless</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Anthony Bourdain, Irvine Welsh</t>
+          <t>Lauren Roberts</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/01/2000</t>
+          <t>07/11/2023</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -5823,17 +5524,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rookie: My Public, Private, and Secret Life</t>
+          <t>Eragon: Inheritance, Book I</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Joshua Bassett</t>
+          <t>Christopher Paolini</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Authors Equity</t>
+          <t>Paolini International LLC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5843,8 +5544,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
-        </is>
+          <t>01/11/2001</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -5853,17 +5557,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Renaissance of a Boss: Notes from a Creative Reawakening</t>
+          <t>Ten Days in a Mad-House</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rick Ross, Neil Martinez-Belkin</t>
+          <t>Nellie Bly</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hanover Square Press</t>
+          <t>Norman Munro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5873,8 +5577,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
-        </is>
+          <t>01/01/1887</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/audiobooks.xlsx
+++ b/audiobooks.xlsx
@@ -737,9 +737,19 @@
           <t>Nicholas Epley</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Knopf</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -757,10 +767,23 @@
           <t>Morgan Housel</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Harriman House</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>01/09/2020</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -840,23 +863,10 @@
           <t>Jocko Willink, Leif Babin</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>St. Martin's Press</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Macmillan</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>01/10/2015</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -908,7 +918,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Free Press</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1137,7 +1147,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -1248,9 +1258,19 @@
           <t>Emma Grede</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Avid Reader Press/Simon &amp; Schuster</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1320,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1486,7 +1506,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Red Tower Books</t>
+          <t>Red Tower Books (Entangled Publishing)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1628,7 +1648,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>02/09/2014</t>
+          <t>01/09/2014</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1651,7 +1671,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Entangled Publishing, LLC</t>
+          <t>Red Tower Books (Entangled Publishing)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1684,7 +1704,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bantam Books</t>
+          <t>Bantam Spectra</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1841,14 +1861,24 @@
           <t>Marieme Seck</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pck;</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>25/01/2025</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2072,7 +2102,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -2103,7 +2133,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>28/05/2020</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2247,9 +2277,19 @@
           <t>Lena Dunham</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Random House</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -2267,10 +2307,23 @@
           <t>Marieme Seck</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pck;</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>25/01/2025</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2287,9 +2340,19 @@
           <t>Freida McFadden</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Poisoned Pen Press</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>27/01/2026</t>
         </is>
       </c>
     </row>
@@ -2307,9 +2370,19 @@
           <t>Belle Burden</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Dial Press</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>13/01/2026</t>
         </is>
       </c>
     </row>
@@ -2327,9 +2400,19 @@
           <t>Allen Levi</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Atria Books</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
         </is>
       </c>
     </row>
@@ -2347,10 +2430,23 @@
           <t>Shelby Van Pelt</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ecco</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>03/05/2022</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -2367,9 +2463,19 @@
           <t>Carley Fortune</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Berkley Books</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -2420,10 +2526,23 @@
           <t>James Clear</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Avery Publishing</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>16/10/2018</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -2440,10 +2559,23 @@
           <t>Sarah J. Maas</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bloomsbury Publishing</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>05/05/2015</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2565,7 +2697,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21/04/2020</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2651,7 +2783,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Red Tower Books</t>
+          <t>Red Tower Books (Entangled Publishing)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2682,10 +2814,23 @@
           <t>Sarah J. Maas</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bloomsbury Publishing</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>03/05/2016</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2702,9 +2847,19 @@
           <t>Elizabeth Strout</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Random House</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2889,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>01/09/2010</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2755,9 +2910,19 @@
           <t>Nicholas Epley</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Knopf</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2942,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Bloom Books</t>
+          <t>Elle Kennedy Inc.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2919,7 +3084,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3290,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bloom Books</t>
+          <t>Elle Kennedy Inc.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3218,7 +3383,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Zando – Slowburn</t>
+          <t>Slowburn</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3246,9 +3411,19 @@
           <t>Emma Brodie</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ballantine Books</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -3299,10 +3474,23 @@
           <t>Callie Hart</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Independently Published</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>04/06/2024</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3321,12 +3509,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Grand Central Publishing</t>
+          <t>Forever</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3514,7 +3702,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>26/04/2022</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -3568,10 +3756,23 @@
           <t>Jack Steen</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Deathbed Publishing</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10/03/2021</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3678,10 +3879,23 @@
           <t>Freida McFadden</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bookouture</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Hachette</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>11/07/2023</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3985,7 +4199,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Rand McNally</t>
+          <t>Rand McNally &amp; Company</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4208,10 +4422,23 @@
           <t>Lindsay C. Gibson, PsyD</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New Harbinger Publications</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>01/06/2015</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4240,7 +4467,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>01/03/2021</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -4261,10 +4488,23 @@
           <t>Becky Kennedy</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Harper Wave</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>13/09/2022</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -4313,7 +4553,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Penguin Press</t>
+          <t>Penguin Books</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4379,7 +4619,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Penguin Books</t>
+          <t>Penguin Press</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4389,7 +4629,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21/04/2020</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4422,7 +4662,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>28/01/2023</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4445,17 +4685,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lovebugs</t>
+          <t>Gallery Books</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>02/02/2015</t>
+          <t>16/06/2015</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4599,10 +4839,23 @@
           <t>Stephen Fry</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Michael Joseph</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>01/01/2017</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -4682,10 +4935,23 @@
           <t>Rosalie Gilbert</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mango Publishing</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>27/10/2020</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -4780,7 +5046,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4801,19 +5067,9 @@
           <t>Jesmyn Ward</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Scribner</t>
-        </is>
-      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -4903,7 +5159,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01/09/2010</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -4936,7 +5192,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20/04/2020</t>
+          <t>10/04/2020</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -5035,7 +5291,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>03/11/2015</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -5134,7 +5390,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07/11/1997</t>
+          <t>01/11/1997</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -5155,9 +5411,19 @@
           <t>Joby Martin, Charles Martin</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Faithwords</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5546,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01/05/2015</t>
+          <t>05/05/2015</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -5400,23 +5666,10 @@
           <t>Stephenie Meyer</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Little, Brown and Company</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>04/08/2020</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5544,7 +5797,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/11/2001</t>
+          <t>01/01/2002</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/audiobooks.xlsx
+++ b/audiobooks.xlsx
@@ -729,27 +729,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A Little More Social: How Small Choices Create Unexpected Happiness, Health, and Connection</t>
+          <t>The Psychology of Money: Timeless lessons on wealth, greed, and happiness</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nicholas Epley</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Knopf</t>
+          <t>Morgan Housel</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -759,31 +749,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Psychology of Money: Timeless lessons on wealth, greed, and happiness</t>
+          <t>Disrupt Everything—and Win: Take Control of Your Future</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Morgan Housel</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Harriman House</t>
+          <t>James Patterson, Patrick Leddin PhD</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>01/09/2020</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -800,23 +777,10 @@
           <t>Chris Voss, Tahl Raz</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Harper Business</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>17/05/2016</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -825,27 +789,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>How to Talk to Anyone and Be More Charismatic: Improve Communication &amp; People Skills, Master Small Talk, Build Confidence &amp; Influence, Overcome Social Anxiety, and Make Friends in Any Conversation</t>
+          <t>Unreasonable Hospitality: The Remarkable Power of Giving People More Than They Expect</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nathan Soren</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Independently Published</t>
+          <t>Will Guidara</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>03/07/2025</t>
         </is>
       </c>
     </row>
@@ -875,31 +829,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unreasonable Hospitality: The Remarkable Power of Giving People More Than They Expect</t>
+          <t>How to Talk to Anyone and Be More Charismatic: Improve Communication &amp; People Skills, Master Small Talk, Build Confidence &amp; Influence, Overcome Social Anxiety, and Make Friends in Any Conversation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Will Guidara</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Optimism Press</t>
+          <t>Nathan Soren</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>25/10/2022</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -908,31 +849,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The 7 Habits of Highly Effective People: 30th Anniversary Edition</t>
+          <t>A Little More Social: How Small Choices Create Unexpected Happiness, Health, and Connection</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stephen R. Covey, Sean Covey</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Nicholas Epley</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>01/01/1989</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -941,31 +869,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Think and Grow Rich</t>
+          <t>The 7 Habits of Highly Effective People: 30th Anniversary Edition</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Napoleon Hill</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>The Ralston Society</t>
+          <t>Stephen R. Covey, Sean Covey</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>01/01/1937</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -982,23 +897,10 @@
           <t>Napoleon Hill, Ross Cornwell</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>The Ralston Society</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>01/03/1937</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1007,27 +909,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Future Rich Person: The New Rules for Building Wealth (Even if You're Stuck, Broke, and that Billionaire Won't Text You Back...)</t>
+          <t>Think and Grow Rich</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Haley Sacks</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Ballantine Books</t>
+          <t>Napoleon Hill</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -1105,19 +997,9 @@
           <t>Belle Burden</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Dial Press</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>13/01/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -1135,19 +1017,9 @@
           <t>Hayden Panettiere</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Grand Central Publishing</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -1165,23 +1037,10 @@
           <t>Jennette McCurdy</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>09/08/2022</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1198,19 +1057,9 @@
           <t>Bunnie Xo</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Dey Street Books</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>17/02/2026</t>
         </is>
       </c>
     </row>
@@ -1228,19 +1077,9 @@
           <t>Christina Applegate</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Little, Brown and Company</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>03/03/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -1250,27 +1089,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Start With Yourself: A New Vision for Work &amp; Life</t>
+          <t>Bad Bunny: ‘What’s the Point in Being Here? To Show the World Who I Am’</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Emma Grede</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Avid Reader Press/Simon &amp; Schuster</t>
+          <t>Julyssa Lopez, Rolling Stone</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -1280,27 +1109,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Smile, or You're Doing it Wrong: A Journey from Rock Bottom to Redemption</t>
+          <t>Phases: A Memoir</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Andy Glaze</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Fedd Books</t>
+          <t>Brandy</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -1310,31 +1129,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kitchen Confidential: Adventures in the Culinary Underbelly</t>
+          <t>Start With Yourself: A New Vision for Work &amp; Life</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Anthony Bourdain, Irvine Welsh</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Bloomsbury Publishing</t>
+          <t>Emma Grede</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>01/08/2000</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1343,27 +1149,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Told You So</t>
+          <t>(Un)educated: My Life as a Teacher, and Why You Should Never Become One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mayci Neeley</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Francis Foster</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>07/10/2025</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -1373,27 +1169,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Renaissance of a Boss: Notes from a Creative Reawakening</t>
+          <t>Kitchen Confidential: Adventures in the Culinary Underbelly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rick Ross, Neil Martinez-Belkin</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Hanover Square Press</t>
+          <t>Anthony Bourdain, Irvine Welsh</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -1471,23 +1257,10 @@
           <t>J.R.R. Tolkien</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>George Allen &amp; Unwin</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>29/07/1954</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1504,23 +1277,10 @@
           <t>Rebecca Yarros</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Red Tower Books (Entangled Publishing)</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>02/05/2023</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1537,23 +1297,10 @@
           <t>Pierce Brown</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Del Rey Books</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>28/01/2014</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1570,23 +1317,10 @@
           <t>Sarah J. Maas</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Bloomsbury Publishing</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>02/08/2012</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1603,23 +1337,10 @@
           <t>Sarah J. Maas</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Bloomsbury Publishing</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>02/05/2017</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1636,23 +1357,10 @@
           <t>Sarah J. Maas</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Bloomsbury Publishing</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>01/09/2014</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1669,23 +1377,10 @@
           <t>Rebecca Yarros</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Red Tower Books (Entangled Publishing)</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>07/11/2023</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1694,31 +1389,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A Game of Thrones: A Song of Ice and Fire: Book One</t>
+          <t>Crown of Midnight</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>George R. R. Martin</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Bantam Spectra</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>01/08/1996</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1727,31 +1409,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Crown of Midnight</t>
+          <t>The Two Towers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Bloomsbury USA</t>
+          <t>J.R.R. Tolkien</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>27/08/2013</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1760,31 +1429,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Two Towers</t>
+          <t>A Game of Thrones: A Song of Ice and Fire: Book One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>J.R.R. Tolkien</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>George Allen &amp; Unwin</t>
+          <t>George R. R. Martin</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>11/11/1954</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1861,24 +1517,14 @@
           <t>Marieme Seck</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Pck;</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>25/01/2025</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1894,24 +1540,14 @@
           <t>James Clear</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Avery Publishing</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>16/10/2018</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1919,32 +1555,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12 Laws of the Universe</t>
+          <t>Detached: How to Let Go, Heal, and Become Irresistible</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Manhardeep Singh</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Independently published</t>
-        </is>
-      </c>
+          <t>Sabrina Alexis Bendory</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>20/10/2021</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1952,29 +1578,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Detached: How to Let Go, Heal, and Become Irresistible</t>
+          <t>Mastering Conversation Skills Goodbye Awkwardness. Learn to Master the Art of Conversation and Become A Great Communicator, Even if You've Always Been Shy or Hate Small Talk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sabrina Alexis Bendory</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Thought Catalog Books</t>
-        </is>
-      </c>
+          <t>Helen Stone</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>09/09/2025</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1983,32 +1601,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Subtle Art of Not Giving a F*ck: A Counterintuitive Approach to Living a Good Life</t>
+          <t>12 Laws of the Universe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mark Manson</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>HarperOne</t>
-        </is>
-      </c>
+          <t>Manhardeep Singh</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>13/09/2016</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2016,32 +1624,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mastering Conversation Skills Goodbye Awkwardness. Learn to Master the Art of Conversation and Become A Great Communicator, Even if You've Always Been Shy or Hate Small Talk</t>
+          <t>What's Going Right: A Powerful New Method for Optimizing Your Mental Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Helen Stone</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Author's Republic</t>
-        </is>
-      </c>
+          <t>Paul Conti</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>31/03/2020</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2049,32 +1647,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Inner Engineering: A Yogi's Guide to Joy</t>
+          <t>The Subtle Art of Not Giving a F*ck: A Counterintuitive Approach to Living a Good Life</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sadhguru Vasudev</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Spiegel &amp; Grau</t>
-        </is>
-      </c>
+          <t>Mark Manson</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>20/09/2016</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2082,29 +1670,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stop Letting Everything Affect You: How to break free from overthinking, emotional chaos and self-sabotage</t>
+          <t>Self Discipline: Develop Everlasting Habits to Master Self-Control, Productivity, Mental Toughness, and a Spartan Mindset for Creating a Life of Success to Beat Addiction, Procrastination, &amp; Laziness</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Daniel Chidiac</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Undercover Publishing House</t>
-        </is>
-      </c>
+          <t>Steve G. Martin</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>07/07/2025</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -2121,24 +1701,14 @@
           <t>Brianna Wiest</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Thought Catalog Books</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>28/05/2020</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2146,32 +1716,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>How To Win Friends And Influence People</t>
+          <t>Self Discipline &amp; Time Management: Discover Powerful Strategies to Develop Everlasting Habits to Increase Productivity, Master Mental Toughness, Amplify Focus, and Achieve Your Goals!</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dale Carnegie</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
+          <t>Steve G. Martin</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>01/11/1936</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2247,19 +1807,9 @@
           <t>Caro Claire Burke</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Knopf</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -2277,19 +1827,9 @@
           <t>Lena Dunham</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Random House</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -2307,23 +1847,10 @@
           <t>Marieme Seck</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Pck;</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>25/01/2025</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2340,19 +1867,9 @@
           <t>Freida McFadden</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Poisoned Pen Press</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>27/01/2026</t>
         </is>
       </c>
     </row>
@@ -2362,27 +1879,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Strangers: A Memoir of Marriage</t>
+          <t>Theo of Golden: A Novel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Belle Burden</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Dial Press</t>
+          <t>Allen Levi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>13/01/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -2392,27 +1899,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Theo of Golden: A Novel</t>
+          <t>Strangers: A Memoir of Marriage</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Allen Levi</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Atria Books</t>
+          <t>Belle Burden</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>03/10/2025</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -2430,23 +1927,10 @@
           <t>Shelby Van Pelt</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Ecco</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>03/05/2022</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -2455,27 +1939,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Our Perfect Storm</t>
+          <t>Lights Out: An Into Darkness Novel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Carley Fortune</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Berkley Books</t>
+          <t>Navessa Allen</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -2485,31 +1959,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lights Out: An Into Darkness Novel</t>
+          <t>A Court of Thorns and Roses</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Slowburn</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>06/08/2024</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2518,31 +1979,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
+          <t>Our Perfect Storm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>James Clear</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Avery Publishing</t>
+          <t>Carley Fortune</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>16/10/2018</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -2551,31 +1999,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A Court of Thorns and Roses</t>
+          <t>The Fellowship of the Ring</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bloomsbury Publishing</t>
+          <t>J.R.R. Tolkien</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>05/05/2015</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -2584,27 +2019,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Game On: An Into Darkness Novel</t>
+          <t>This Is Me: A Reckoning</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Slowburn</t>
+          <t>Hayden Panettiere</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -2614,27 +2039,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Night We Met</t>
+          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Abby Jimenez</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Forever</t>
+          <t>James Clear</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -2644,31 +2059,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Fellowship of the Ring</t>
+          <t>The Night We Met</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>J.R.R. Tolkien</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>George Allen &amp; Unwin</t>
+          <t>Abby Jimenez</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>29/07/1954</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -2677,31 +2079,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stoicism: How to Use Stoic Philosophy to Find Inner Peace and Happiness</t>
+          <t>Phoebe Berman's Gonna Lose It: A Novel</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jason Hemlock</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Bouchard Publishing</t>
+          <t>Brooke Averick</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>01/01/2020</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2710,27 +2099,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>My Husband's Wife: A Novel</t>
+          <t>Game On: An Into Darkness Novel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alice Feeney</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Flatiron Books</t>
+          <t>Navessa Allen</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Macmillan</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>20/01/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -2740,31 +2119,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Correspondent: A Novel</t>
+          <t>My Husband's Wife: A Novel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Virginia Evans</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Crown Publishing Group</t>
+          <t>Alice Feeney</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>29/04/2025</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -2773,31 +2139,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fourth Wing</t>
+          <t>The Correspondent: A Novel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rebecca Yarros</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Red Tower Books (Entangled Publishing)</t>
+          <t>Virginia Evans</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>02/05/2023</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2806,31 +2159,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A Court of Mist and Fury</t>
+          <t>The Midnight Train: A Novel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bloomsbury Publishing</t>
+          <t>Matt Haig</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>03/05/2016</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -2839,27 +2179,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Things We Never Say: A Novel</t>
+          <t>The Land and Its People: Essays</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Elizabeth Strout</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Random House</t>
+          <t>David Sedaris</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -2869,31 +2199,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Action Bible: God's Redemptive Story</t>
+          <t>A Court of Mist and Fury</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Doug Mauss</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>David C Cook</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>01/01/2010</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2902,27 +2219,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A Little More Social: How Small Choices Create Unexpected Happiness, Health, and Connection</t>
+          <t>Fourth Wing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nicholas Epley</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Knopf</t>
+          <t>Rebecca Yarros</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -2932,31 +2239,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Deal – Reine Verhandlungssache: Off-Campus 1 \| Roman \| BookTok-Liebling \| Prickelnde College-Romance für New Adults</t>
+          <t>Every Summer After</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Elle Kennedy</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Elle Kennedy Inc.</t>
+          <t>Carley Fortune</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>24/02/2015</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2965,31 +2259,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Red Rising</t>
+          <t>Detached: How to Let Go, Heal, and Become Irresistible</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pierce Brown</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Del Rey Books</t>
+          <t>Sabrina Alexis Bendory</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>28/01/2014</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -2998,31 +2279,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Throne of Glass</t>
+          <t>The Action Bible: God's Redemptive Story</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Bloomsbury Publishing</t>
+          <t>Doug Mauss</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>02/08/2012</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -3031,31 +2299,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The 48 Laws of Power</t>
+          <t>Fever Dream: Small-town, dating show, rival's little sister romance</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Robert Greene</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Viking Press</t>
+          <t>Elsie Silver</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>01/01/1998</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -3064,27 +2319,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>This Is Me: A Reckoning</t>
+          <t>Red Rising</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hayden Panettiere</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Grand Central Publishing</t>
+          <t>Pierce Brown</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -3094,27 +2339,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>This Story Might Save Your Life: A Novel</t>
+          <t>Throne of Glass</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tiffany Crum</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Flatiron Books</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Macmillan</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -3124,27 +2359,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Fourth Option: A Novel</t>
+          <t>The 48 Laws of Power</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jack Carr, M.P. Woodward</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Atria/Emily Bestler Books</t>
+          <t>Robert Greene</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -3154,31 +2379,18 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A Court of Wings and Ruin</t>
+          <t>Stoicism: How to Use Stoic Philosophy to Find Inner Peace and Happiness</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Bloomsbury Publishing</t>
+          <t>Jason Hemlock</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>02/05/2017</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3255,23 +2467,10 @@
           <t>Navessa Allen</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Slowburn</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>06/08/2024</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3280,31 +2479,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Deal – Reine Verhandlungssache: Off-Campus 1 \| Roman \| BookTok-Liebling \| Prickelnde College-Romance für New Adults</t>
+          <t>Phoebe Berman's Gonna Lose It: A Novel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Elle Kennedy</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Elle Kennedy Inc.</t>
+          <t>Brooke Averick</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>24/02/2015</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3313,27 +2499,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This Story Might Save Your Life: A Novel</t>
+          <t>Every Summer After</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tiffany Crum</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Flatiron Books</t>
+          <t>Carley Fortune</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Macmillan</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -3351,19 +2527,9 @@
           <t>Elsie Silver</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Atria Books</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -3373,27 +2539,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Caught Up</t>
+          <t>This Story Might Save Your Life: A Novel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Slowburn</t>
+          <t>Tiffany Crum</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>10/06/2025</t>
         </is>
       </c>
     </row>
@@ -3411,19 +2567,9 @@
           <t>Emma Brodie</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ballantine Books</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -3433,31 +2579,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Heated Rivalry</t>
+          <t>Caught Up</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rachel Reid</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Carina Press</t>
+          <t>Navessa Allen</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>25/03/2019</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3466,31 +2599,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quicksilver: The Fae &amp; Alchemy Series, Book 1</t>
+          <t>Dolly All the Time: A GMA Book Club Pick</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Callie Hart</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Independently Published</t>
+          <t>Annabel Monaghan</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>04/06/2024</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3499,27 +2619,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Brimstone: The Fae &amp; Alchemy Series, Book 2</t>
+          <t>The Seven Husbands of Evelyn Hugo: A Novel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Callie Hart</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Forever</t>
+          <t>Taylor Jenkins Reid</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>18/11/2025</t>
         </is>
       </c>
     </row>
@@ -3529,31 +2639,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Every Summer After</t>
+          <t>Heated Rivalry</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Carley Fortune</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Berkley Books</t>
+          <t>Rachel Reid</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>10/05/2022</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3630,19 +2727,9 @@
           <t>Freida McFadden</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Poisoned Pen Press</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>27/01/2026</t>
         </is>
       </c>
     </row>
@@ -3652,27 +2739,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Fourth Option: A Novel</t>
+          <t>The Housemaid: An absolutely addictive psychological thriller with a jaw-dropping twist</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jack Carr, M.P. Woodward</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Atria/Emily Bestler Books</t>
+          <t>Freida McFadden</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -3682,31 +2759,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Housemaid: An absolutely addictive psychological thriller with a jaw-dropping twist</t>
+          <t>The Fourth Option: A Novel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Bookouture</t>
+          <t>Jack Carr, M.P. Woodward</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>26/04/2022</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3715,31 +2779,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Silent Patient</t>
+          <t>The Mad Wife</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alex Michaelides</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Celadon Books</t>
+          <t>Meagan Church</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>05/02/2019</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3748,31 +2799,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Asylum Confessions: Deathbed Confessions of the Criminally Insane</t>
+          <t>Nobody Knows You're Here: A Psychological Suspense Thriller</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jack Steen</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Deathbed Publishing</t>
+          <t>Bryn Greenwood</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>10/03/2021</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3781,27 +2819,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Mad Wife</t>
+          <t>The Silent Patient</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Meagan Church</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Sourcebooks Landmark</t>
+          <t>Alex Michaelides</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>30/09/2025</t>
         </is>
       </c>
     </row>
@@ -3811,27 +2839,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nobody Knows You're Here: A Psychological Suspense Thriller</t>
+          <t>Mad Mabel: A Novel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bryn Greenwood</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Podium Publishing</t>
+          <t>Sally Hepworth</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>16/09/2025</t>
         </is>
       </c>
     </row>
@@ -3841,27 +2859,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mad Mabel: A Novel</t>
+          <t>The Asylum Confessions: Deathbed Confessions of the Criminally Insane</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sally Hepworth</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>St. Martin's Press</t>
+          <t>Jack Steen</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Macmillan</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -3871,31 +2879,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Housemaid's Secret: A totally gripping psychological thriller with a shocking twist</t>
+          <t>The Final Target</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Bookouture</t>
+          <t>Nora Roberts</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>11/07/2023</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -3904,27 +2899,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Judge Stone: A Novel</t>
+          <t>The Housemaid's Secret: A totally gripping psychological thriller with a shocking twist</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>James Patterson, Viola Davis</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Little, Brown and Company</t>
+          <t>Freida McFadden</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>09/03/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -4002,23 +2987,10 @@
           <t>Chris Harris</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Little, Brown Books for Young Readers</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>27/09/2022</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -4035,23 +3007,10 @@
           <t>Rick Riordan</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Miramax Books</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>28/06/2005</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4068,23 +3027,10 @@
           <t>Arnold Lobel</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>02/11/2004</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -4093,31 +3039,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Warriors #1: Into the Wild: A Stunning Deluxe Edition of the Epic Beginning of the Warriors Cats Series</t>
+          <t>How to Catch a Monster</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Erin Hunter</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HarperCollins</t>
+          <t>Adam Wallace</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>21/01/2003</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4126,27 +3059,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KPop Demon Hunters: The Official Deluxe Junior Novelization: The Official Retelling</t>
+          <t>Pete the Cat and the Perfect Pizza Party</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jessica Yoon</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Random House Books for Young Readers</t>
+          <t>James Dean, Kimberly Dean</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -4156,31 +3079,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Miles the Brave</t>
+          <t>The Beginner's Bible: Timeless Children's Stories</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Storybutton, Mike Marshall, Steven Forbis</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Storybutton</t>
+          <t>The Beginner's Bible</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>12/10/2024</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -4189,31 +3099,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Boxcar Children Collection Volume 1: The Boxcar Children, Surprise Island, Yellow House Mystery</t>
+          <t>Warriors #1: Into the Wild: A Stunning Deluxe Edition of the Epic Beginning of the Warriors Cats Series</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gertrude Chandler Warner</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Rand McNally &amp; Company</t>
+          <t>Erin Hunter</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>01/01/1924</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -4222,31 +3119,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Beginner's Bible: Timeless Children's Stories</t>
+          <t>Miles the Brave</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The Beginner's Bible</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Mission City Press, Inc.</t>
+          <t>Storybutton, Mike Marshall, Steven Forbis</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>01/01/1989</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -4255,31 +3139,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Lion, the Witch and the Wardrobe: Classic Fantasy Tale for Kids</t>
+          <t>KPop Demon Hunters: The Official Deluxe Junior Novelization: The Official Retelling</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C. S. Lewis</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Geoffrey Bles</t>
+          <t>Jessica Yoon</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>16/10/1950</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4288,31 +3159,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pete the Cat and the Perfect Pizza Party</t>
+          <t>Walter the Whale Shark: And His Teeny Tiny Teeth</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>James Dean, Kimberly Dean</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HarperCollins</t>
+          <t>Katrine Crow</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>03/09/2019</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4381,31 +3239,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Anxious Generation: How the Great Rewiring of Childhood Is Causing an Epidemic of Mental Illness</t>
+          <t>Dear Therapist: I Can't Stand My Sister-in-Law</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jonathan Haidt</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Penguin Press</t>
+          <t>Lori Gottlieb, The Atlantic</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>26/03/2024</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -4414,31 +3259,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adult Children of Emotionally Immature Parents: How to Heal from Distant, Rejecting, or Self-Involved Parents</t>
+          <t>The Anxious Generation: How the Great Rewiring of Childhood Is Causing an Epidemic of Mental Illness</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lindsay C. Gibson, PsyD</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New Harbinger Publications</t>
+          <t>Jonathan Haidt</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>01/06/2015</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4447,31 +3279,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hunt, Gather, Parent: What Ancient Cultures Can Teach Us About the Lost Art of Raising Happy, Helpful Little Humans</t>
+          <t>Adult Children of Emotionally Immature Parents: How to Heal from Distant, Rejecting, or Self-Involved Parents</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Michaeleen Doucleff</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Avid Reader Press / Simon &amp; Schuster</t>
+          <t>Lindsay C. Gibson, PsyD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>01/03/2021</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -4480,31 +3299,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Good Inside: A Practical Guide to Resilient Parenting Prioritizing Connection Over Correction</t>
+          <t>Hunt, Gather, Parent: What Ancient Cultures Can Teach Us About the Lost Art of Raising Happy, Helpful Little Humans</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Becky Kennedy</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Harper Wave</t>
+          <t>Michaeleen Doucleff</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>13/09/2022</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4513,27 +3319,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Tired Dad.: 100 Reflections on Showing Up for What Matters Most</t>
+          <t>The Tree with Matchmaking Powers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jon Gustin</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Convergent Books</t>
+          <t>Jeff Maysh, The Atlantic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -4543,31 +3339,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Expecting Better: Why the Conventional Pregnancy Wisdom Is Wrong--and What You Really Need to Know</t>
+          <t>Good Inside: A Practical Guide to Resilient Parenting Prioritizing Connection Over Correction</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Emily Oster</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Penguin Books</t>
+          <t>Becky Kennedy</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>20/08/2013</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -4576,31 +3359,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Seven Principles for Making Marriage Work: A Practical Guide from the Country’s Foremost Relationship Expert, Revised and Updated</t>
+          <t>Expecting Better: Why the Conventional Pregnancy Wisdom Is Wrong--and What You Really Need to Know</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>John M. Gottman, PhD, Nan Silver</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Harmony</t>
+          <t>Emily Oster</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>01/01/1999</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -4617,23 +3387,10 @@
           <t>Emily Oster</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Penguin Press</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>01/01/2019</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -4642,31 +3399,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Men with Adult ADHD: How to Raise Emotionally Intelligent Men and Improve Relationships</t>
+          <t>The Seven Principles for Making Marriage Work: A Practical Guide from the Country’s Foremost Relationship Expert, Revised and Updated</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Garth Zeus</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Garth Zeus</t>
+          <t>John M. Gottman, PhD, Nan Silver</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>28/01/2023</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4675,31 +3419,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Oh Crap! Potty Training: Everything Modern Parents Need to Know to Do It Once and Do It Right</t>
+          <t>Men with Adult ADHD: How to Raise Emotionally Intelligent Men and Improve Relationships</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jamie Glowacki</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Gallery Books</t>
+          <t>Garth Zeus</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>16/06/2015</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4776,23 +3507,10 @@
           <t>Yuval Noah Harari</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Dvir Publishing House Ltd.</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>01/01/2011</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -4801,27 +3519,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Traversal</t>
+          <t>Mythos</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Maria Popova</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Farrar, Straus and Giroux</t>
+          <t>Stephen Fry</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>17/02/2026</t>
         </is>
       </c>
     </row>
@@ -4831,31 +3539,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mythos</t>
+          <t>1929: Inside the Greatest Crash in Wall Street History--and How It Shattered a Nation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Stephen Fry</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Michael Joseph</t>
+          <t>Andrew Ross Sorkin</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>01/01/2017</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -4872,23 +3567,10 @@
           <t>Howard Zinn</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Harper &amp; Row</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>01/01/1980</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4897,27 +3579,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1929: Inside the Greatest Crash in Wall Street History--and How It Shattered a Nation</t>
+          <t>The Coming Storm: Power, Conflict, and Warnings from History</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Andrew Ross Sorkin</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Viking Press</t>
+          <t>Odd Arne Westad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>14/10/2025</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -4927,31 +3599,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Very Secret Sex Lives of Medieval Women: An Inside Look at Women &amp; Sex in Medieval Times</t>
+          <t>How to Hide an Empire: A History of the Greater United States</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rosalie Gilbert</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Mango Publishing</t>
+          <t>Daniel Immerwahr</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>27/10/2020</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -4960,31 +3619,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>How to Hide an Empire: A History of the Greater United States</t>
+          <t>Codename Nemo: The Hunt for a Nazi U-Boat and the Elusive Enigma Machine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Daniel Immerwahr</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Farrar, Straus and Giroux</t>
+          <t>Charles Lachman</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>19/02/2019</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -4993,31 +3639,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Codename Nemo: The Hunt for a Nazi U-Boat and the Elusive Enigma Machine</t>
+          <t>The Very Secret Sex Lives of Medieval Women: An Inside Look at Women &amp; Sex in Medieval Times</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charles Lachman</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Diversion Books</t>
+          <t>Rosalie Gilbert</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>04/06/2024</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -5026,31 +3659,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Third Reich: A History of Nazi Germany</t>
+          <t>Empire of the Summer Moon: Quanah Parker and the Rise and Fall of the Comanches, the Most Powerful Indian Tribe in American History</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thomas Childers</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Simon &amp; Schuster</t>
+          <t>S. C. Gwynne</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>01/01/2017</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -5059,12 +3679,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>On Witness and Respair: Essays</t>
+          <t>The Third Reich: A History of Nazi Germany</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jesmyn Ward</t>
+          <t>Thomas Childers</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5147,23 +3767,10 @@
           <t>Doug Mauss</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>David C Cook</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>01/01/2010</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -5172,31 +3779,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>How to Hold a Cockroach: A book for those who are free and don't know it</t>
+          <t>Shaolin Spirit: The Way to Self-Mastery</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Matthew Maxwell</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Hearthstone</t>
+          <t>Shi Heng Yi</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10/04/2020</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -5205,31 +3799,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The King James Bible</t>
+          <t>How to Hold a Cockroach: A book for those who are free and don't know it</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uncredited</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Robert Barker</t>
+          <t>Matthew Maxwell</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>01/01/1611</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -5238,31 +3819,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Alchemist: A Modern Classic Fable of Spiritual Healing, Self-Discovery, and the Power of Dreams in a Visually Stunning Graphic Novel—Get Lost in the Pages of This Captivating Summer Read</t>
+          <t>The King James Bible</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paulo Coelho</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HarperOne</t>
+          <t>Uncredited</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>01/11/2010</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -5271,31 +3839,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NIV Listener's Audio Bible: Complete Bible: Vocal Performance by Max McLean</t>
+          <t>The Alchemist: A Modern Classic Fable of Spiritual Healing, Self-Discovery, and the Power of Dreams in a Visually Stunning Graphic Novel—Get Lost in the Pages of This Captivating Summer Read</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Zondervan</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Zondervan</t>
+          <t>Paulo Coelho</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>03/11/2015</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5312,23 +3867,10 @@
           <t>Alan Watts</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Shambhala</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>01/01/1995</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -5337,31 +3879,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mere Christianity</t>
+          <t>NIV Listener's Audio Bible: Complete Bible: Vocal Performance by Max McLean</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C. S. Lewis</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Geoffrey Bles</t>
+          <t>Zondervan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>07/07/1952</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -5370,31 +3899,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Four Agreements: A Practical Guide to Personal Freedom</t>
+          <t>Mere Christianity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Don Miguel Ruiz, Janet Mills</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Amber-Allen Publishing</t>
+          <t>C. S. Lewis</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>01/11/1997</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -5403,27 +3919,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stand Firm and Act Like Men: Becoming the Man You Were Created to Be Instead of Who the World Says You Are</t>
+          <t>The Four Agreements: A Practical Guide to Personal Freedom</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Joby Martin, Charles Martin</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Faithwords</t>
+          <t>Don Miguel Ruiz, Janet Mills</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>07/10/2025</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -5433,31 +3939,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Book of Enoch: The Complete Audiobook</t>
+          <t>Stand Firm and Act Like Men: Becoming the Man You Were Created to Be Instead of Who the World Says You Are</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christopher Glyn</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SAGA Egmont</t>
+          <t>Joby Martin, Charles Martin</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>08/07/2019</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5534,23 +4027,10 @@
           <t>Sarah J. Maas</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Bloomsbury Publishing</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>05/05/2015</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -5567,23 +4047,10 @@
           <t>Sarah J. Maas</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Bloomsbury Publishing</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>03/05/2016</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -5600,23 +4067,10 @@
           <t>Stephenie Meyer</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Little, Brown and Company</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>05/10/2005</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -5625,31 +4079,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lord of the Flies</t>
+          <t>The Summer I Turned Pretty</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>William Golding</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Faber and Faber</t>
+          <t>Jenny Han</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>17/09/1954</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -5678,31 +4119,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Summer I Turned Pretty</t>
+          <t>The Summer of Second Chances</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jenny Han</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Simon &amp; Schuster Books for Young Readers</t>
+          <t>K. L. Walther</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>05/05/2009</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -5711,31 +4139,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Better Than the Movies</t>
+          <t>Lord of the Flies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lynn Painter</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Simon &amp; Schuster</t>
+          <t>William Golding</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>04/05/2021</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -5744,31 +4159,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Powerless</t>
+          <t>Better Than the Movies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lauren Roberts</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Lynn Painter</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>07/11/2023</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -5785,23 +4187,10 @@
           <t>Christopher Paolini</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Paolini International LLC</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>01/01/2002</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -5810,31 +4199,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ten Days in a Mad-House</t>
+          <t>A Good Girl's Guide to Murder</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nellie Bly</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Norman Munro</t>
+          <t>Holly Jackson</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>01/01/1887</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/audiobooks.xlsx
+++ b/audiobooks.xlsx
@@ -737,10 +737,23 @@
           <t>Morgan Housel</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Harriman House</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>01/09/2020</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -749,18 +762,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Disrupt Everything—and Win: Take Control of Your Future</t>
+          <t>How to Talk to Anyone and Be More Charismatic: Improve Communication &amp; People Skills, Master Small Talk, Build Confidence &amp; Influence, Overcome Social Anxiety, and Make Friends in Any Conversation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>James Patterson, Patrick Leddin PhD</t>
+          <t>Nathan Soren</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Nathan Soren</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>14/05/2025</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -777,10 +803,23 @@
           <t>Chris Voss, Tahl Raz</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Harper Business</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>17/05/2016</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -797,10 +836,23 @@
           <t>Will Guidara</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Optimism Press</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>25/10/2022</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -817,10 +869,23 @@
           <t>Jocko Willink, Leif Babin</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>St. Martin's Press</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Macmillan</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>20/10/2015</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -829,18 +894,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>How to Talk to Anyone and Be More Charismatic: Improve Communication &amp; People Skills, Master Small Talk, Build Confidence &amp; Influence, Overcome Social Anxiety, and Make Friends in Any Conversation</t>
+          <t>Speak Like a CEO: How to Speak with Power, Lead with Clarity, and Command Any Room Without Saying a Word Too Much</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nathan Soren</t>
+          <t>CALDER MP KNOX</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>McGraw-Hill Companies</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31/03/2005</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -849,18 +927,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A Little More Social: How Small Choices Create Unexpected Happiness, Health, and Connection</t>
+          <t>The 7 Habits of Highly Effective People: 30th Anniversary Edition</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nicholas Epley</t>
+          <t>Stephen R. Covey, Sean Covey</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Free Press</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>01/01/1989</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -869,18 +960,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The 7 Habits of Highly Effective People: 30th Anniversary Edition</t>
+          <t>Millionaire Mindset and Habits for Success</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stephen R. Covey, Sean Covey</t>
+          <t>M.A. Myers</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Author's Republic</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>19/01/2022</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -897,10 +1001,23 @@
           <t>Napoleon Hill, Ross Cornwell</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>The Ralston Society</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>01/03/1937</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -917,10 +1034,23 @@
           <t>Napoleon Hill</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The Ralston Society</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>01/03/1937</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -997,9 +1127,19 @@
           <t>Belle Burden</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dial Press</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>13/01/2026</t>
         </is>
       </c>
     </row>
@@ -1009,18 +1149,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>This Is Me: A Reckoning</t>
+          <t>I'm Glad My Mom Died</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hayden Panettiere</t>
+          <t>Jennette McCurdy</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>09/08/2022</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1029,17 +1182,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>I'm Glad My Mom Died</t>
+          <t>Stripped Down: Unfiltered and Unapologetic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jennette McCurdy</t>
+          <t>Bunnie Xo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Dey Street Books</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
         </is>
       </c>
     </row>
@@ -1049,18 +1212,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stripped Down: Unfiltered and Unapologetic</t>
+          <t>Kitchen Confidential: Adventures in the Culinary Underbelly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bunnie Xo</t>
+          <t>Anthony Bourdain, Irvine Welsh</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>01/08/2000</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1069,17 +1245,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You with the Sad Eyes: A Memoir</t>
+          <t>This Is Me: A Reckoning</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Christina Applegate</t>
+          <t>Hayden Panettiere</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Grand Central Publishing</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -1089,17 +1275,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bad Bunny: ‘What’s the Point in Being Here? To Show the World Who I Am’</t>
+          <t>You with the Sad Eyes: A Memoir</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Julyssa Lopez, Rolling Stone</t>
+          <t>Christina Applegate</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>03/03/2026</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1305,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Phases: A Memoir</t>
+          <t>The Make-Believe: A Memoir of Magic and Madness</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brandy</t>
+          <t>Hannah Murray</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>The Dial Press</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -1137,9 +1343,19 @@
           <t>Emma Grede</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Avid Reader Press/Simon &amp; Schuster</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -1149,18 +1365,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>(Un)educated: My Life as a Teacher, and Why You Should Never Become One</t>
+          <t>Wild Rescues: A Paramedic’s Extreme Adventures in Yosemite, Yellowstone, and Grand Teton</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Francis Foster</t>
+          <t>Kevin Grange</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Chicago Review Press</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>01/03/2021</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1169,18 +1398,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kitchen Confidential: Adventures in the Culinary Underbelly</t>
+          <t>Born a Crime: Stories from a South African Childhood</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Anthony Bourdain, Irvine Welsh</t>
+          <t>Trevor Noah</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Spiegel &amp; Grau</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>15/11/2016</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1257,10 +1499,23 @@
           <t>J.R.R. Tolkien</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>George Allen &amp; Unwin</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>29/07/1954</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1277,10 +1532,23 @@
           <t>Rebecca Yarros</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Red Tower Books</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>02/05/2023</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1297,10 +1565,23 @@
           <t>Pierce Brown</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Del Rey Books</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>28/01/2014</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1317,10 +1598,23 @@
           <t>Sarah J. Maas</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bloomsbury Publishing</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>02/08/2012</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1329,18 +1623,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A Court of Wings and Ruin</t>
+          <t>A Game of Thrones: A Song of Ice and Fire: Book One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>George R. R. Martin</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bantam Spectra</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>01/08/1996</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1349,7 +1656,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Heir of Fire</t>
+          <t>A Court of Wings and Ruin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1357,10 +1664,23 @@
           <t>Sarah J. Maas</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bloomsbury Publishing</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>02/05/2017</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1369,18 +1689,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Iron Flame</t>
+          <t>Heir of Fire</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rebecca Yarros</t>
+          <t>Sarah J. Maas</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bloomsbury YA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>02/09/2014</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1389,18 +1722,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Crown of Midnight</t>
+          <t>Iron Flame</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>Rebecca Yarros</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Red Tower Books (Entangled Publishing)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>07/11/2023</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1409,17 +1755,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Two Towers</t>
+          <t>True Paranormal Stories From Cops</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>J.R.R. Tolkien</t>
+          <t>Scary Studios</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Scary Studios</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -1429,18 +1785,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A Game of Thrones: A Song of Ice and Fire: Book One</t>
+          <t>Crown of Midnight</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>George R. R. Martin</t>
+          <t>Sarah J. Maas</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bloomsbury USA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>01/08/2013</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1517,13 +1886,21 @@
           <t>Marieme Seck</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Marieme Seck</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -1540,14 +1917,24 @@
           <t>James Clear</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Avery Publishing</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>16/10/2018</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1555,22 +1942,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Detached: How to Let Go, Heal, and Become Irresistible</t>
+          <t>Mastering Conversation Skills Goodbye Awkwardness. Learn to Master the Art of Conversation and Become A Great Communicator, Even if You've Always Been Shy or Hate Small Talk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sabrina Alexis Bendory</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Helen Stone</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Author's Republic</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>31/03/2020</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1578,21 +1975,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mastering Conversation Skills Goodbye Awkwardness. Learn to Master the Art of Conversation and Become A Great Communicator, Even if You've Always Been Shy or Hate Small Talk</t>
+          <t>Detached: How to Let Go, Heal, and Become Irresistible</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Helen Stone</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Sabrina Alexis Bendory</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Thought Catalog Books</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1601,21 +2006,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12 Laws of the Universe</t>
+          <t>Dealing with Feeling: Use Your Emotions to Create the Life You Want</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Manhardeep Singh</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Marc Brackett Ph.D.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Celadon Books</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1624,22 +2037,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What's Going Right: A Powerful New Method for Optimizing Your Mental Health</t>
+          <t>The Subtle Art of Not Giving a F*ck: A Counterintuitive Approach to Living a Good Life</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paul Conti</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Mark Manson</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HarperOne</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>13/09/2016</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1647,22 +2070,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Subtle Art of Not Giving a F*ck: A Counterintuitive Approach to Living a Good Life</t>
+          <t>Self Discipline: Develop Everlasting Habits to Master Self-Control, Productivity, Mental Toughness, and a Spartan Mindset for Creating a Life of Success to Beat Addiction, Procrastination, &amp; Laziness</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mark Manson</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Steve G. Martin</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>GA Publishing</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>26/02/2022</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1670,21 +2103,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Self Discipline: Develop Everlasting Habits to Master Self-Control, Productivity, Mental Toughness, and a Spartan Mindset for Creating a Life of Success to Beat Addiction, Procrastination, &amp; Laziness</t>
+          <t>How to Not Die in Prison: A Survival Guide</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Steve G. Martin</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Taylor Sheridan, Tom Nelson</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1693,22 +2134,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Mountain is You: Transforming Self-Sabotage Into Self-Mastery</t>
+          <t>12 Laws of the Universe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brianna Wiest</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Manhardeep Singh</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Independently published</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>20/10/2021</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,22 +2167,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Self Discipline &amp; Time Management: Discover Powerful Strategies to Develop Everlasting Habits to Increase Productivity, Master Mental Toughness, Amplify Focus, and Achieve Your Goals!</t>
+          <t>The Mountain is You: Transforming Self-Sabotage Into Self-Mastery</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Steve G. Martin</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Brianna Wiest</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Thought Catalog Books</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>01/01/2020</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1807,9 +2268,19 @@
           <t>Caro Claire Burke</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Knopf</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -1819,18 +2290,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Famesick: A Memoir</t>
+          <t>Harry Potter and the Sorcerer's Stone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lena Dunham</t>
+          <t>J.K. Rowling</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Scholastic Corporation</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>01/09/1998</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1839,17 +2323,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Not giving a F*ck Anymore.: Stop People-Pleasing, Set Boundaries, and Start Living on Your Own Terms.</t>
+          <t>Famesick: A Memoir</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Marieme Seck</t>
+          <t>Lena Dunham</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Random House</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -1859,17 +2353,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dear Debbie</t>
+          <t>Cancel Me If You Can</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
+          <t>Dave Portnoy</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Gallery Books</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -1879,17 +2383,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Theo of Golden: A Novel</t>
+          <t>Not giving a F*ck Anymore.: Stop People-Pleasing, Set Boundaries, and Start Living on Your Own Terms.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Allen Levi</t>
+          <t>Marieme Seck</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Marieme Seck</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
         </is>
       </c>
     </row>
@@ -1899,17 +2413,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Strangers: A Memoir of Marriage</t>
+          <t>Regime Change: Inside the Imperial Presidency of Donald Trump</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Belle Burden</t>
+          <t>Maggie Haberman, Jonathan Swan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -1919,18 +2443,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Remarkably Bright Creatures: A Read with Jenna Pick</t>
+          <t>Theo of Golden: A Novel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Shelby Van Pelt</t>
+          <t>Allen Levi</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Atria Books</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1939,17 +2476,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lights Out: An Into Darkness Novel</t>
+          <t>The Calamity Club: A Novel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
+          <t>Kathryn Stockett</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Spiegel &amp; Grau</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -1959,17 +2506,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A Court of Thorns and Roses</t>
+          <t>It Could Have Been Her: A Novel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>Lisa Jewell</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Atria Books</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -1979,18 +2536,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Our Perfect Storm</t>
+          <t>A Court of Thorns and Roses</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Carley Fortune</t>
+          <t>Sarah J. Maas</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>05/05/2015</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1999,17 +2569,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Fellowship of the Ring</t>
+          <t>Strangers: A Memoir of Marriage</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>J.R.R. Tolkien</t>
+          <t>Belle Burden</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Dial Press</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>13/01/2026</t>
         </is>
       </c>
     </row>
@@ -2019,18 +2599,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>This Is Me: A Reckoning</t>
+          <t>Lights Out: An Into Darkness Novel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hayden Panettiere</t>
+          <t>Navessa Allen</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Slowburn</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>06/08/2024</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2039,18 +2632,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
+          <t>The Fellowship of the Ring</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>James Clear</t>
+          <t>J.R.R. Tolkien</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>George Allen &amp; Unwin</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>29/07/1954</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2059,17 +2665,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Night We Met</t>
+          <t>Dear Debbie</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Abby Jimenez</t>
+          <t>Freida McFadden</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Poisoned Pen Press</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>27/01/2026</t>
         </is>
       </c>
     </row>
@@ -2079,18 +2695,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Phoebe Berman's Gonna Lose It: A Novel</t>
+          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brooke Averick</t>
+          <t>James Clear</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Avery Publishing</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>16/10/2018</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2099,18 +2728,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Game On: An Into Darkness Novel</t>
+          <t>Remarkably Bright Creatures: A Read with Jenna Pick</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
+          <t>Shelby Van Pelt</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ecco Press</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>01/05/2022</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2119,18 +2761,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>My Husband's Wife: A Novel</t>
+          <t>How to Hold a Cockroach: A book for those who are free and don't know it</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alice Feeney</t>
+          <t>Matthew Maxwell</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Hearthstone</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>10/04/2020</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2139,18 +2794,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Correspondent: A Novel</t>
+          <t>Every Summer After</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Virginia Evans</t>
+          <t>Carley Fortune</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Berkley Books</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>10/05/2022</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2159,17 +2827,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Midnight Train: A Novel</t>
+          <t>Our Perfect Storm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Matt Haig</t>
+          <t>Carley Fortune</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Penguin Publishing Group</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -2179,18 +2857,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Land and Its People: Essays</t>
+          <t>Fourth Wing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>David Sedaris</t>
+          <t>Rebecca Yarros</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Red Tower Books</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>02/05/2023</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2207,10 +2898,23 @@
           <t>Sarah J. Maas</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Bloomsbury Publishing</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>03/05/2016</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2219,18 +2923,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fourth Wing</t>
+          <t>The Correspondent: A Novel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rebecca Yarros</t>
+          <t>Virginia Evans</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Crown</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>29/04/2025</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2239,18 +2956,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Every Summer After</t>
+          <t>Mastering Conversation Skills Goodbye Awkwardness. Learn to Master the Art of Conversation and Become A Great Communicator, Even if You've Always Been Shy or Hate Small Talk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Carley Fortune</t>
+          <t>Helen Stone</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Author's Republic</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>31/03/2020</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2259,17 +2989,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Detached: How to Let Go, Heal, and Become Irresistible</t>
+          <t>The Night We Met</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sabrina Alexis Bendory</t>
+          <t>Abby Jimenez</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Forever</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -2279,12 +3019,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Action Bible: God's Redemptive Story</t>
+          <t>Claude AI for Beginners: How to Use Claude to Write Better, Research Faster, and Boost Productivity</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Doug Mauss</t>
+          <t>Nicholas Hunter</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2299,17 +3039,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fever Dream: Small-town, dating show, rival's little sister romance</t>
+          <t>Nobody Knows You're Here: A Psychological Suspense Thriller</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Elsie Silver</t>
+          <t>Bryn Greenwood</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Podium Publishing</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
         </is>
       </c>
     </row>
@@ -2319,17 +3069,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Red Rising</t>
+          <t>Game On: An Into Darkness Novel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pierce Brown</t>
+          <t>Navessa Allen</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Slowburn</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
         </is>
       </c>
     </row>
@@ -2339,17 +3099,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Throne of Glass</t>
+          <t>Whistler: A Novel</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>Ann Patchett</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Harper</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -2359,18 +3129,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The 48 Laws of Power</t>
+          <t>Red Rising</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Robert Greene</t>
+          <t>Pierce Brown</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Del Rey Books</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>28/01/2014</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2379,18 +3162,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Stoicism: How to Use Stoic Philosophy to Find Inner Peace and Happiness</t>
+          <t>Throne of Glass</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jason Hemlock</t>
+          <t>Sarah J. Maas</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>02/08/2012</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2467,10 +3263,23 @@
           <t>Navessa Allen</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Slowburn</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>06/08/2024</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2479,18 +3288,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Phoebe Berman's Gonna Lose It: A Novel</t>
+          <t>Every Summer After</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brooke Averick</t>
+          <t>Carley Fortune</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Berkley Books</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10/05/2022</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2499,17 +3321,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Every Summer After</t>
+          <t>Dolly All the Time: A GMA Book Club Pick</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Carley Fortune</t>
+          <t>Annabel Monaghan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>G.P. Putnam's Sons</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
@@ -2519,17 +3351,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fever Dream: Small-town, dating show, rival's little sister romance</t>
+          <t>Phoebe Berman's Gonna Lose It: A Novel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Elsie Silver</t>
+          <t>Brooke Averick</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Crown</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
@@ -2547,9 +3389,19 @@
           <t>Tiffany Crum</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Flatiron Books</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Macmillan</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
@@ -2559,18 +3411,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Into the Blue: Reese's Book Club: A Love Story</t>
+          <t>The Love Hypothesis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Emma Brodie</t>
+          <t>Ali Hazelwood</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Berkley Books</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>14/09/2021</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2579,17 +3444,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caught Up</t>
+          <t>Into the Blue: Reese's Book Club: A Love Story</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
+          <t>Emma Brodie</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ballantine Books</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -2599,18 +3474,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dolly All the Time: A GMA Book Club Pick</t>
+          <t>The Seven Husbands of Evelyn Hugo: A Novel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Annabel Monaghan</t>
+          <t>Taylor Jenkins Reid</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Atria Books</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>13/06/2017</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2619,18 +3507,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Seven Husbands of Evelyn Hugo: A Novel</t>
+          <t>Caught Up</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Taylor Jenkins Reid</t>
+          <t>Navessa Allen</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Zando – Slowburn</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2639,18 +3540,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Heated Rivalry</t>
+          <t>Quicksilver: The Fae &amp; Alchemy Series, Book 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rachel Reid</t>
+          <t>Callie Hart</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Independently Published</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>03/06/2024</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2719,17 +3633,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dear Debbie</t>
+          <t>It Could Have Been Her: A Novel</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
+          <t>Lisa Jewell</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Atria Books</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -2739,7 +3663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Housemaid: An absolutely addictive psychological thriller with a jaw-dropping twist</t>
+          <t>Dear Debbie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2747,9 +3671,19 @@
           <t>Freida McFadden</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Poisoned Pen Press</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>27/01/2026</t>
         </is>
       </c>
     </row>
@@ -2759,17 +3693,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Fourth Option: A Novel</t>
+          <t>Nobody Knows You're Here: A Psychological Suspense Thriller</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jack Carr, M.P. Woodward</t>
+          <t>Bryn Greenwood</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Podium Publishing</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
         </is>
       </c>
     </row>
@@ -2779,17 +3723,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Mad Wife</t>
+          <t>Mad Mabel: A Novel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Meagan Church</t>
+          <t>Sally Hepworth</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>St. Martin's Press</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Macmillan</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -2799,17 +3753,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nobody Knows You're Here: A Psychological Suspense Thriller</t>
+          <t>The Mad Wife</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bryn Greenwood</t>
+          <t>Meagan Church</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sourcebooks Landmark</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
         </is>
       </c>
     </row>
@@ -2819,18 +3783,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Silent Patient</t>
+          <t>The Asylum Confessions: Deathbed Confessions of the Criminally Insane</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alex Michaelides</t>
+          <t>Jack Steen</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Deathbed Publishing</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10/03/2021</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2839,17 +3816,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mad Mabel: A Novel</t>
+          <t>Nine Lives: A Novel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sally Hepworth</t>
+          <t>Catherine Steadman</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bantam</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -2859,18 +3846,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Asylum Confessions: Deathbed Confessions of the Criminally Insane</t>
+          <t>The Silent Patient</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jack Steen</t>
+          <t>Alex Michaelides</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Celadon Books</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>05/02/2019</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2879,18 +3879,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Final Target</t>
+          <t>The Housemaid: An absolutely addictive psychological thriller with a jaw-dropping twist</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nora Roberts</t>
+          <t>Freida McFadden</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bookouture</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Hachette</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>26/04/2022</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2899,7 +3912,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Housemaid's Secret: A totally gripping psychological thriller with a shocking twist</t>
+          <t>The Coworker</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2907,10 +3920,23 @@
           <t>Freida McFadden</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Poisoned Pen Press</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>29/08/2023</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2979,18 +4005,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If You Laugh, I'm Starting This Book Over</t>
+          <t>Harry Potter and the Sorcerer's Stone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chris Harris</t>
+          <t>J.K. Rowling</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Scholastic Corporation</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>01/09/1998</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2999,18 +4038,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Lightning Thief: Percy Jackson and the Olympians: Book 1</t>
+          <t>Disney*Pixar Storybook Collection</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rick Riordan</t>
+          <t>Disney Press</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Disney Press</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>05/07/2011</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3019,18 +4071,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Frog and Toad Audio Collection: A Box Set of 3 Books From the Classic Animal Friendship and Adventure Series for Kids [ages 4-8] – A Heartwarming Caldecott and Newbery Honor Collection</t>
+          <t>Harry Potter and the Chamber of Secrets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arnold Lobel</t>
+          <t>J.K. Rowling</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>02/07/1998</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3039,18 +4104,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>How to Catch a Monster</t>
+          <t>The Lightning Thief: Percy Jackson and the Olympians: Book 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Adam Wallace</t>
+          <t>Rick Riordan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Miramax Books</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>28/06/2005</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3059,18 +4137,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pete the Cat and the Perfect Pizza Party</t>
+          <t>Frog and Toad Audio Collection: A Box Set of 3 Books From the Classic Animal Friendship and Adventure Series for Kids [ages 4-8] – A Heartwarming Caldecott and Newbery Honor Collection</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>James Dean, Kimberly Dean</t>
+          <t>Arnold Lobel</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>02/11/2004</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3079,18 +4170,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Beginner's Bible: Timeless Children's Stories</t>
+          <t>Walter the Whale Shark: And His Teeny Tiny Teeth</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Beginner's Bible</t>
+          <t>Katrine Crow</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Flowerpot Press</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>07/07/2020</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3099,18 +4203,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Warriors #1: Into the Wild: A Stunning Deluxe Edition of the Epic Beginning of the Warriors Cats Series</t>
+          <t>Harry Potter and the Prisoner of Azkaban</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Erin Hunter</t>
+          <t>J.K. Rowling</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>08/07/1999</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3119,18 +4236,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Miles the Brave</t>
+          <t>If You Laugh, I'm Starting This Book Over</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Storybutton, Mike Marshall, Steven Forbis</t>
+          <t>Chris Harris</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Little, Brown Books for Young Readers</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Hachette</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>27/09/2022</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3139,18 +4269,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KPop Demon Hunters: The Official Deluxe Junior Novelization: The Official Retelling</t>
+          <t>The Boxcar Children Collection Volume 1: The Boxcar Children, Surprise Island, Yellow House Mystery</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jessica Yoon</t>
+          <t>Gertrude Chandler Warner</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Rand McNally</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>01/01/1924</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3159,18 +4302,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Walter the Whale Shark: And His Teeny Tiny Teeth</t>
+          <t>The Lion, the Witch and the Wardrobe: Classic Fantasy Tale for Kids</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Katrine Crow</t>
+          <t>C. S. Lewis</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Geoffrey Bles</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>16/10/1950</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3239,18 +4395,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dear Therapist: I Can't Stand My Sister-in-Law</t>
+          <t>The Anxious Generation: How the Great Rewiring of Childhood Is Causing an Epidemic of Mental Illness</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lori Gottlieb, The Atlantic</t>
+          <t>Jonathan Haidt</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Penguin Press</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>26/03/2024</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3259,17 +4428,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Anxious Generation: How the Great Rewiring of Childhood Is Causing an Epidemic of Mental Illness</t>
+          <t>Things I Told My Notes App: The Funny And Candid Guide To Living Your Best Life From the Gen - Z Bridget Jones</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jonathan Haidt</t>
+          <t>Milly Goldsmith</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Transworld Publishers Ltd (Bantam Books)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
@@ -3284,13 +4463,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lindsay C. Gibson, PsyD</t>
+          <t>Lindsay C. Gibson PsyD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New Harbinger Publications</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>01/06/2015</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3307,10 +4499,23 @@
           <t>Michaeleen Doucleff</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Avid Reader Press</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>02/03/2021</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3319,17 +4524,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Tree with Matchmaking Powers</t>
+          <t>My Parent the Peacock: Discovery and Recovery from Narcissistic Parenting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jeff Maysh, The Atlantic</t>
+          <t>Kathleen Saxton</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sheldon Press</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
         </is>
       </c>
     </row>
@@ -3347,10 +4562,23 @@
           <t>Becky Kennedy</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Harper Wave</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>13/09/2022</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3359,17 +4587,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Expecting Better: Why the Conventional Pregnancy Wisdom Is Wrong--and What You Really Need to Know</t>
+          <t>How to Start: Discovering Your Life's Work</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emily Oster</t>
+          <t>Jodi Kantor</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -3379,7 +4617,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cribsheet: A Data-Driven Guide to Better, More Relaxed Parenting, from Birth to Preschool</t>
+          <t>Expecting Better: Why the Conventional Pregnancy Wisdom Is Wrong--and What You Really Need to Know</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3387,10 +4625,23 @@
           <t>Emily Oster</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Penguin Press</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>20/08/2013</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3399,18 +4650,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Seven Principles for Making Marriage Work: A Practical Guide from the Country’s Foremost Relationship Expert, Revised and Updated</t>
+          <t>Cribsheet: A Data-Driven Guide to Better, More Relaxed Parenting, from Birth to Preschool</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>John M. Gottman, PhD, Nan Silver</t>
+          <t>Emily Oster</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Penguin Press</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>09/04/2019</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3419,18 +4683,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Men with Adult ADHD: How to Raise Emotionally Intelligent Men and Improve Relationships</t>
+          <t>The Seven Principles for Making Marriage Work: A Practical Guide from the Country’s Foremost Relationship Expert, Revised and Updated</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Garth Zeus</t>
+          <t>John M. Gottman PhD, Nan Silver</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Harmony</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>01/01/1999</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3444,7 +4721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3507,10 +4784,23 @@
           <t>Yuval Noah Harari</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dvir Publishing House Ltd.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>01/01/2011</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3527,10 +4817,23 @@
           <t>Stephen Fry</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Michael Joseph</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>01/01/2017</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3539,18 +4842,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1929: Inside the Greatest Crash in Wall Street History--and How It Shattered a Nation</t>
+          <t>A People's History of the United States</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Andrew Ross Sorkin</t>
+          <t>Howard Zinn</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Harper &amp; Row</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>01/01/1980</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3559,18 +4875,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A People's History of the United States</t>
+          <t>Guns Up!: A Firsthand Account of the Vietnam War</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Howard Zinn</t>
+          <t>Johnnie Clark</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ballantine Books</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>01/01/1984</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3579,18 +4908,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Coming Storm: Power, Conflict, and Warnings from History</t>
+          <t>1929: Inside the Greatest Crash in Wall Street History--and How It Shattered a Nation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Odd Arne Westad</t>
+          <t>Andrew Ross Sorkin</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Viking Press</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3599,18 +4941,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>How to Hide an Empire: A History of the Greater United States</t>
+          <t>The Very Secret Sex Lives of Medieval Women: An Inside Look at Women &amp; Sex in Medieval Times</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Daniel Immerwahr</t>
+          <t>Rosalie Gilbert</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mango Publishing</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>27/10/2020</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3619,18 +4974,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Codename Nemo: The Hunt for a Nazi U-Boat and the Elusive Enigma Machine</t>
+          <t>Conspiracies of World War II: Devious Plots, Sinister Saboteurs and Extraordinary Enigmas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charles Lachman</t>
+          <t>Alexander Macdonald</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Arcturus Publishing</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>01/11/2023</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3639,18 +5007,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Very Secret Sex Lives of Medieval Women: An Inside Look at Women &amp; Sex in Medieval Times</t>
+          <t>The Third Reich: A History of Nazi Germany</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rosalie Gilbert</t>
+          <t>Thomas Childers</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>01/04/2017</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3659,37 +5040,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Empire of the Summer Moon: Quanah Parker and the Rise and Fall of the Comanches, the Most Powerful Indian Tribe in American History</t>
+          <t>The American Revolution: An Intimate History</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S. C. Gwynne</t>
+          <t>Geoffrey C. Ward, Ken Burns</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Knopf</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>The Third Reich: A History of Nazi Germany</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Thomas Childers</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
         </is>
       </c>
     </row>
@@ -3759,18 +5130,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Action Bible: God's Redemptive Story</t>
+          <t>How to Hold a Cockroach: A book for those who are free and don't know it</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Doug Mauss</t>
+          <t>Matthew Maxwell</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Hearthstone</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10/04/2020</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3779,18 +5163,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shaolin Spirit: The Way to Self-Mastery</t>
+          <t>Become What You Are</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Shi Heng Yi</t>
+          <t>Alan Watts</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Shambhala</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>01/01/1995</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3799,18 +5196,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>How to Hold a Cockroach: A book for those who are free and don't know it</t>
+          <t>The King James Bible</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Matthew Maxwell</t>
+          <t>Uncredited</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Robert Barker</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>01/01/1611</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3819,18 +5229,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The King James Bible</t>
+          <t>The Alchemist: A Modern Classic Fable of Spiritual Healing, Self-Discovery, and the Power of Dreams in a Visually Stunning Graphic Novel—Get Lost in the Pages of This Captivating Summer Read</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uncredited</t>
+          <t>Paulo Coelho</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HarperOne</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>01/11/2010</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3839,18 +5262,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Alchemist: A Modern Classic Fable of Spiritual Healing, Self-Discovery, and the Power of Dreams in a Visually Stunning Graphic Novel—Get Lost in the Pages of This Captivating Summer Read</t>
+          <t>The Action Bible: God's Redemptive Story</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paulo Coelho</t>
+          <t>Doug Mauss</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>David C Cook</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>01/01/2010</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3859,17 +5295,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Become What You Are</t>
+          <t>Stand Firm and Act Like Men: Becoming the Man You Were Created to Be Instead of Who the World Says You Are</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alan Watts</t>
+          <t>Joby Martin, Charles Martin</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Hachette Nashville</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
         </is>
       </c>
     </row>
@@ -3887,10 +5333,23 @@
           <t>Zondervan</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Zondervan</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>03/11/2015</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3907,10 +5366,23 @@
           <t>C. S. Lewis</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Geoffrey Bles</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>07/07/1952</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3927,10 +5399,23 @@
           <t>Don Miguel Ruiz, Janet Mills</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Amber-Allen Publishing</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>01/01/1997</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3939,18 +5424,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stand Firm and Act Like Men: Becoming the Man You Were Created to Be Instead of Who the World Says You Are</t>
+          <t>Becoming Supernatural: How Common People Are Doing The Uncommon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Joby Martin, Charles Martin</t>
+          <t>Dr. Joe Dispenza</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Hay House</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>05/03/2019</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4027,10 +5525,23 @@
           <t>Sarah J. Maas</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bloomsbury Publishing</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>05/05/2015</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -4047,10 +5558,23 @@
           <t>Sarah J. Maas</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bloomsbury Publishing</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>03/05/2016</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4059,18 +5583,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Twilight</t>
+          <t>The Summer I Turned Pretty</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Stephenie Meyer</t>
+          <t>Jenny Han</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Simon &amp; Schuster Books for Young Readers</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>05/05/2009</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -4079,18 +5616,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Summer I Turned Pretty</t>
+          <t>Twilight</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jenny Han</t>
+          <t>Stephenie Meyer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Hachette</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>01/09/2005</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -4099,17 +5649,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Midnight Sun</t>
+          <t>True Paranormal Stories: 10 Real Encounters You'll Never Forget</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Stephenie Meyer</t>
+          <t>Scary Studios</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -4119,18 +5674,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Summer of Second Chances</t>
+          <t>Midnight Sun</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>K. L. Walther</t>
+          <t>Stephenie Meyer</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Hachette</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>04/08/2020</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -4139,18 +5707,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lord of the Flies</t>
+          <t>Harry Potter and the Goblet of Fire</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>William Golding</t>
+          <t>J.K. Rowling</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Bloomsbury</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>08/07/2000</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -4159,18 +5740,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Better Than the Movies</t>
+          <t>Girls Like Girls</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lynn Painter</t>
+          <t>Hayley Kiyoko</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Wednesday Books</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>30/05/2023</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -4179,18 +5773,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eragon: Inheritance, Book I</t>
+          <t>Better Than the Movies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Christopher Paolini</t>
+          <t>Lynn Painter</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>04/05/2021</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4199,18 +5806,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A Good Girl's Guide to Murder</t>
+          <t>Eragon: Inheritance, Book I</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Holly Jackson</t>
+          <t>Christopher Paolini</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Paolini International Publishing</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>01/01/2002</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/audiobooks.xlsx
+++ b/audiobooks.xlsx
@@ -749,7 +749,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01/09/2020</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,27 +762,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>How to Talk to Anyone and Be More Charismatic: Improve Communication &amp; People Skills, Master Small Talk, Build Confidence &amp; Influence, Overcome Social Anxiety, and Make Friends in Any Conversation</t>
+          <t>Never Split the Difference: Unlock Your Persuasion Potential in Professional and Personal Life</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nathan Soren</t>
+          <t>Chris Voss, Tahl Raz</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nathan Soren</t>
+          <t>Harper Business</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>17/05/2016</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -795,27 +795,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Never Split the Difference: Unlock Your Persuasion Potential in Professional and Personal Life</t>
+          <t>Unreasonable Hospitality: The Remarkable Power of Giving People More Than They Expect</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chris Voss, Tahl Raz</t>
+          <t>Will Guidara</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Harper Business</t>
+          <t>Optimism Press</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17/05/2016</t>
+          <t>25/10/2022</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -828,17 +828,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unreasonable Hospitality: The Remarkable Power of Giving People More Than They Expect</t>
+          <t>How to Talk to Anyone and Be More Charismatic: Improve Communication &amp; People Skills, Master Small Talk, Build Confidence &amp; Influence, Overcome Social Anxiety, and Make Friends in Any Conversation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Will Guidara</t>
+          <t>Nathan Soren</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Optimism Press</t>
+          <t>Nathan Soren</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25/10/2022</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -894,17 +894,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Speak Like a CEO: How to Speak with Power, Lead with Clarity, and Command Any Room Without Saying a Word Too Much</t>
+          <t>Think and Grow Rich! The Original Version, Restored and Revised</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CALDER MP KNOX</t>
+          <t>Napoleon Hill, Ross Cornwell</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>McGraw-Hill Companies</t>
+          <t>The Ralston Society</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31/03/2005</t>
+          <t>01/03/1937</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -937,7 +937,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Free Press</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Millionaire Mindset and Habits for Success</t>
+          <t>Think and Grow Rich</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M.A. Myers</t>
+          <t>Napoleon Hill</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Author's Republic</t>
+          <t>The Ralston Society</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19/01/2022</t>
+          <t>01/01/1937</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -993,31 +993,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Think and Grow Rich! The Original Version, Restored and Revised</t>
+          <t>Speak Like a CEO: How to Speak with Power, Lead with Clarity, and Command Any Room Without Saying a Word Too Much</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Napoleon Hill, Ross Cornwell</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>The Ralston Society</t>
+          <t>CALDER MP KNOX</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>01/03/1937</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1026,17 +1013,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Think and Grow Rich</t>
+          <t>Millionaire Mindset and Habits for Success</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Napoleon Hill</t>
+          <t>M.A. Myers</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>The Ralston Society</t>
+          <t>Author's Republic</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1046,7 +1033,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01/03/1937</t>
+          <t>01/10/2022</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1149,31 +1136,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I'm Glad My Mom Died</t>
+          <t>Joyful, Anyway</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jennette McCurdy</t>
+          <t>Kate Bowler</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>The Dial Press</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>09/08/2022</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
+          <t>07/04/2026</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1212,27 +1196,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kitchen Confidential: Adventures in the Culinary Underbelly</t>
+          <t>I'm Glad My Mom Died</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Anthony Bourdain, Irvine Welsh</t>
+          <t>Jennette McCurdy</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bloomsbury Publishing</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01/08/2000</t>
+          <t>09/08/2022</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1245,28 +1229,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>This Is Me: A Reckoning</t>
+          <t>Kitchen Confidential: Adventures in the Culinary Underbelly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hayden Panettiere</t>
+          <t>Anthony Bourdain, Irvine Welsh</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Grand Central Publishing</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
-        </is>
+          <t>01/01/2000</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1305,27 +1292,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Make-Believe: A Memoir of Magic and Madness</t>
+          <t>This Is Me: A Reckoning</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hannah Murray</t>
+          <t>Hayden Panettiere</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The Dial Press</t>
+          <t>Grand Central Publishing</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
     </row>
@@ -1335,28 +1322,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Start With Yourself: A New Vision for Work &amp; Life</t>
+          <t>Wild Rescues: A Paramedic’s Extreme Adventures in Yosemite, Yellowstone, and Grand Teton</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emma Grede</t>
+          <t>Kevin Grange</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Avid Reader Press/Simon &amp; Schuster</t>
+          <t>Chicago Review Press</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
-        </is>
+          <t>06/04/2021</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1365,31 +1355,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wild Rescues: A Paramedic’s Extreme Adventures in Yosemite, Yellowstone, and Grand Teton</t>
+          <t>Start With Yourself: A New Vision for Work &amp; Life</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kevin Grange</t>
+          <t>Emma Grede</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Chicago Review Press</t>
+          <t>Avid Reader Press/Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/03/2021</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
+          <t>14/04/2026</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1534,7 +1521,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Red Tower Books</t>
+          <t>Red Tower Books (Entangled Publishing)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1590,27 +1577,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Throne of Glass</t>
+          <t>A Game of Thrones: A Song of Ice and Fire: Book One</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>George R. R. Martin</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bloomsbury Publishing</t>
+          <t>Bantam Spectra</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>02/08/2012</t>
+          <t>01/08/1996</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1623,31 +1610,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A Game of Thrones: A Song of Ice and Fire: Book One</t>
+          <t>True Paranormal Stories From Cops</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>George R. R. Martin</t>
+          <t>Scary Studios</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bantam Spectra</t>
+          <t>Scary Studios</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01/08/1996</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+          <t>07/07/2026</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A Court of Wings and Ruin</t>
+          <t>Throne of Glass</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1676,7 +1660,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>02/05/2017</t>
+          <t>02/08/2012</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1689,7 +1673,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Heir of Fire</t>
+          <t>A Court of Wings and Ruin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1699,7 +1683,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bloomsbury YA</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1709,7 +1693,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>02/09/2014</t>
+          <t>02/05/2017</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1722,27 +1706,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Iron Flame</t>
+          <t>Heir of Fire</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rebecca Yarros</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Red Tower Books (Entangled Publishing)</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07/11/2023</t>
+          <t>02/09/2014</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1755,17 +1739,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>True Paranormal Stories From Cops</t>
+          <t>Iron Flame</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Scary Studios</t>
+          <t>Rebecca Yarros</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Scary Studios</t>
+          <t>Red Tower Books (Entangled Publishing)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1775,8 +1759,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
-        </is>
+          <t>07/11/2023</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1805,7 +1792,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01/08/2013</t>
+          <t>15/08/2013</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1888,7 +1875,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Marieme Seck</t>
+          <t>Pck;</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1898,10 +1885,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>25/01/2025</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1942,17 +1931,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mastering Conversation Skills Goodbye Awkwardness. Learn to Master the Art of Conversation and Become A Great Communicator, Even if You've Always Been Shy or Hate Small Talk</t>
+          <t>Detached: How to Let Go, Heal, and Become Irresistible</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Helen Stone</t>
+          <t>Sabrina Alexis Bendory</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Author's Republic</t>
+          <t>Thought Catalog Books</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1962,12 +1951,10 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31/03/2020</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1975,17 +1962,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Detached: How to Let Go, Heal, and Become Irresistible</t>
+          <t>Mastering Conversation Skills Goodbye Awkwardness. Learn to Master the Art of Conversation and Become A Great Communicator, Even if You've Always Been Shy or Hate Small Talk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sabrina Alexis Bendory</t>
+          <t>Helen Stone</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Thought Catalog Books</t>
+          <t>Author's Republic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1995,10 +1982,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>01/03/2020</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2006,30 +1995,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dealing with Feeling: Use Your Emotions to Create the Life You Want</t>
+          <t>The Subtle Art of Not Giving a F*ck: A Counterintuitive Approach to Living a Good Life</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Marc Brackett Ph.D.</t>
+          <t>Mark Manson</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Celadon Books</t>
+          <t>HarperOne</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>13/09/2016</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2037,27 +2028,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Subtle Art of Not Giving a F*ck: A Counterintuitive Approach to Living a Good Life</t>
+          <t>The Mountain is You: Transforming Self-Sabotage Into Self-Mastery</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mark Manson</t>
+          <t>Brianna Wiest</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HarperOne</t>
+          <t>Thought Catalog Books</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13/09/2016</t>
+          <t>28/05/2020</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2070,32 +2061,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Self Discipline: Develop Everlasting Habits to Master Self-Control, Productivity, Mental Toughness, and a Spartan Mindset for Creating a Life of Success to Beat Addiction, Procrastination, &amp; Laziness</t>
+          <t>How to Not Die in Prison: A Survival Guide</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Steve G. Martin</t>
+          <t>Taylor Sheridan, Tom Nelson</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GA Publishing</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>26/02/2022</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2103,30 +2092,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>How to Not Die in Prison: A Survival Guide</t>
+          <t>12 Laws of the Universe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Taylor Sheridan, Tom Nelson</t>
+          <t>Manhardeep Singh</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independently published</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>20/10/2021</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2134,7 +2125,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12 Laws of the Universe</t>
+          <t>Law of Attraction: Secrets to manifesting more of what you want and less of what you don't</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2144,7 +2135,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Independently published</t>
+          <t>Echo Point Books &amp; Media, LLC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2154,7 +2145,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20/10/2021</t>
+          <t>21/01/2025</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2167,17 +2158,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Mountain is You: Transforming Self-Sabotage Into Self-Mastery</t>
+          <t>Sex So Great She Can't Get Enough</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brianna Wiest</t>
+          <t>Barbara Keesling PhD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Thought Catalog Books</t>
+          <t>M. Evans &amp; Company</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2187,7 +2178,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2323,27 +2314,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Famesick: A Memoir</t>
+          <t>Cancel Me If You Can</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lena Dunham</t>
+          <t>Dave Portnoy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Random House</t>
+          <t>Gallery Books</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -2353,27 +2344,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cancel Me If You Can</t>
+          <t>Famesick: A Memoir</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dave Portnoy</t>
+          <t>Lena Dunham</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gallery Books</t>
+          <t>Random House</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -2391,19 +2382,9 @@
           <t>Marieme Seck</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Marieme Seck</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
     </row>
@@ -2413,27 +2394,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Regime Change: Inside the Imperial Presidency of Donald Trump</t>
+          <t>Theo of Golden: A Novel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Maggie Haberman, Jonathan Swan</t>
+          <t>Allen Levi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Atria Books</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Simon &amp; Schuster</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>03/10/2025</t>
         </is>
       </c>
     </row>
@@ -2443,31 +2424,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Theo of Golden: A Novel</t>
+          <t>The Calamity Club: A Novel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Allen Levi</t>
+          <t>Kathryn Stockett</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Atria Books</t>
+          <t>Spiegel &amp; Grau</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
+          <t>05/05/2026</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -2476,27 +2454,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Calamity Club: A Novel</t>
+          <t>Regime Change: Inside the Imperial Presidency of Donald Trump</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kathryn Stockett</t>
+          <t>Maggie Haberman, Jonathan Swan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Spiegel &amp; Grau</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -2569,28 +2547,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Strangers: A Memoir of Marriage</t>
+          <t>Lights Out: An Into Darkness Novel</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Belle Burden</t>
+          <t>Navessa Allen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dial Press</t>
+          <t>Zando</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
-        </is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2599,31 +2580,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lights Out: An Into Darkness Novel</t>
+          <t>Strangers: A Memoir of Marriage</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
+          <t>Belle Burden</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Slowburn</t>
+          <t>Dial Press</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06/08/2024</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
+          <t>13/01/2026</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -2665,28 +2643,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dear Debbie</t>
+          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
+          <t>James Clear</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Poisoned Pen Press</t>
+          <t>Avery Publishing</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
-        </is>
+          <t>16/10/2018</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2695,27 +2676,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
+          <t>How to Hold a Cockroach: A book for those who are free and don't know it</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>James Clear</t>
+          <t>Matthew Maxwell</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Avery Publishing</t>
+          <t>Hearthstone</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>16/10/2018</t>
+          <t>10/04/2020</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2728,31 +2709,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Remarkably Bright Creatures: A Read with Jenna Pick</t>
+          <t>Dear Debbie</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shelby Van Pelt</t>
+          <t>Freida McFadden</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ecco Press</t>
+          <t>Poisoned Pen Press</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>01/05/2022</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
+          <t>27/01/2026</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -2761,27 +2739,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>How to Hold a Cockroach: A book for those who are free and don't know it</t>
+          <t>Remarkably Bright Creatures: A Read with Jenna Pick</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Matthew Maxwell</t>
+          <t>Shelby Van Pelt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hearthstone</t>
+          <t>Ecco Press</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10/04/2020</t>
+          <t>03/05/2022</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2794,31 +2772,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Every Summer After</t>
+          <t>Claude AI for Beginners: How to Use Claude to Write Better, Research Faster, and Boost Productivity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Carley Fortune</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Berkley Books</t>
+          <t>Nicholas Hunter</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>10/05/2022</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -2827,17 +2792,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Our Perfect Storm</t>
+          <t>Joyful, Anyway</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Carley Fortune</t>
+          <t>Kate Bowler</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Penguin Publishing Group</t>
+          <t>The Dial Press</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2847,7 +2812,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -2857,27 +2822,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fourth Wing</t>
+          <t>Every Summer After</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rebecca Yarros</t>
+          <t>Carley Fortune</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Red Tower Books</t>
+          <t>Berkley Books</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>02/05/2023</t>
+          <t>10/05/2022</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2923,27 +2888,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Correspondent: A Novel</t>
+          <t>Harry Potter and the Chamber of Secrets</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Virginia Evans</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Crown</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>29/04/2025</t>
+          <t>02/07/1998</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2956,17 +2921,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mastering Conversation Skills Goodbye Awkwardness. Learn to Master the Art of Conversation and Become A Great Communicator, Even if You've Always Been Shy or Hate Small Talk</t>
+          <t>Fourth Wing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Helen Stone</t>
+          <t>Rebecca Yarros</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Author's Republic</t>
+          <t>Red Tower Books (Entangled Publishing)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2976,7 +2941,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>31/03/2020</t>
+          <t>02/05/2023</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2989,28 +2954,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Night We Met</t>
+          <t>The Correspondent: A Novel</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Abby Jimenez</t>
+          <t>Virginia Evans</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Forever</t>
+          <t>Crown Publishing Group</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
-        </is>
+          <t>29/04/2025</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -3019,17 +2987,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Claude AI for Beginners: How to Use Claude to Write Better, Research Faster, and Boost Productivity</t>
+          <t>Nobody Knows You're Here: A Psychological Suspense Thriller</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nicholas Hunter</t>
+          <t>Bryn Greenwood</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Podium Publishing</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
         </is>
       </c>
     </row>
@@ -3039,27 +3017,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nobody Knows You're Here: A Psychological Suspense Thriller</t>
+          <t>Our Perfect Storm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bryn Greenwood</t>
+          <t>Carley Fortune</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Podium Publishing</t>
+          <t>Berkley Books</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -3069,28 +3047,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Game On: An Into Darkness Novel</t>
+          <t>Red Rising</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
+          <t>Pierce Brown</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Slowburn</t>
+          <t>Del Rey Books</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
-        </is>
+          <t>28/01/2014</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3099,27 +3080,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Whistler: A Novel</t>
+          <t>The Night We Met</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ann Patchett</t>
+          <t>Abby Jimenez</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Forever</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>24/03/2026</t>
         </is>
       </c>
     </row>
@@ -3129,31 +3110,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Red Rising</t>
+          <t>Whistler: A Novel</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pierce Brown</t>
+          <t>Ann Patchett</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Del Rey Books</t>
+          <t>Harper</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>28/01/2014</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>1</v>
+          <t>02/06/2026</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -3162,31 +3140,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Throne of Glass</t>
+          <t>Dolly All the Time: A GMA Book Club Pick</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>Annabel Monaghan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Bloomsbury Publishing</t>
+          <t>G.P. Putnam's Sons</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>02/08/2012</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
+          <t>26/05/2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3265,7 +3240,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Slowburn</t>
+          <t>Zando</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3275,7 +3250,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>06/08/2024</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -3361,7 +3336,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Crown</t>
+          <t>Crown Publishing Group (NY)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3391,7 +3366,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Flatiron Books</t>
+          <t>Flatiron Books: Pine &amp; Cedar</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3444,28 +3419,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Into the Blue: Reese's Book Club: A Love Story</t>
+          <t>The Seven Husbands of Evelyn Hugo: A Novel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emma Brodie</t>
+          <t>Taylor Jenkins Reid</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ballantine Books</t>
+          <t>Atria Books</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
-        </is>
+          <t>13/06/2017</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3474,31 +3452,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Seven Husbands of Evelyn Hugo: A Novel</t>
+          <t>Into the Blue: Reese's Book Club: A Love Story</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Taylor Jenkins Reid</t>
+          <t>Emma Brodie</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Atria Books</t>
+          <t>Ballantine Books</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13/06/2017</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
+          <t>07/04/2026</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -3517,7 +3492,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Zando – Slowburn</t>
+          <t>Zando - Slowburn</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3550,7 +3525,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Independently Published</t>
+          <t>Self-published</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3560,7 +3535,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>03/06/2024</t>
+          <t>04/06/2024</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3783,31 +3758,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Asylum Confessions: Deathbed Confessions of the Criminally Insane</t>
+          <t>The Fourth Option: A Novel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jack Steen</t>
+          <t>Jack Carr, M.P. Woodward</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Deathbed Publishing</t>
+          <t>Atria/Emily Bestler Books</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10/03/2021</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
+          <t>12/05/2026</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -3816,28 +3788,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nine Lives: A Novel</t>
+          <t>The Asylum Confessions: Deathbed Confessions of the Criminally Insane</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Catherine Steadman</t>
+          <t>Jack Steen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bantam</t>
+          <t>Deathbed Publishing</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
-        </is>
+          <t>01/08/2020</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3846,31 +3821,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Silent Patient</t>
+          <t>Judge Stone: A Novel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alex Michaelides</t>
+          <t>James Patterson, Viola Davis</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Celadon Books</t>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>05/02/2019</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
+          <t>09/03/2026</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -3879,31 +3851,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Housemaid: An absolutely addictive psychological thriller with a jaw-dropping twist</t>
+          <t>Nine Lives: A Novel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
+          <t>Catherine Steadman</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bookouture</t>
+          <t>Bantam</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>26/04/2022</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
+          <t>23/06/2026</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -3912,17 +3881,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Coworker</t>
+          <t>The Silent Patient</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
+          <t>Alex Michaelides</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Poisoned Pen Press</t>
+          <t>Celadon Books</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3932,7 +3901,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29/08/2023</t>
+          <t>05/02/2019</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4038,27 +4007,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Disney*Pixar Storybook Collection</t>
+          <t>Harry Potter and the Chamber of Secrets</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Disney Press</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Disney Press</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>05/07/2011</t>
+          <t>02/07/1998</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -4071,27 +4040,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Harry Potter and the Chamber of Secrets</t>
+          <t>Disney*Pixar Storybook Collection</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>J.K. Rowling</t>
+          <t>Disney Press</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Disney Press</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>02/07/1998</t>
+          <t>01/01/2006</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -4104,27 +4073,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Lightning Thief: Percy Jackson and the Olympians: Book 1</t>
+          <t>Harry Potter and the Prisoner of Azkaban</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rick Riordan</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Miramax Books</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28/06/2005</t>
+          <t>08/07/1999</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -4170,17 +4139,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Walter the Whale Shark: And His Teeny Tiny Teeth</t>
+          <t>The Lightning Thief: Percy Jackson and the Olympians: Book 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Katrine Crow</t>
+          <t>Rick Riordan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Flowerpot Press</t>
+          <t>Miramax Books</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4190,7 +4159,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>07/07/2020</t>
+          <t>28/06/2005</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -4203,27 +4172,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Harry Potter and the Prisoner of Azkaban</t>
+          <t>The Story of Moana: A Tale of Courage and Adventure</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>J.K. Rowling</t>
+          <t>Kari Sutherland</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Disney Press</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>08/07/1999</t>
+          <t>11/10/2016</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4236,27 +4205,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>If You Laugh, I'm Starting This Book Over</t>
+          <t>The Boxcar Children Collection Volume 1: The Boxcar Children, Surprise Island, Yellow House Mystery</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chris Harris</t>
+          <t>Gertrude Chandler Warner</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Little, Brown Books for Young Readers</t>
+          <t>Rand McNally</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>27/09/2022</t>
+          <t>01/01/1924</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4269,17 +4238,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Boxcar Children Collection Volume 1: The Boxcar Children, Surprise Island, Yellow House Mystery</t>
+          <t>How to Catch a Mermaid</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gertrude Chandler Warner</t>
+          <t>Adam Wallace</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rand McNally</t>
+          <t>Sourcebooks Wonderland</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4289,7 +4258,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/01/1924</t>
+          <t>17/07/2018</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4428,28 +4397,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Things I Told My Notes App: The Funny And Candid Guide To Living Your Best Life From the Gen - Z Bridget Jones</t>
+          <t>Adult Children of Emotionally Immature Parents: How to Heal from Distant, Rejecting, or Self-Involved Parents</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Milly Goldsmith</t>
+          <t>Lindsay C. Gibson PsyD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Transworld Publishers Ltd (Bantam Books)</t>
+          <t>New Harbinger Publications</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
-        </is>
+          <t>01/06/2015</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4458,27 +4430,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Adult Children of Emotionally Immature Parents: How to Heal from Distant, Rejecting, or Self-Involved Parents</t>
+          <t>Hunt, Gather, Parent: What Ancient Cultures Can Teach Us About the Lost Art of Raising Happy, Helpful Little Humans</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lindsay C. Gibson PsyD</t>
+          <t>Michaeleen Doucleff</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>New Harbinger Publications</t>
+          <t>Avid Reader Press / Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/06/2015</t>
+          <t>01/03/2021</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -4491,31 +4463,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hunt, Gather, Parent: What Ancient Cultures Can Teach Us About the Lost Art of Raising Happy, Helpful Little Humans</t>
+          <t>Things I Told My Notes App: The Funny And Candid Guide To Living Your Best Life From the Gen - Z Bridget Jones</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Michaeleen Doucleff</t>
+          <t>Milly Goldsmith</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Avid Reader Press</t>
+          <t>Bantam</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>02/03/2021</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+          <t>25/06/2026</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4524,28 +4493,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>My Parent the Peacock: Discovery and Recovery from Narcissistic Parenting</t>
+          <t>Good Inside: A Practical Guide to Resilient Parenting Prioritizing Connection Over Correction</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kathleen Saxton</t>
+          <t>Becky Kennedy</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sheldon Press</t>
+          <t>Harper Wave</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
-        </is>
+          <t>13/09/2022</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -4554,27 +4526,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Good Inside: A Practical Guide to Resilient Parenting Prioritizing Connection Over Correction</t>
+          <t>Expecting Better: Why the Conventional Pregnancy Wisdom Is Wrong--and What You Really Need to Know</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Becky Kennedy</t>
+          <t>Emily Oster</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Harper Wave</t>
+          <t>Penguin Books</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13/09/2022</t>
+          <t>20/08/2013</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -4587,27 +4559,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>How to Start: Discovering Your Life's Work</t>
+          <t>Dear Therapist: I Can't Stand My Sister-in-Law</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jodi Kantor</t>
+          <t>Lori Gottlieb, The Atlantic</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Little, Brown and Company</t>
+          <t>The Atlantic</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4584,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Expecting Better: Why the Conventional Pregnancy Wisdom Is Wrong--and What You Really Need to Know</t>
+          <t>Cribsheet: A Data-Driven Guide to Better, More Relaxed Parenting, from Birth to Preschool</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4627,7 +4594,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Penguin Press</t>
+          <t>Penguin Books</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4637,7 +4604,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20/08/2013</t>
+          <t>21/04/2020</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4650,27 +4617,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cribsheet: A Data-Driven Guide to Better, More Relaxed Parenting, from Birth to Preschool</t>
+          <t>What If Friendship, Not Marriage, Was at the Center of Life?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Emily Oster</t>
+          <t>Rhaina Cohen, The Atlantic</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Penguin Press</t>
+          <t>The Atlantic</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>09/04/2019</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4786,7 +4753,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Dvir Publishing House Ltd.</t>
+          <t>Harvill Secker</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4796,7 +4763,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01/01/2011</t>
+          <t>04/09/2014</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -4809,17 +4776,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mythos</t>
+          <t>Sisters of Scandal: Mind-blowing tales of history's boldest and baddest women</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Stephen Fry</t>
+          <t>Ainslie Harvey</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Michael Joseph</t>
+          <t>Affirm Press</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4829,11 +4796,8 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
+          <t>25/11/2025</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -4842,27 +4806,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A People's History of the United States</t>
+          <t>Mythos</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Howard Zinn</t>
+          <t>Stephen Fry</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Harper &amp; Row</t>
+          <t>Michael Joseph</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/01/1980</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -4875,27 +4839,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Guns Up!: A Firsthand Account of the Vietnam War</t>
+          <t>The Third Reich: A History of Nazi Germany</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Johnnie Clark</t>
+          <t>Thomas Childers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ballantine Books</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01/01/1984</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -4908,31 +4872,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1929: Inside the Greatest Crash in Wall Street History--and How It Shattered a Nation</t>
+          <t>The Finest Hotel in Kabul: A People's History of Afghanistan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Andrew Ross Sorkin</t>
+          <t>Lyse Doucet</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Viking Press</t>
+          <t>Allen Lane</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+          <t>04/11/2025</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4941,27 +4902,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Very Secret Sex Lives of Medieval Women: An Inside Look at Women &amp; Sex in Medieval Times</t>
+          <t>A People's History of the United States</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rosalie Gilbert</t>
+          <t>Howard Zinn</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mango Publishing</t>
+          <t>Harper &amp; Row</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27/10/2020</t>
+          <t>01/01/1980</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -4974,17 +4935,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Conspiracies of World War II: Devious Plots, Sinister Saboteurs and Extraordinary Enigmas</t>
+          <t>Odyssey: The Greek Myths Reimagined</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alexander Macdonald</t>
+          <t>Stephen Fry</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Arcturus Publishing</t>
+          <t>Michael Joseph</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4994,7 +4955,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/11/2023</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -5007,27 +4968,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Third Reich: A History of Nazi Germany</t>
+          <t>Guns Up!: A Firsthand Account of the Vietnam War</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thomas Childers</t>
+          <t>Johnnie Clark</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Ballantine Books</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/04/2017</t>
+          <t>12/06/1984</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -5040,17 +5001,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The American Revolution: An Intimate History</t>
+          <t>1929: Inside the Greatest Crash in Wall Street History--and How It Shattered a Nation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Geoffrey C. Ward, Ken Burns</t>
+          <t>Andrew Ross Sorkin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Knopf</t>
+          <t>Viking Press</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5060,7 +5021,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5144,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01/01/1995</t>
+          <t>01/07/1995</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -5249,7 +5210,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01/11/2010</t>
+          <t>01/01/2010</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -5262,27 +5223,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Action Bible: God's Redemptive Story</t>
+          <t>NIV Listener's Audio Bible: Complete Bible: Vocal Performance by Max McLean</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Doug Mauss</t>
+          <t>Zondervan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>David C Cook</t>
+          <t>Zondervan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01/01/2010</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -5305,7 +5266,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hachette Nashville</t>
+          <t>Faithwords</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5325,27 +5286,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NIV Listener's Audio Bible: Complete Bible: Vocal Performance by Max McLean</t>
+          <t>Mere Christianity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Zondervan</t>
+          <t>C. S. Lewis</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zondervan</t>
+          <t>Geoffrey Bles</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>03/11/2015</t>
+          <t>07/07/1952</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -5358,17 +5319,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mere Christianity</t>
+          <t>The Four Agreements: A Practical Guide to Personal Freedom</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C. S. Lewis</t>
+          <t>Don Miguel Ruiz, Janet Mills</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Geoffrey Bles</t>
+          <t>Amber-Allen Publishing</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5378,7 +5339,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07/07/1952</t>
+          <t>01/01/1997</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -5391,17 +5352,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Four Agreements: A Practical Guide to Personal Freedom</t>
+          <t>The Book of Enoch</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Don Miguel Ruiz, Janet Mills</t>
+          <t>George Schodde</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Amber-Allen Publishing</t>
+          <t>W. F. Draper</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5411,7 +5372,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/01/1997</t>
+          <t>01/01/1882</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -5583,27 +5544,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Summer I Turned Pretty</t>
+          <t>Harry Potter and the Goblet of Fire</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jenny Han</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster Books for Young Readers</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>05/05/2009</t>
+          <t>08/07/2000</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -5616,27 +5577,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Twilight</t>
+          <t>The Summer I Turned Pretty</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Stephenie Meyer</t>
+          <t>Jenny Han</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Little, Brown and Company</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01/09/2005</t>
+          <t>05/05/2009</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -5649,23 +5610,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>True Paranormal Stories: 10 Real Encounters You'll Never Forget</t>
+          <t>Twilight</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scary Studios</t>
+          <t>Stephenie Meyer</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
-        </is>
+          <t>05/10/2005</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -5674,27 +5643,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Midnight Sun</t>
+          <t>Harry Potter and the Order of the Phoenix</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Stephenie Meyer</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Little, Brown and Company</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>04/08/2020</t>
+          <t>21/06/2003</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -5707,31 +5676,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Harry Potter and the Goblet of Fire</t>
+          <t>True Paranormal Stories: 10 Real Encounters You'll Never Forget</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>J.K. Rowling</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Bloomsbury</t>
+          <t>Scary Studios</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>08/07/2000</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -5740,27 +5696,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Girls Like Girls</t>
+          <t>Midnight Sun</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hayley Kiyoko</t>
+          <t>Stephenie Meyer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wednesday Books</t>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30/05/2023</t>
+          <t>04/08/2020</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -5806,27 +5762,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eragon: Inheritance, Book I</t>
+          <t>Harry Potter and the Half-Blood Prince</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christopher Paolini</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paolini International Publishing</t>
+          <t>Bloomsbury (UK) and Scholastic (US)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01/01/2002</t>
+          <t>16/07/2005</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/audiobooks.xlsx
+++ b/audiobooks.xlsx
@@ -749,7 +749,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>08/09/2020</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,31 +762,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Never Split the Difference: Unlock Your Persuasion Potential in Professional and Personal Life</t>
+          <t>Disrupt Everything—and Win: Take Control of Your Future</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chris Voss, Tahl Raz</t>
+          <t>James Patterson, Patrick Leddin PhD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Harper Business</t>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17/05/2016</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
+          <t>29/09/2025</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -795,27 +792,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unreasonable Hospitality: The Remarkable Power of Giving People More Than They Expect</t>
+          <t>Never Split the Difference: Unlock Your Persuasion Potential in Professional and Personal Life</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Will Guidara</t>
+          <t>Chris Voss, Tahl Raz</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Optimism Press</t>
+          <t>Harper Business</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25/10/2022</t>
+          <t>17/05/2016</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -828,27 +825,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>How to Talk to Anyone and Be More Charismatic: Improve Communication &amp; People Skills, Master Small Talk, Build Confidence &amp; Influence, Overcome Social Anxiety, and Make Friends in Any Conversation</t>
+          <t>Extreme Ownership: How U.S. Navy SEALs Lead and Win</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nathan Soren</t>
+          <t>Jocko Willink, Leif Babin</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nathan Soren</t>
+          <t>St. Martin's Press</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>20/10/2015</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -861,27 +858,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Extreme Ownership: How U.S. Navy SEALs Lead and Win</t>
+          <t>Unreasonable Hospitality: The Remarkable Power of Giving People More Than They Expect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jocko Willink, Leif Babin</t>
+          <t>Will Guidara</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>St. Martin's Press</t>
+          <t>Optimism Press</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20/10/2015</t>
+          <t>25/10/2022</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -894,17 +891,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Think and Grow Rich! The Original Version, Restored and Revised</t>
+          <t>How to Talk to Anyone and Be More Charismatic: Improve Communication &amp; People Skills, Master Small Talk, Build Confidence &amp; Influence, Overcome Social Anxiety, and Make Friends in Any Conversation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Napoleon Hill, Ross Cornwell</t>
+          <t>Nathan Soren</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The Ralston Society</t>
+          <t>Nathan Soren</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -914,7 +911,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01/03/1937</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -927,27 +924,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The 7 Habits of Highly Effective People: 30th Anniversary Edition</t>
+          <t>Speak Like a CEO: How to Speak with Power, Lead with Clarity, and Command Any Room Without Saying a Word Too Much</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stephen R. Covey, Sean Covey</t>
+          <t>CALDER MP KNOX</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>McGraw-Hill Companies</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/01/1989</t>
+          <t>01/04/2005</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -960,27 +957,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Think and Grow Rich</t>
+          <t>The 7 Habits of Highly Effective People: 30th Anniversary Edition</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Napoleon Hill</t>
+          <t>Stephen R. Covey, Sean Covey</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The Ralston Society</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/01/1937</t>
+          <t>01/01/1989</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -993,18 +990,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Speak Like a CEO: How to Speak with Power, Lead with Clarity, and Command Any Room Without Saying a Word Too Much</t>
+          <t>Millionaire Mindset and Habits for Success</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CALDER MP KNOX</t>
+          <t>M.A. Myers</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Author's Republic</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>24/10/2022</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1013,17 +1023,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Millionaire Mindset and Habits for Success</t>
+          <t>Think and Grow Rich</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M.A. Myers</t>
+          <t>Napoleon Hill</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Author's Republic</t>
+          <t>The Ralston Society</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1033,7 +1043,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01/10/2022</t>
+          <t>01/03/1937</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1136,28 +1146,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Joyful, Anyway</t>
+          <t>I'm Glad My Mom Died</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kate Bowler</t>
+          <t>Jennette McCurdy</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The Dial Press</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
-        </is>
+          <t>09/08/2022</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1186,7 +1199,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
     </row>
@@ -1196,27 +1209,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>I'm Glad My Mom Died</t>
+          <t>The Woman in Me</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jennette McCurdy</t>
+          <t>Britney Spears</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Gallery Books</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Simon &amp; Schuster</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>09/08/2022</t>
+          <t>24/10/2023</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1262,27 +1275,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>You with the Sad Eyes: A Memoir</t>
+          <t>Joyful, Anyway</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Christina Applegate</t>
+          <t>Kate Bowler</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Little, Brown and Company</t>
+          <t>Random House Publishing Group</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -1322,17 +1335,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wild Rescues: A Paramedic’s Extreme Adventures in Yosemite, Yellowstone, and Grand Teton</t>
+          <t>Straight from the Heart: The official autobiography by the legendary Total Eclipse of the Heart singer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kevin Grange</t>
+          <t>Bonnie Tyler</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Chicago Review Press</t>
+          <t>Coronet Books</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1342,7 +1355,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06/04/2021</t>
+          <t>28/09/2023</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1355,27 +1368,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Start With Yourself: A New Vision for Work &amp; Life</t>
+          <t>You with the Sad Eyes: A Memoir</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Emma Grede</t>
+          <t>Christina Applegate</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Avid Reader Press/Simon &amp; Schuster</t>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>03/03/2026</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1398,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Born a Crime: Stories from a South African Childhood</t>
+          <t>Wild Rescues: A Paramedic’s Extreme Adventures in Yosemite, Yellowstone, and Grand Teton</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trevor Noah</t>
+          <t>Kevin Grange</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Spiegel &amp; Grau</t>
+          <t>Chicago Review Press</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1405,7 +1418,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>15/11/2016</t>
+          <t>06/04/2021</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1587,7 +1600,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bantam Spectra</t>
+          <t>Bantam Books</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1610,28 +1623,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>True Paranormal Stories From Cops</t>
+          <t>Throne of Glass</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scary Studios</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Scary Studios</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
-        </is>
+          <t>02/08/2012</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1640,7 +1656,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Throne of Glass</t>
+          <t>A Court of Wings and Ruin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1660,7 +1676,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>02/08/2012</t>
+          <t>02/05/2017</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1673,27 +1689,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A Court of Wings and Ruin</t>
+          <t>Iron Flame</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>Rebecca Yarros</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bloomsbury Publishing</t>
+          <t>Entangled Publishing, LLC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>02/05/2017</t>
+          <t>07/11/2023</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1716,7 +1732,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bloomsbury Publishing</t>
+          <t>Bloomsbury YA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1739,17 +1755,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Iron Flame</t>
+          <t>True Paranormal Stories From Cops</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rebecca Yarros</t>
+          <t>Scary Studios</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Red Tower Books (Entangled Publishing)</t>
+          <t>Scary Studios</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1759,11 +1775,8 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>07/11/2023</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
+          <t>07/07/2026</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1875,7 +1888,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pck;</t>
+          <t>Marieme Seck</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1885,12 +1898,10 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25/01/2025</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1931,17 +1942,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Detached: How to Let Go, Heal, and Become Irresistible</t>
+          <t>Mastering Conversation Skills Goodbye Awkwardness. Learn to Master the Art of Conversation and Become A Great Communicator, Even if You've Always Been Shy or Hate Small Talk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sabrina Alexis Bendory</t>
+          <t>Helen Stone</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Thought Catalog Books</t>
+          <t>Author's Republic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1951,10 +1962,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>01/03/2020</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1962,27 +1975,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mastering Conversation Skills Goodbye Awkwardness. Learn to Master the Art of Conversation and Become A Great Communicator, Even if You've Always Been Shy or Hate Small Talk</t>
+          <t>The Subtle Art of Not Giving a F*ck: A Counterintuitive Approach to Living a Good Life</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Helen Stone</t>
+          <t>Mark Manson</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Author's Republic</t>
+          <t>HarperOne</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01/03/2020</t>
+          <t>13/09/2016</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1995,32 +2008,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Subtle Art of Not Giving a F*ck: A Counterintuitive Approach to Living a Good Life</t>
+          <t>Detached: How to Let Go, Heal, and Become Irresistible</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mark Manson</t>
+          <t>Sabrina Alexis Bendory</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HarperOne</t>
+          <t>Thought Catalog Books</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13/09/2016</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2028,17 +2039,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Mountain is You: Transforming Self-Sabotage Into Self-Mastery</t>
+          <t>Sex So Great She Can't Get Enough</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brianna Wiest</t>
+          <t>Barbara Keesling PhD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thought Catalog Books</t>
+          <t>M. Evans &amp; Company</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2048,7 +2059,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28/05/2020</t>
+          <t>25/09/2005</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2061,30 +2072,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>How to Not Die in Prison: A Survival Guide</t>
+          <t>Self Discipline: Develop Everlasting Habits to Master Self-Control, Productivity, Mental Toughness, and a Spartan Mindset for Creating a Life of Success to Beat Addiction, Procrastination, &amp; Laziness</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Taylor Sheridan, Tom Nelson</t>
+          <t>Steve G. Martin</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>GA Publishing</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>26/02/2022</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2092,17 +2105,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12 Laws of the Universe</t>
+          <t>The Mountain is You: Transforming Self-Sabotage Into Self-Mastery</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Manhardeep Singh</t>
+          <t>Brianna Wiest</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Independently published</t>
+          <t>Thought Catalog Books</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2112,7 +2125,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20/10/2021</t>
+          <t>28/05/2020</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2125,7 +2138,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Law of Attraction: Secrets to manifesting more of what you want and less of what you don't</t>
+          <t>12 Laws of the Universe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2135,7 +2148,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Echo Point Books &amp; Media, LLC</t>
+          <t>Independently published</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2145,7 +2158,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21/01/2025</t>
+          <t>01/10/2021</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2158,32 +2171,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sex So Great She Can't Get Enough</t>
+          <t>How to Not Die in Prison: A Survival Guide</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Barbara Keesling PhD</t>
+          <t>Taylor Sheridan, Tom Nelson</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>M. Evans &amp; Company</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2281,17 +2292,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Harry Potter and the Sorcerer's Stone</t>
+          <t>Not giving a F*ck Anymore.: Stop People-Pleasing, Set Boundaries, and Start Living on Your Own Terms.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>J.K. Rowling</t>
+          <t>Marieme Seck</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Scholastic Corporation</t>
+          <t>Marieme Seck</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2301,11 +2312,8 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01/09/1998</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
+          <t>18/06/2026</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2314,27 +2322,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cancel Me If You Can</t>
+          <t>Famesick: A Memoir</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dave Portnoy</t>
+          <t>Lena Dunham</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Gallery Books</t>
+          <t>Random House</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -2344,27 +2352,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Famesick: A Memoir</t>
+          <t>The Calamity Club: A Novel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lena Dunham</t>
+          <t>Kathryn Stockett</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Random House</t>
+          <t>Spiegel &amp; Grau</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -2374,17 +2382,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Not giving a F*ck Anymore.: Stop People-Pleasing, Set Boundaries, and Start Living on Your Own Terms.</t>
+          <t>Cancel Me If You Can</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Marieme Seck</t>
+          <t>Dave Portnoy</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Gallery Books</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -2394,28 +2412,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Theo of Golden: A Novel</t>
+          <t>Harry Potter and the Sorcerer's Stone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Allen Levi</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Atria Books</t>
+          <t>Scholastic</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
-        </is>
+          <t>01/09/1998</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2424,27 +2445,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Calamity Club: A Novel</t>
+          <t>Theo of Golden: A Novel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kathryn Stockett</t>
+          <t>Allen Levi</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Spiegel &amp; Grau</t>
+          <t>Atria Books</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>11/11/2025</t>
         </is>
       </c>
     </row>
@@ -2484,28 +2505,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>It Could Have Been Her: A Novel</t>
+          <t>How to Hold a Cockroach: A book for those who are free and don't know it</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lisa Jewell</t>
+          <t>Matthew Maxwell</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Atria Books</t>
+          <t>Hearthstone</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
-        </is>
+          <t>10/04/2020</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2557,7 +2581,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Zando</t>
+          <t>Slowburn</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2567,7 +2591,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/08/2024</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2580,28 +2604,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Strangers: A Memoir of Marriage</t>
+          <t>The Fellowship of the Ring</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belle Burden</t>
+          <t>J.R.R. Tolkien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Dial Press</t>
+          <t>George Allen &amp; Unwin</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
-        </is>
+          <t>29/07/1954</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2610,27 +2637,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Fellowship of the Ring</t>
+          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>J.R.R. Tolkien</t>
+          <t>James Clear</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>George Allen &amp; Unwin</t>
+          <t>Avery Publishing</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>29/07/1954</t>
+          <t>16/10/2018</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2643,27 +2670,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
+          <t>The Odyssey</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>James Clear</t>
+          <t>Homer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Avery Publishing</t>
+          <t>Antonios Damilas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16/10/2018</t>
+          <t>01/01/1488</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2676,27 +2703,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>How to Hold a Cockroach: A book for those who are free and don't know it</t>
+          <t>Harry Potter and the Chamber of Secrets</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Matthew Maxwell</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hearthstone</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10/04/2020</t>
+          <t>02/07/1998</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2709,27 +2736,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dear Debbie</t>
+          <t>It Could Have Been Her: A Novel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
+          <t>Lisa Jewell</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Poisoned Pen Press</t>
+          <t>Atria Books</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -2739,31 +2766,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Remarkably Bright Creatures: A Read with Jenna Pick</t>
+          <t>Strangers: A Memoir of Marriage</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Shelby Van Pelt</t>
+          <t>Belle Burden</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ecco Press</t>
+          <t>Dial Press</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>03/05/2022</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
+          <t>13/01/2026</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -2772,17 +2796,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Claude AI for Beginners: How to Use Claude to Write Better, Research Faster, and Boost Productivity</t>
+          <t>Dear Debbie</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nicholas Hunter</t>
+          <t>Freida McFadden</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Poisoned Pen Press</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>Independent</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>27/01/2026</t>
         </is>
       </c>
     </row>
@@ -2792,28 +2826,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Joyful, Anyway</t>
+          <t>Remarkably Bright Creatures: A Read with Jenna Pick</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kate Bowler</t>
+          <t>Shelby Van Pelt</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>The Dial Press</t>
+          <t>Ecco</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
-        </is>
+          <t>03/05/2022</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2822,27 +2859,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Every Summer After</t>
+          <t>Fourth Wing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Carley Fortune</t>
+          <t>Rebecca Yarros</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Berkley Books</t>
+          <t>Red Tower Books (Entangled Publishing)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10/05/2022</t>
+          <t>02/05/2023</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2888,27 +2925,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Harry Potter and the Chamber of Secrets</t>
+          <t>The Five-Star Weekend</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>J.K. Rowling</t>
+          <t>Elin Hilderbrand</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>02/07/1998</t>
+          <t>13/06/2023</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2921,27 +2958,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fourth Wing</t>
+          <t>Red Rising</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rebecca Yarros</t>
+          <t>Pierce Brown</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Red Tower Books (Entangled Publishing)</t>
+          <t>Del Rey Books</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>02/05/2023</t>
+          <t>28/01/2014</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2987,28 +3024,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nobody Knows You're Here: A Psychological Suspense Thriller</t>
+          <t>Every Summer After</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bryn Greenwood</t>
+          <t>Carley Fortune</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Podium Publishing</t>
+          <t>Berkley Books</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
-        </is>
+          <t>10/05/2022</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -3017,27 +3057,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Our Perfect Storm</t>
+          <t>Whistler: A Novel</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Carley Fortune</t>
+          <t>Ann Patchett</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Berkley Books</t>
+          <t>Harper</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
     </row>
@@ -3047,17 +3087,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Red Rising</t>
+          <t>Dolly All the Time: A GMA Book Club Pick</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pierce Brown</t>
+          <t>Annabel Monaghan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Del Rey Books</t>
+          <t>G.P. Putnam's Sons</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3067,11 +3107,8 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>28/01/2014</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
+          <t>26/05/2026</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -3080,27 +3117,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Night We Met</t>
+          <t>Our Perfect Storm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Abby Jimenez</t>
+          <t>Carley Fortune</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Forever</t>
+          <t>Berkley Books</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -3110,27 +3147,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Whistler: A Novel</t>
+          <t>Nobody Knows You're Here: A Psychological Suspense Thriller</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ann Patchett</t>
+          <t>Bryn Greenwood</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Podium Publishing</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>16/09/2025</t>
         </is>
       </c>
     </row>
@@ -3140,27 +3177,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dolly All the Time: A GMA Book Club Pick</t>
+          <t>Mad Mabel: A Novel</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Annabel Monaghan</t>
+          <t>Sally Hepworth</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>G.P. Putnam's Sons</t>
+          <t>St. Martin's Press</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3277,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Zando</t>
+          <t>Slowburn</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3250,7 +3287,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/08/2024</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -3326,17 +3363,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Phoebe Berman's Gonna Lose It: A Novel</t>
+          <t>Unbound</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brooke Averick</t>
+          <t>Ali Hazelwood</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Crown Publishing Group (NY)</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3346,7 +3383,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
     </row>
@@ -3356,27 +3393,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>This Story Might Save Your Life: A Novel</t>
+          <t>Phoebe Berman's Gonna Lose It: A Novel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tiffany Crum</t>
+          <t>Brooke Averick</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Flatiron Books: Pine &amp; Cedar</t>
+          <t>Crown</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
@@ -3386,31 +3423,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Love Hypothesis</t>
+          <t>The Romance Revival</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ali Hazelwood</t>
+          <t>Christina Lauren</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Berkley Books</t>
+          <t>Gallery Books</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14/09/2021</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
+          <t>14/07/2026</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -3452,27 +3486,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Into the Blue: Reese's Book Club: A Love Story</t>
+          <t>This Story Might Save Your Life: A Novel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emma Brodie</t>
+          <t>Tiffany Crum</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ballantine Books</t>
+          <t>Flatiron Books: Pine &amp; Cedar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
     </row>
@@ -3482,31 +3516,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Caught Up</t>
+          <t>Into the Blue: Reese's Book Club: A Love Story</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
+          <t>Emma Brodie</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Zando - Slowburn</t>
+          <t>Ballantine Books</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
+          <t>07/04/2026</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -3758,28 +3789,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Fourth Option: A Novel</t>
+          <t>The Silent Patient</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jack Carr, M.P. Woodward</t>
+          <t>Alex Michaelides</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Atria/Emily Bestler Books</t>
+          <t>Celadon Books</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
-        </is>
+          <t>05/02/2019</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3808,7 +3842,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/08/2020</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3821,28 +3855,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Judge Stone: A Novel</t>
+          <t>The Coworker</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>James Patterson, Viola Davis</t>
+          <t>Freida McFadden</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Little, Brown and Company</t>
+          <t>Poisoned Pen Press</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
-        </is>
+          <t>29/08/2023</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3851,27 +3888,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nine Lives: A Novel</t>
+          <t>The Guilty Ones: A Psychological Thriller</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Catherine Steadman</t>
+          <t>Kyla Stone</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bantam</t>
+          <t>Paper Moon Press</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>31/12/2025</t>
         </is>
       </c>
     </row>
@@ -3881,27 +3918,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Silent Patient</t>
+          <t>The Housemaid: An absolutely addictive psychological thriller with a jaw-dropping twist</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alex Michaelides</t>
+          <t>Freida McFadden</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Celadon Books</t>
+          <t>Bookouture</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>05/02/2019</t>
+          <t>01/04/2022</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3984,7 +4021,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Scholastic Corporation</t>
+          <t>Scholastic</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4040,27 +4077,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Disney*Pixar Storybook Collection</t>
+          <t>Harry Potter and the Prisoner of Azkaban</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Disney Press</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Disney Press</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>08/07/1999</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -4073,27 +4110,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Harry Potter and the Prisoner of Azkaban</t>
+          <t>Frog and Toad Audio Collection: A Box Set of 3 Books From the Classic Animal Friendship and Adventure Series for Kids [ages 4-8] – A Heartwarming Caldecott and Newbery Honor Collection</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>J.K. Rowling</t>
+          <t>Arnold Lobel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08/07/1999</t>
+          <t>02/11/2004</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -4106,27 +4143,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Frog and Toad Audio Collection: A Box Set of 3 Books From the Classic Animal Friendship and Adventure Series for Kids [ages 4-8] – A Heartwarming Caldecott and Newbery Honor Collection</t>
+          <t>The Lightning Thief: Percy Jackson and the Olympians: Book 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arnold Lobel</t>
+          <t>Rick Riordan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Miramax Books</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>02/11/2004</t>
+          <t>28/06/2005</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -4139,17 +4176,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Lightning Thief: Percy Jackson and the Olympians: Book 1</t>
+          <t>Disney*Pixar Storybook Collection</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rick Riordan</t>
+          <t>Disney Press</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Miramax Books</t>
+          <t>Disney Press</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4159,7 +4196,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28/06/2005</t>
+          <t>01/01/2006</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -4172,27 +4209,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Story of Moana: A Tale of Courage and Adventure</t>
+          <t>Little House in the Big Woods</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kari Sutherland</t>
+          <t>Laura Ingalls Wilder</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Disney Press</t>
+          <t>Harper &amp; Brothers</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11/10/2016</t>
+          <t>01/01/1932</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4205,17 +4242,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Boxcar Children Collection Volume 1: The Boxcar Children, Surprise Island, Yellow House Mystery</t>
+          <t>How to Catch a Monster</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gertrude Chandler Warner</t>
+          <t>Adam Wallace</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rand McNally</t>
+          <t>Sourcebooks Wonderland</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4225,7 +4262,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/01/1924</t>
+          <t>05/09/2017</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4271,17 +4308,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Lion, the Witch and the Wardrobe: Classic Fantasy Tale for Kids</t>
+          <t>Walter the Whale Shark: And His Teeny Tiny Teeth</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C. S. Lewis</t>
+          <t>Katrine Crow</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Geoffrey Bles</t>
+          <t>Flowerpot Press</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4291,7 +4328,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16/10/1950</t>
+          <t>07/07/2020</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4430,27 +4467,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hunt, Gather, Parent: What Ancient Cultures Can Teach Us About the Lost Art of Raising Happy, Helpful Little Humans</t>
+          <t>What If Friendship, Not Marriage, Was at the Center of Life?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Michaeleen Doucleff</t>
+          <t>Rhaina Cohen, The Atlantic</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Avid Reader Press / Simon &amp; Schuster</t>
+          <t>The Atlantic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/03/2021</t>
+          <t>01/10/2020</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -4463,27 +4500,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Things I Told My Notes App: The Funny And Candid Guide To Living Your Best Life From the Gen - Z Bridget Jones</t>
+          <t>Dear Therapist: I'm Having an Affair and I've Never Been Happier. Should I Confess?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Milly Goldsmith</t>
+          <t>Lori Gottlieb, The Atlantic</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bantam</t>
+          <t>The Atlantic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -4493,27 +4525,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Good Inside: A Practical Guide to Resilient Parenting Prioritizing Connection Over Correction</t>
+          <t>Hunt, Gather, Parent: What Ancient Cultures Can Teach Us About the Lost Art of Raising Happy, Helpful Little Humans</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Becky Kennedy</t>
+          <t>Michaeleen Doucleff</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Harper Wave</t>
+          <t>Avid Reader Press / Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13/09/2022</t>
+          <t>02/03/2021</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -4526,31 +4558,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Expecting Better: Why the Conventional Pregnancy Wisdom Is Wrong--and What You Really Need to Know</t>
+          <t>Dear Therapist: I Can't Stand My Sister-in-Law</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Emily Oster</t>
+          <t>Lori Gottlieb, The Atlantic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Penguin Books</t>
+          <t>The Atlantic</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>20/08/2013</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -4559,23 +4583,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dear Therapist: I Can't Stand My Sister-in-Law</t>
+          <t>Good Inside: A Practical Guide to Resilient Parenting Prioritizing Connection Over Correction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lori Gottlieb, The Atlantic</t>
+          <t>Becky Kennedy</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The Atlantic</t>
+          <t>Harper Wave</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>13/09/2022</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -4584,7 +4616,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cribsheet: A Data-Driven Guide to Better, More Relaxed Parenting, from Birth to Preschool</t>
+          <t>Expecting Better: Why the Conventional Pregnancy Wisdom Is Wrong--and What You Really Need to Know</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4594,7 +4626,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Penguin Books</t>
+          <t>The Penguin Press</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4604,7 +4636,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21/04/2020</t>
+          <t>20/08/2013</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4617,27 +4649,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What If Friendship, Not Marriage, Was at the Center of Life?</t>
+          <t>The Seven Principles for Making Marriage Work: A Practical Guide from the Country’s Foremost Relationship Expert, Revised and Updated</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rhaina Cohen, The Atlantic</t>
+          <t>John M. Gottman PhD, Nan Silver</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The Atlantic</t>
+          <t>Three Rivers Press</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>16/03/1999</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4650,17 +4682,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Seven Principles for Making Marriage Work: A Practical Guide from the Country’s Foremost Relationship Expert, Revised and Updated</t>
+          <t>Cribsheet: A Data-Driven Guide to Better, More Relaxed Parenting, from Birth to Preschool</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>John M. Gottman PhD, Nan Silver</t>
+          <t>Emily Oster</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Harmony</t>
+          <t>Penguin Press</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4670,7 +4702,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01/01/1999</t>
+          <t>09/04/2019</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4751,11 +4783,6 @@
           <t>Yuval Noah Harari</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Harvill Secker</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Independent</t>
@@ -4763,7 +4790,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>04/09/2014</t>
+          <t>01/01/2011</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -4806,7 +4833,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mythos</t>
+          <t>Odyssey: The Greek Myths Reimagined</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4826,7 +4853,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -4839,22 +4866,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Third Reich: A History of Nazi Germany</t>
+          <t>Mythos</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thomas Childers</t>
+          <t>Stephen Fry</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Michael Joseph</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4872,28 +4899,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Finest Hotel in Kabul: A People's History of Afghanistan</t>
+          <t>The Third Reich: A History of Nazi Germany</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lyse Doucet</t>
+          <t>Thomas Childers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Allen Lane</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
-        </is>
+          <t>10/10/2017</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -4935,17 +4965,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Odyssey: The Greek Myths Reimagined</t>
+          <t>The Very Secret Sex Lives of Medieval Women: An Inside Look at Women &amp; Sex in Medieval Times</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stephen Fry</t>
+          <t>Rosalie Gilbert</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Michael Joseph</t>
+          <t>Mango Publishing</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4955,7 +4985,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>27/10/2020</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4968,27 +4998,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Guns Up!: A Firsthand Account of the Vietnam War</t>
+          <t>Codename Nemo: The Hunt for a Nazi U-Boat and the Elusive Enigma Machine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Johnnie Clark</t>
+          <t>Charles Lachman</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ballantine Books</t>
+          <t>Diversion Books</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12/06/1984</t>
+          <t>04/06/2024</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -5001,27 +5031,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1929: Inside the Greatest Crash in Wall Street History--and How It Shattered a Nation</t>
+          <t>The Finest Hotel in Kabul: A People's History of Afghanistan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Andrew Ross Sorkin</t>
+          <t>Lyse Doucet</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Viking Press</t>
+          <t>Cornerstone</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>18/09/2025</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5240,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01/01/2010</t>
+          <t>01/11/2010</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -5231,23 +5261,10 @@
           <t>Zondervan</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Zondervan</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>01/01/2015</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5256,28 +5273,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stand Firm and Act Like Men: Becoming the Man You Were Created to Be Instead of Who the World Says You Are</t>
+          <t>Mere Christianity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Joby Martin, Charles Martin</t>
+          <t>C. S. Lewis</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Faithwords</t>
+          <t>Geoffrey Bles</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
-        </is>
+          <t>07/07/1952</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -5286,31 +5306,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mere Christianity</t>
+          <t>Stand Firm and Act Like Men: Becoming the Man You Were Created to Be Instead of Who the World Says You Are</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C. S. Lewis</t>
+          <t>Joby Martin, Charles Martin</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Geoffrey Bles</t>
+          <t>FaithWords</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07/07/1952</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
+          <t>07/10/2025</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -5352,27 +5369,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Book of Enoch</t>
+          <t>The Secret</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>George Schodde</t>
+          <t>Rhonda Byrne</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>W. F. Draper</t>
+          <t>Atria Books</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/01/1882</t>
+          <t>01/11/2006</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -5676,18 +5693,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>True Paranormal Stories: 10 Real Encounters You'll Never Forget</t>
+          <t>Midnight Sun</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Scary Studios</t>
+          <t>Stephenie Meyer</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Hachette</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>04/08/2020</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -5696,31 +5726,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Midnight Sun</t>
+          <t>True Paranormal Stories: 10 Real Encounters You'll Never Forget</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stephenie Meyer</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Little, Brown and Company</t>
+          <t>Scary Studios</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hachette</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>04/08/2020</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -5729,27 +5746,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Better Than the Movies</t>
+          <t>Harry Potter and the Half-Blood Prince</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lynn Painter</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury, Scholastic</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>04/05/2021</t>
+          <t>16/07/2005</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -5762,27 +5779,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Harry Potter and the Half-Blood Prince</t>
+          <t>Better Than the Movies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>J.K. Rowling</t>
+          <t>Lynn Painter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bloomsbury (UK) and Scholastic (US)</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16/07/2005</t>
+          <t>04/05/2021</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/audiobooks.xlsx
+++ b/audiobooks.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Psychology of Money: Timeless lessons on wealth, greed, and happiness</t>
+          <t>The Psychology of Money: The transformative multimillion-copy personal finance bestseller</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>08/09/2020</t>
+          <t>01/01/2020</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,28 +762,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Disrupt Everything—and Win: Take Control of Your Future</t>
+          <t>Never Split the Difference: Unlock Your Persuasion Potential in Professional and Personal Life</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>James Patterson, Patrick Leddin PhD</t>
+          <t>Chris Voss, Tahl Raz</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Little, Brown and Company</t>
+          <t>Harper Business</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
-        </is>
+          <t>17/05/2016</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -792,27 +795,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Never Split the Difference: Unlock Your Persuasion Potential in Professional and Personal Life</t>
+          <t>Extreme Ownership: How U.S. Navy SEALs Lead and Win</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chris Voss, Tahl Raz</t>
+          <t>Jocko Willink, Leif Babin</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Harper Business</t>
+          <t>St. Martin's Press</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17/05/2016</t>
+          <t>20/10/2015</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -825,31 +828,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Extreme Ownership: How U.S. Navy SEALs Lead and Win</t>
+          <t>Speak Like a CEO: How to Speak with Power, Lead with Clarity, and Command Any Room Without Saying a Word Too Much</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jocko Willink, Leif Babin</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>St. Martin's Press</t>
+          <t>CALDER MP KNOX</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Macmillan</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>20/10/2015</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -858,17 +848,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unreasonable Hospitality: The Remarkable Power of Giving People More Than They Expect</t>
+          <t>How to Talk to Anyone and Be More Charismatic: Improve Communication &amp; People Skills, Master Small Talk, Build Confidence &amp; Influence, Overcome Social Anxiety, and Make Friends in Any Conversation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Will Guidara</t>
+          <t>Nathan Soren</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Optimism Press</t>
+          <t>Nathan Soren</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -878,7 +868,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25/10/2022</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -891,17 +881,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>How to Talk to Anyone and Be More Charismatic: Improve Communication &amp; People Skills, Master Small Talk, Build Confidence &amp; Influence, Overcome Social Anxiety, and Make Friends in Any Conversation</t>
+          <t>Unreasonable Hospitality: The Remarkable Power of Giving People More Than They Expect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nathan Soren</t>
+          <t>Will Guidara</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nathan Soren</t>
+          <t>Optimism Press</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -911,7 +901,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>25/10/2022</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -924,27 +914,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Speak Like a CEO: How to Speak with Power, Lead with Clarity, and Command Any Room Without Saying a Word Too Much</t>
+          <t>The 7 Habits of Highly Effective People: 30th Anniversary Edition</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CALDER MP KNOX</t>
+          <t>Stephen R. Covey, Sean Covey</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>McGraw-Hill Companies</t>
+          <t>Free Press</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/04/2005</t>
+          <t>01/01/1989</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -957,27 +947,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The 7 Habits of Highly Effective People: 30th Anniversary Edition</t>
+          <t>Think and Grow Rich</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stephen R. Covey, Sean Covey</t>
+          <t>Mitch Horowitz, Napoleon Hill, Theresa Puskar</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>The Ralston Society</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/01/1989</t>
+          <t>01/01/1937</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -990,17 +980,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Millionaire Mindset and Habits for Success</t>
+          <t>Think and Grow Rich! The Original Version, Restored and Revised</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>M.A. Myers</t>
+          <t>Napoleon Hill, Ross Cornwell</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Author's Republic</t>
+          <t>The Ralston Society</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1010,7 +1000,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24/10/2022</t>
+          <t>01/03/1937</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1023,17 +1013,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Think and Grow Rich</t>
+          <t>Las 32 leyes inquebrantables del dinero y el éxito: Transforma tu vida y libera tu potencial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Napoleon Hill</t>
+          <t>Brian Tracy</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>The Ralston Society</t>
+          <t>Reverté Management</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1043,7 +1033,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01/03/1937</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1189,12 +1179,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dey Street Books</t>
+          <t>HarperCollins Publishers</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1209,27 +1199,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Woman in Me</t>
+          <t>Kitchen Confidential: Adventures in the Culinary Underbelly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Britney Spears</t>
+          <t>Anthony Bourdain, Irvine Welsh</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gallery Books</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24/10/2023</t>
+          <t>01/01/2000</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1242,31 +1232,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kitchen Confidential: Adventures in the Culinary Underbelly</t>
+          <t>Dogs, Boys, and Other Things I’ve Cried About: A Memoir</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Anthony Bourdain, Irvine Welsh</t>
+          <t>Isabel Klee</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>William Morrow</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01/01/2000</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+          <t>28/04/2026</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1275,17 +1262,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Joyful, Anyway</t>
+          <t>The Make-Believe: A Memoir of Magic and Madness</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kate Bowler</t>
+          <t>Hannah Murray</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Random House Publishing Group</t>
+          <t>Dial Press</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1295,7 +1282,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -1335,31 +1322,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Straight from the Heart: The official autobiography by the legendary Total Eclipse of the Heart singer</t>
+          <t>In the Days of My Youth I Was Told What It Means to Be a Man: A Memoir</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bonnie Tyler</t>
+          <t>Tom Junod</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Coronet Books</t>
+          <t>Doubleday</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28/09/2023</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
+          <t>10/03/2026</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1368,12 +1352,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>You with the Sad Eyes: A Memoir</t>
+          <t>Going There (read by Katie Couric)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Christina Applegate</t>
+          <t>Katie Couric</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1388,8 +1372,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
-        </is>
+          <t>26/10/2021</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1398,31 +1385,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wild Rescues: A Paramedic’s Extreme Adventures in Yosemite, Yellowstone, and Grand Teton</t>
+          <t>You with the Sad Eyes: A Memoir</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kevin Grange</t>
+          <t>Christina Applegate</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Chicago Review Press</t>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06/04/2021</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
+          <t>03/03/2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1436,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1534,7 +1518,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Red Tower Books (Entangled Publishing)</t>
+          <t>Red Tower Books</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1600,7 +1584,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bantam Books</t>
+          <t>Bantam Spectra</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1676,7 +1660,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>02/05/2017</t>
+          <t>01/05/2017</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1699,7 +1683,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Entangled Publishing, LLC</t>
+          <t>Red Tower Books (Entangled Publishing)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1755,60 +1739,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>True Paranormal Stories From Cops</t>
+          <t>Crown of Midnight</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Scary Studios</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Scary Studios</t>
+          <t>Bloomsbury USA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Crown of Midnight</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Sarah J. Maas</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Bloomsbury USA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>15/08/2013</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+          <t>27/08/2013</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1942,27 +1896,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mastering Conversation Skills Goodbye Awkwardness. Learn to Master the Art of Conversation and Become A Great Communicator, Even if You've Always Been Shy or Hate Small Talk</t>
+          <t>The Subtle Art of Not Giving a F*ck: A Counterintuitive Approach to Living a Good Life</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Helen Stone</t>
+          <t>Mark Manson</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Author's Republic</t>
+          <t>HarperOne</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/03/2020</t>
+          <t>13/09/2016</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1975,32 +1929,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Subtle Art of Not Giving a F*ck: A Counterintuitive Approach to Living a Good Life</t>
+          <t>Regulate Your F*cking Nervous System: The No-Nonsense Guide to Understanding Why Your Body Won't Calm Down (And How to Finally Fix It)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mark Manson</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HarperOne</t>
-        </is>
-      </c>
+          <t>Marieme Seck</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>13/09/2016</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2039,17 +1983,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sex So Great She Can't Get Enough</t>
+          <t>Mastering Conversation Skills Goodbye Awkwardness. Learn to Master the Art of Conversation and Become A Great Communicator, Even if You've Always Been Shy or Hate Small Talk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Barbara Keesling PhD</t>
+          <t>Helen Stone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>M. Evans &amp; Company</t>
+          <t>Author's Republic</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2059,7 +2003,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25/09/2005</t>
+          <t>31/03/2020</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2072,17 +2016,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Self Discipline: Develop Everlasting Habits to Master Self-Control, Productivity, Mental Toughness, and a Spartan Mindset for Creating a Life of Success to Beat Addiction, Procrastination, &amp; Laziness</t>
+          <t>The Mountain is You: Transforming Self-Sabotage Into Self-Mastery</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Steve G. Martin</t>
+          <t>Brianna Wiest</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GA Publishing</t>
+          <t>Thought Catalog Books</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2092,7 +2036,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>26/02/2022</t>
+          <t>28/05/2020</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2105,17 +2049,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Mountain is You: Transforming Self-Sabotage Into Self-Mastery</t>
+          <t>Sex So Great She Can't Get Enough</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brianna Wiest</t>
+          <t>Barbara Keesling PhD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thought Catalog Books</t>
+          <t>M. Evans &amp; Company</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2125,7 +2069,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28/05/2020</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2138,17 +2082,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12 Laws of the Universe</t>
+          <t>Stop Letting Everything Affect You: How to break free from overthinking, emotional chaos and self-sabotage</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Manhardeep Singh</t>
+          <t>Daniel Chidiac</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Independently published</t>
+          <t>Undercover Publishing House</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2158,7 +2102,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/10/2021</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2171,30 +2115,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>How to Not Die in Prison: A Survival Guide</t>
+          <t>The Power of Now</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Taylor Sheridan, Tom Nelson</t>
+          <t>Eckhart Tolle</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Namaste Publishing</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>01/01/1997</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2292,17 +2238,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Not giving a F*ck Anymore.: Stop People-Pleasing, Set Boundaries, and Start Living on Your Own Terms.</t>
+          <t>Harry Potter and the Sorcerer's Stone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marieme Seck</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Marieme Seck</t>
+          <t>Scholastic</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2312,8 +2258,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
-        </is>
+          <t>01/09/1998</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2322,27 +2271,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Famesick: A Memoir</t>
+          <t>The Calamity Club: A Novel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lena Dunham</t>
+          <t>Kathryn Stockett</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Random House</t>
+          <t>Spiegel &amp; Grau</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
     </row>
@@ -2352,27 +2301,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Calamity Club: A Novel</t>
+          <t>Famesick: A Memoir</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kathryn Stockett</t>
+          <t>Lena Dunham</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Spiegel &amp; Grau</t>
+          <t>Random House</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
     </row>
@@ -2382,27 +2331,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cancel Me If You Can</t>
+          <t>Not giving a F*ck Anymore.: Stop People-Pleasing, Set Boundaries, and Start Living on Your Own Terms.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dave Portnoy</t>
+          <t>Marieme Seck</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gallery Books</t>
+          <t>Marieme Seck</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -2412,31 +2361,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Harry Potter and the Sorcerer's Stone</t>
+          <t>Theo of Golden: A Novel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>J.K. Rowling</t>
+          <t>Allen Levi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Scholastic</t>
+          <t>Atria Books</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01/09/1998</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
+          <t>03/10/2025</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -2445,17 +2391,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Theo of Golden: A Novel</t>
+          <t>Cancel Me If You Can</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Allen Levi</t>
+          <t>Dave Portnoy</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Atria Books</t>
+          <t>Gallery Books</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2465,7 +2411,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -2475,28 +2421,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Regime Change: Inside the Imperial Presidency of Donald Trump</t>
+          <t>Harry Potter and the Chamber of Secrets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Maggie Haberman, Jonathan Swan</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
-        </is>
+          <t>02/07/1998</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2505,17 +2454,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>How to Hold a Cockroach: A book for those who are free and don't know it</t>
+          <t>Lights Out: An Into Darkness Novel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Matthew Maxwell</t>
+          <t>Navessa Allen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hearthstone</t>
+          <t>Zando - Slowburn</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2525,7 +2474,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10/04/2020</t>
+          <t>06/08/2024</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2538,27 +2487,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A Court of Thorns and Roses</t>
+          <t>The Odyssey</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>Homer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bloomsbury Publishing</t>
+          <t>Antonios Damilas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>05/05/2015</t>
+          <t>01/01/1488</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2571,27 +2520,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lights Out: An Into Darkness Novel</t>
+          <t>A Court of Thorns and Roses</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Slowburn</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>01/08/2024</t>
+          <t>05/05/2015</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2604,27 +2553,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Fellowship of the Ring</t>
+          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>J.R.R. Tolkien</t>
+          <t>James Clear</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>George Allen &amp; Unwin</t>
+          <t>Avery Publishing</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>29/07/1954</t>
+          <t>16/10/2018</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2637,31 +2586,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
+          <t>Regime Change: Inside the Imperial Presidency of Donald Trump</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>James Clear</t>
+          <t>Maggie Haberman, Jonathan Swan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Avery Publishing</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16/10/2018</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
+          <t>23/06/2026</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -2670,27 +2616,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Odyssey</t>
+          <t>The Fellowship of the Ring</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Homer</t>
+          <t>J.R.R. Tolkien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Antonios Damilas</t>
+          <t>George Allen &amp; Unwin</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>01/01/1488</t>
+          <t>29/07/1954</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2703,27 +2649,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Harry Potter and the Chamber of Secrets</t>
+          <t>The Odyssey</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>J.K. Rowling</t>
+          <t>Homer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Antonios Damilas</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>02/07/1998</t>
+          <t>01/01/1488</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2736,27 +2682,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>It Could Have Been Her: A Novel</t>
+          <t>Strangers: A Memoir of Marriage</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lisa Jewell</t>
+          <t>Belle Burden</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Atria Books</t>
+          <t>Dial Press</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
     </row>
@@ -2766,27 +2712,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Strangers: A Memoir of Marriage</t>
+          <t>Dear Debbie</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belle Burden</t>
+          <t>Freida McFadden</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Dial Press</t>
+          <t>Poisoned Pen Press</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
     </row>
@@ -2796,27 +2742,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dear Debbie</t>
+          <t>Mad Mabel: A Novel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
+          <t>Sally Hepworth</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Poisoned Pen Press</t>
+          <t>St. Martin's Press</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -2826,27 +2772,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Remarkably Bright Creatures: A Read with Jenna Pick</t>
+          <t>Fourth Wing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Shelby Van Pelt</t>
+          <t>Rebecca Yarros</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ecco</t>
+          <t>Red Tower Books</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>03/05/2022</t>
+          <t>02/05/2023</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2859,27 +2805,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fourth Wing</t>
+          <t>The 48 Laws of Power</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rebecca Yarros</t>
+          <t>Robert Greene</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Red Tower Books (Entangled Publishing)</t>
+          <t>Viking Press</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>02/05/2023</t>
+          <t>01/01/1998</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2925,31 +2871,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Five-Star Weekend</t>
+          <t>Whistler: A Novel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Elin Hilderbrand</t>
+          <t>Ann Patchett</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Little, Brown and Company</t>
+          <t>Harper</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>13/06/2023</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
+          <t>02/06/2026</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -2991,27 +2934,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Correspondent: A Novel</t>
+          <t>Remarkably Bright Creatures: A Read with Jenna Pick</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Virginia Evans</t>
+          <t>Shelby Van Pelt</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Crown Publishing Group</t>
+          <t>Ecco Press</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>29/04/2025</t>
+          <t>03/05/2022</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3024,31 +2967,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Every Summer After</t>
+          <t>The Shampoo Effect: A Read with Jenna Pick: A Novel</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Carley Fortune</t>
+          <t>Jenny Jackson</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Berkley Books</t>
+          <t>Pamela Dorman Books</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10/05/2022</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
+          <t>30/06/2026</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -3057,27 +2997,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Whistler: A Novel</t>
+          <t>Phoebe Berman's Gonna Lose It: A Novel</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ann Patchett</t>
+          <t>Brooke Averick</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Crown</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
@@ -3087,17 +3027,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dolly All the Time: A GMA Book Club Pick</t>
+          <t>The Correspondent: A Novel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Annabel Monaghan</t>
+          <t>Virginia Evans</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>G.P. Putnam's Sons</t>
+          <t>Crown Publishing Group</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3107,8 +3047,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
-        </is>
+          <t>29/04/2025</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3117,17 +3060,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Our Perfect Storm</t>
+          <t>Biological War: A Scenario</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carley Fortune</t>
+          <t>Annie Jacobsen</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Berkley Books</t>
+          <t>Dutton</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3137,7 +3080,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
     </row>
@@ -3147,27 +3090,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nobody Knows You're Here: A Psychological Suspense Thriller</t>
+          <t>My Husband's Wife: A Novel</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bryn Greenwood</t>
+          <t>Alice Feeney</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Podium Publishing</t>
+          <t>Flatiron Books</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>20/01/2026</t>
         </is>
       </c>
     </row>
@@ -3177,28 +3120,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mad Mabel: A Novel</t>
+          <t>A Game of Thrones: A Song of Ice and Fire: Book One</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sally Hepworth</t>
+          <t>George R. R. Martin</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>St. Martin's Press</t>
+          <t>Bantam Spectra</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
-        </is>
+          <t>01/08/1996</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3277,7 +3223,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Slowburn</t>
+          <t>Zando - Slowburn</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3287,7 +3233,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01/08/2024</t>
+          <t>06/08/2024</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -3300,17 +3246,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Every Summer After</t>
+          <t>Phoebe Berman's Gonna Lose It: A Novel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Carley Fortune</t>
+          <t>Brooke Averick</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Berkley Books</t>
+          <t>Crown</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3320,11 +3266,8 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10/05/2022</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
+          <t>26/05/2026</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -3363,17 +3306,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unbound</t>
+          <t>Every Summer After</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ali Hazelwood</t>
+          <t>Carley Fortune</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Berkley Books</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3383,8 +3326,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
-        </is>
+          <t>10/05/2022</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3393,27 +3339,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Phoebe Berman's Gonna Lose It: A Novel</t>
+          <t>The Romance Revival</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brooke Averick</t>
+          <t>Christina Lauren</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Crown</t>
+          <t>Gallery Books</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
     </row>
@@ -3423,17 +3369,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Romance Revival</t>
+          <t>The Seven Husbands of Evelyn Hugo: A Novel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Christina Lauren</t>
+          <t>Taylor Jenkins Reid</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gallery Books</t>
+          <t>Atria Books</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3443,8 +3389,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
-        </is>
+          <t>13/06/2017</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3453,31 +3402,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Seven Husbands of Evelyn Hugo: A Novel</t>
+          <t>This Story Might Save Your Life: A Novel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Taylor Jenkins Reid</t>
+          <t>Tiffany Crum</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Atria Books</t>
+          <t>Flatiron Books: Pine &amp; Cedar</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>13/06/2017</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
+          <t>10/03/2026</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -3486,27 +3432,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>This Story Might Save Your Life: A Novel</t>
+          <t>Into the Blue: Reese's Book Club: A Love Story</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tiffany Crum</t>
+          <t>Emma Brodie</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Flatiron Books: Pine &amp; Cedar</t>
+          <t>Ballantine Books</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -3516,28 +3462,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Into the Blue: Reese's Book Club: A Love Story</t>
+          <t>Caught Up</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Emma Brodie</t>
+          <t>Navessa Allen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ballantine Books</t>
+          <t>Zando</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
-        </is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3546,27 +3495,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Quicksilver: The Fae &amp; Alchemy Series, Book 1</t>
+          <t>The Love Hypothesis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Callie Hart</t>
+          <t>Ali Hazelwood</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Self-published</t>
+          <t>Berkley Books</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>04/06/2024</t>
+          <t>14/09/2021</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3639,27 +3588,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>It Could Have Been Her: A Novel</t>
+          <t>Dear Debbie</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lisa Jewell</t>
+          <t>Freida McFadden</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Atria Books</t>
+          <t>Poisoned Pen Press</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
     </row>
@@ -3669,27 +3618,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dear Debbie</t>
+          <t>Mad Mabel: A Novel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
+          <t>Sally Hepworth</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Poisoned Pen Press</t>
+          <t>St. Martin's Press</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -3699,27 +3648,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nobody Knows You're Here: A Psychological Suspense Thriller</t>
+          <t>It Could Have Been Her: A Novel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bryn Greenwood</t>
+          <t>Lisa Jewell</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Podium Publishing</t>
+          <t>Atria Books</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>23/06/2026</t>
         </is>
       </c>
     </row>
@@ -3729,27 +3678,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mad Mabel: A Novel</t>
+          <t>Nobody Knows You're Here: A Psychological Suspense Thriller</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sally Hepworth</t>
+          <t>Bryn Greenwood</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>St. Martin's Press</t>
+          <t>Podium Publishing</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>16/09/2025</t>
         </is>
       </c>
     </row>
@@ -3822,17 +3771,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Asylum Confessions: Deathbed Confessions of the Criminally Insane</t>
+          <t>The Guilty Ones: A Psychological Thriller</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jack Steen</t>
+          <t>Kyla Stone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deathbed Publishing</t>
+          <t>Paper Moon Press</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3842,11 +3791,8 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
+          <t>28/01/2026</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -3855,17 +3801,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Coworker</t>
+          <t>The Asylum Confessions: Deathbed Confessions of the Criminally Insane</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
+          <t>Jack Steen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Poisoned Pen Press</t>
+          <t>Deathbed Publishing</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3875,7 +3821,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29/08/2023</t>
+          <t>10/03/2021</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3888,28 +3834,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Guilty Ones: A Psychological Thriller</t>
+          <t>Incidents Around the House: A Novel: The Inspiration for the Movie "Other Mommy"</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kyla Stone</t>
+          <t>Josh Malerman</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paper Moon Press</t>
+          <t>Del Rey</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31/12/2025</t>
-        </is>
+          <t>25/06/2024</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4110,27 +4059,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Frog and Toad Audio Collection: A Box Set of 3 Books From the Classic Animal Friendship and Adventure Series for Kids [ages 4-8] – A Heartwarming Caldecott and Newbery Honor Collection</t>
+          <t>The Lightning Thief: Percy Jackson and the Olympians: Book 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arnold Lobel</t>
+          <t>Rick Riordan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Miramax Books</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>02/11/2004</t>
+          <t>28/06/2005</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -4143,27 +4092,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Lightning Thief: Percy Jackson and the Olympians: Book 1</t>
+          <t>Frog and Toad Audio Collection: A Box Set of 3 Books From the Classic Animal Friendship and Adventure Series for Kids [ages 4-8] – A Heartwarming Caldecott and Newbery Honor Collection</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rick Riordan</t>
+          <t>Arnold Lobel</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Miramax Books</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28/06/2005</t>
+          <t>02/11/2004</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -4209,27 +4158,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Little House in the Big Woods</t>
+          <t>The Lion, the Witch and the Wardrobe: Classic Fantasy Tale for Kids</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Laura Ingalls Wilder</t>
+          <t>C. S. Lewis</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Harper &amp; Brothers</t>
+          <t>Geoffrey Bles</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/01/1932</t>
+          <t>16/10/1950</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4242,27 +4191,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>How to Catch a Monster</t>
+          <t>Little House in the Big Woods</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Adam Wallace</t>
+          <t>Laura Ingalls Wilder</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sourcebooks Wonderland</t>
+          <t>Harper &amp; Brothers</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>05/09/2017</t>
+          <t>01/01/1932</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4275,17 +4224,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>How to Catch a Mermaid</t>
+          <t>The Boxcar Children Collection Volume 1: The Boxcar Children, Surprise Island, Yellow House Mystery</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Adam Wallace</t>
+          <t>Gertrude Chandler Warner</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sourcebooks Wonderland</t>
+          <t>Rand McNally</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4295,7 +4244,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17/07/2018</t>
+          <t>01/01/1924</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4308,17 +4257,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Walter the Whale Shark: And His Teeny Tiny Teeth</t>
+          <t>Spider-Man Storybook Collection</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Katrine Crow</t>
+          <t>Marvel Press</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Flowerpot Press</t>
+          <t>Marvel Press</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4328,7 +4277,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>07/07/2020</t>
+          <t>03/05/2016</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4467,27 +4416,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What If Friendship, Not Marriage, Was at the Center of Life?</t>
+          <t>Hunt, Gather, Parent: What Ancient Cultures Can Teach Us About the Lost Art of Raising Happy, Helpful Little Humans</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rhaina Cohen, The Atlantic</t>
+          <t>Michaeleen Doucleff</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The Atlantic</t>
+          <t>Avid Reader Press/Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/10/2020</t>
+          <t>01/01/2021</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -4500,23 +4449,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dear Therapist: I'm Having an Affair and I've Never Been Happier. Should I Confess?</t>
+          <t>Good Inside: A Practical Guide to Resilient Parenting Prioritizing Connection Over Correction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lori Gottlieb, The Atlantic</t>
+          <t>Becky Kennedy</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The Atlantic</t>
+          <t>Harper Wave</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>13/09/2022</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -4525,27 +4482,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hunt, Gather, Parent: What Ancient Cultures Can Teach Us About the Lost Art of Raising Happy, Helpful Little Humans</t>
+          <t>Expecting Better: Why the Conventional Pregnancy Wisdom Is Wrong--and What You Really Need to Know</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Michaeleen Doucleff</t>
+          <t>Emily Oster</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Avid Reader Press / Simon &amp; Schuster</t>
+          <t>The Penguin Press</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>02/03/2021</t>
+          <t>01/01/2013</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -4558,17 +4515,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dear Therapist: I Can't Stand My Sister-in-Law</t>
+          <t>The Seven Principles for Making Marriage Work: A Practical Guide from the Country’s Foremost Relationship Expert, Revised and Updated</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lori Gottlieb, The Atlantic</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>The Atlantic</t>
+          <t>John M. Gottman PhD, Nan Silver</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4583,27 +4535,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Good Inside: A Practical Guide to Resilient Parenting Prioritizing Connection Over Correction</t>
+          <t>Cribsheet: A Data-Driven Guide to Better, More Relaxed Parenting, from Birth to Preschool</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Becky Kennedy</t>
+          <t>Emily Oster</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Harper Wave</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>13/09/2022</t>
+          <t>09/04/2019</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4616,31 +4568,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Expecting Better: Why the Conventional Pregnancy Wisdom Is Wrong--and What You Really Need to Know</t>
+          <t>REBUILD: The Complete Guide to Starting Over as a Man</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emily Oster</t>
+          <t>Ralph Brewer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The Penguin Press</t>
+          <t>Help For Men</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>20/08/2013</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
+          <t>16/12/2025</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -4649,27 +4598,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Seven Principles for Making Marriage Work: A Practical Guide from the Country’s Foremost Relationship Expert, Revised and Updated</t>
+          <t>It's Not You: Identifying and Healing from Narcissistic People</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>John M. Gottman PhD, Nan Silver</t>
+          <t>Ramani Durvasula PhD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Three Rivers Press</t>
+          <t>The Open Field</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16/03/1999</t>
+          <t>20/02/2024</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4682,27 +4631,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cribsheet: A Data-Driven Guide to Better, More Relaxed Parenting, from Birth to Preschool</t>
+          <t>Mating in Captivity: In Search of Erotic Intelligence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Emily Oster</t>
+          <t>Esther Perel</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Penguin Press</t>
+          <t>Harper</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>09/04/2019</t>
+          <t>05/09/2006</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4720,7 +4669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4775,12 +4724,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sapiens: A Brief History of Humankind</t>
+          <t>Mythos</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yuval Noah Harari</t>
+          <t>Stephen Fry</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Michael Joseph</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4790,7 +4744,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01/01/2011</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -4803,17 +4757,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sisters of Scandal: Mind-blowing tales of history's boldest and baddest women</t>
+          <t>Sapiens: A Brief History of Humankind</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ainslie Harvey</t>
+          <t>Yuval Noah Harari</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Affirm Press</t>
+          <t>Signal</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4823,8 +4777,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
-        </is>
+          <t>28/10/2014</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4866,22 +4823,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mythos</t>
+          <t>The Third Reich: A History of Nazi Germany</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Stephen Fry</t>
+          <t>Thomas Childers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Michael Joseph</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4899,27 +4856,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Third Reich: A History of Nazi Germany</t>
+          <t>Nuclear War: A Scenario</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thomas Childers</t>
+          <t>Annie Jacobsen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Dutton</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10/10/2017</t>
+          <t>26/03/2024</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -4965,31 +4922,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Very Secret Sex Lives of Medieval Women: An Inside Look at Women &amp; Sex in Medieval Times</t>
+          <t>1929: Inside the Greatest Crash in Wall Street History--and How It Shattered a Nation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rosalie Gilbert</t>
+          <t>Andrew Ross Sorkin</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mango Publishing</t>
+          <t>Viking Press</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>27/10/2020</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
+          <t>14/10/2025</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -4998,17 +4952,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Codename Nemo: The Hunt for a Nazi U-Boat and the Elusive Enigma Machine</t>
+          <t>Christian History: An Enthralling Guide to the Story of Christianity, From Its Early Origins Through the Crusades and Knights Templar to Modern Times</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charles Lachman</t>
+          <t>Billy Wellman, Enthralling History</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Diversion Books</t>
+          <t>Billy Wellman</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5018,7 +4972,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>04/06/2024</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -5031,28 +4985,64 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Finest Hotel in Kabul: A People's History of Afghanistan</t>
+          <t>The Power Broker: Robert Moses and the Fall of New York</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lyse Doucet</t>
+          <t>Robert A. Caro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cornerstone</t>
+          <t>Alfred A. Knopf</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>01/01/1974</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Codename Nemo: The Hunt for a Nazi U-Boat and the Elusive Enigma Machine</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Charles Lachman</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Diversion Books</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>18/09/2025</t>
-        </is>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>04/06/2024</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5141,7 +5131,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10/04/2020</t>
+          <t>01/04/2020</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -5207,7 +5197,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/01/1611</t>
+          <t>02/05/1611</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -5220,27 +5210,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Alchemist: A Modern Classic Fable of Spiritual Healing, Self-Discovery, and the Power of Dreams in a Visually Stunning Graphic Novel—Get Lost in the Pages of This Captivating Summer Read</t>
+          <t>A Life of Meaning: Exploring Our Deepest Questions and Motivations</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paulo Coelho</t>
+          <t>James Hollis PhD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HarperOne</t>
+          <t>Macmillan Audio</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01/11/2010</t>
+          <t>01/12/2020</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -5253,18 +5243,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NIV Listener's Audio Bible: Complete Bible: Vocal Performance by Max McLean</t>
+          <t>The Alchemist: A Modern Classic Fable of Spiritual Healing, Self-Discovery, and the Power of Dreams in a Visually Stunning Graphic Novel—Get Lost in the Pages of This Captivating Summer Read</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Zondervan</t>
+          <t>Paulo Coelho</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HarperOne</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>01/11/2010</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -5273,27 +5276,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mere Christianity</t>
+          <t>NIV Listener's Audio Bible: Complete Bible: Vocal Performance by Max McLean</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C. S. Lewis</t>
+          <t>Zondervan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Geoffrey Bles</t>
+          <t>Zondervan</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>07/07/1952</t>
+          <t>01/01/2015</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -5306,28 +5309,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Stand Firm and Act Like Men: Becoming the Man You Were Created to Be Instead of Who the World Says You Are</t>
+          <t>The Four Agreements: A Practical Guide to Personal Freedom</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Joby Martin, Charles Martin</t>
+          <t>Don Miguel Ruiz, Janet Mills</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FaithWords</t>
+          <t>Amber-Allen Publishing</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
-        </is>
+          <t>01/01/1997</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -5336,17 +5342,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Four Agreements: A Practical Guide to Personal Freedom</t>
+          <t>The Book of Enoch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Don Miguel Ruiz, Janet Mills</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Amber-Allen Publishing</t>
+          <t>George Schodde</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5356,7 +5357,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/01/1997</t>
+          <t>01/01/1882</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -5369,27 +5370,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Secret</t>
+          <t>Becoming Supernatural: How Common People Are Doing The Uncommon</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rhonda Byrne</t>
+          <t>Dr. Joe Dispenza</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Atria Books</t>
+          <t>Hay House LLC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/11/2006</t>
+          <t>31/10/2017</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -5402,31 +5403,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Becoming Supernatural: How Common People Are Doing The Uncommon</t>
+          <t>Stand Firm and Act Like Men: Becoming the Man You Were Created to Be Instead of Who the World Says You Are</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dr. Joe Dispenza</t>
+          <t>Joby Martin, Charles Martin</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hay House</t>
+          <t>Faithwords</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>05/03/2019</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
+          <t>07/10/2025</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5440,7 +5438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5571,7 +5569,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Bloomsbury (UK) / Scholastic (US)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5594,27 +5592,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Summer I Turned Pretty</t>
+          <t>Harry Potter and the Order of the Phoenix</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jenny Han</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>05/05/2009</t>
+          <t>21/06/2003</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -5660,27 +5658,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Harry Potter and the Order of the Phoenix</t>
+          <t>The Summer I Turned Pretty</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>J.K. Rowling</t>
+          <t>Jenny Han</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Simon &amp; Schuster Books for Young Readers</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21/06/2003</t>
+          <t>05/05/2009</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -5693,27 +5691,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Midnight Sun</t>
+          <t>Children of Blood and Bone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stephenie Meyer</t>
+          <t>Tomi Adeyemi</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Little, Brown and Company</t>
+          <t>Henry Holt Books for Young Readers</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>04/08/2020</t>
+          <t>06/03/2018</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -5726,18 +5724,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>True Paranormal Stories: 10 Real Encounters You'll Never Forget</t>
+          <t>Midnight Sun</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Scary Studios</t>
+          <t>Stephenie Meyer</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
+          <t>Hachette</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>04/08/2020</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -5756,7 +5767,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bloomsbury, Scholastic</t>
+          <t>Bloomsbury (UK) / Scholastic (US)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5770,39 +5781,6 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Better Than the Movies</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Lynn Painter</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Simon &amp; Schuster</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>04/05/2021</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
         <v>1</v>
       </c>
     </row>
